--- a/VT_REG1_IND_V12_New.xlsx
+++ b/VT_REG1_IND_V12_New.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261016\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E61D79E3-25AF-4458-8B11-87129383DAFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD6948E-3508-4432-926B-11419BD36A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -6349,7 +6349,9 @@
         <v>1</v>
       </c>
       <c r="H21" s="125"/>
-      <c r="I21" s="125"/>
+      <c r="I21" s="117">
+        <v>1</v>
+      </c>
       <c r="J21" s="125"/>
       <c r="K21" s="125"/>
       <c r="L21" s="125"/>
@@ -8122,8 +8124,8 @@
         <v>DIOAPP</v>
       </c>
       <c r="E23" s="73">
-        <f>'EB1'!$U$7*'EB1'!$U$21/(G23*H23)*1.01</f>
-        <v>0.24567332813926943</v>
+        <f>'EB1'!$G$7*'EB1'!$G$21/(G23*H23)*1.01</f>
+        <v>0.60185037579908673</v>
       </c>
       <c r="F23" s="121">
         <v>0.2</v>
@@ -8139,7 +8141,7 @@
       </c>
       <c r="K23" s="122">
         <f>E23*G23*H23</f>
-        <v>3.8737770381000005</v>
+        <v>9.4899767256000001</v>
       </c>
       <c r="M23" s="108" t="s">
         <v>97</v>

--- a/VT_REG1_IND_V12_New.xlsx
+++ b/VT_REG1_IND_V12_New.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261016\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0AD6948E-3508-4432-926B-11419BD36A9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A015CA-6DB9-44DE-860A-7F003358A36D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1539,7 +1539,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="184">
   <si>
     <t>CommName</t>
   </si>
@@ -3333,13 +3333,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>25212</xdr:colOff>
-      <xdr:row>32</xdr:row>
+      <xdr:row>31</xdr:row>
       <xdr:rowOff>8965</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>3847831</xdr:colOff>
-      <xdr:row>37</xdr:row>
+      <xdr:row>36</xdr:row>
       <xdr:rowOff>85165</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7341,7 +7341,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:U34"/>
+  <dimension ref="B1:U33"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -7852,7 +7852,7 @@
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B18" s="112" t="str">
-        <f t="shared" ref="B18:B24" si="0">O18</f>
+        <f t="shared" ref="B18:B23" si="0">O18</f>
         <v>IBOILECOA</v>
       </c>
       <c r="C18" t="s">
@@ -7880,7 +7880,7 @@
       </c>
       <c r="J18" s="17"/>
       <c r="K18" s="122">
-        <f t="shared" ref="K18:K25" si="1">E18*G18*H18</f>
+        <f t="shared" ref="K18:K24" si="1">E18*G18*H18</f>
         <v>20.533143207600002</v>
       </c>
       <c r="M18" s="108" t="s">
@@ -7895,11 +7895,11 @@
         <v>Demand Technologies Industry Sector - Existing Boiler - Solid Fuels</v>
       </c>
       <c r="Q18" s="112" t="str">
-        <f t="shared" ref="Q18:Q26" si="2">$E$2</f>
+        <f t="shared" ref="Q18:Q25" si="2">$E$2</f>
         <v>PJ</v>
       </c>
       <c r="R18" s="112" t="str">
-        <f t="shared" ref="R18:R26" si="3">$E$2&amp;"a"</f>
+        <f t="shared" ref="R18:R25" si="3">$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
     </row>
@@ -8009,22 +8009,22 @@
     </row>
     <row r="21" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B21" s="112" t="str">
-        <f t="shared" si="0"/>
-        <v>IBOILEDSL</v>
+        <f>O21</f>
+        <v>IOAPPEDSL</v>
       </c>
       <c r="C21" t="s">
         <v>177</v>
       </c>
       <c r="D21" s="112" t="str">
-        <f>$O$5</f>
-        <v>DIBOIL</v>
+        <f>$O$6</f>
+        <v>DIOAPP</v>
       </c>
       <c r="E21" s="73">
-        <f>'EB1'!$G$7*'EB1'!$G$20/(G21*H21)*1.01</f>
-        <v>0</v>
+        <f>'EB1'!$G$7*'EB1'!$G$21/(G21*H21)*1.01</f>
+        <v>0.60185037579908673</v>
       </c>
       <c r="F21" s="121">
-        <v>0.8</v>
+        <v>0.2</v>
       </c>
       <c r="G21" s="121">
         <v>0.5</v>
@@ -8033,22 +8033,22 @@
         <v>31.536000000000001</v>
       </c>
       <c r="I21" s="42">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="K21" s="122">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>E21*G21*H21</f>
+        <v>9.4899767256000001</v>
       </c>
       <c r="M21" s="108" t="s">
         <v>97</v>
       </c>
       <c r="O21" s="112" t="str">
-        <f>LEFT($B$2)&amp;'EB1'!$C$20&amp;$I$2&amp;'EB1'!G$2</f>
-        <v>IBOILEDSL</v>
+        <f>LEFT($B$2)&amp;'EB1'!$C$21&amp;$I$2&amp;'EB1'!G$2</f>
+        <v>IOAPPEDSL</v>
       </c>
       <c r="P21" s="112" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$20&amp;" - "&amp;'EB1'!$G$3</f>
-        <v>Demand Technologies Industry Sector - Existing Boiler - Diesel oil</v>
+        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$21&amp;" - "&amp;'EB1'!$G$3</f>
+        <v>Demand Technologies Industry Sector - Existing Other Appliance - Diesel oil</v>
       </c>
       <c r="Q21" s="112" t="str">
         <f t="shared" si="2"/>
@@ -8114,21 +8114,21 @@
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B23" s="112" t="str">
         <f t="shared" si="0"/>
-        <v>IOAPPEDSL</v>
+        <v>ICOMPEELC</v>
       </c>
       <c r="C23" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="D23" s="112" t="str">
-        <f>$O$6</f>
-        <v>DIOAPP</v>
+        <f>$O$7</f>
+        <v>DICOMP</v>
       </c>
       <c r="E23" s="73">
-        <f>'EB1'!$G$7*'EB1'!$G$21/(G23*H23)*1.01</f>
-        <v>0.60185037579908673</v>
+        <f>'EB1'!$U$7*'EB1'!$U$22/(G23*H23)*1.01</f>
+        <v>0.19653866251141555</v>
       </c>
       <c r="F23" s="121">
-        <v>0.2</v>
+        <v>0.95</v>
       </c>
       <c r="G23" s="121">
         <v>0.5</v>
@@ -8140,19 +8140,19 @@
         <v>10</v>
       </c>
       <c r="K23" s="122">
-        <f>E23*G23*H23</f>
-        <v>9.4899767256000001</v>
+        <f t="shared" si="1"/>
+        <v>3.0990216304800007</v>
       </c>
       <c r="M23" s="108" t="s">
         <v>97</v>
       </c>
       <c r="O23" s="112" t="str">
-        <f>LEFT($B$2)&amp;'EB1'!$C$21&amp;$I$2&amp;'EB1'!G$2</f>
-        <v>IOAPPEDSL</v>
+        <f>LEFT($B$2)&amp;'EB1'!$C$22&amp;$I$2&amp;'EB1'!U$2</f>
+        <v>ICOMPEELC</v>
       </c>
       <c r="P23" s="112" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$21&amp;" - "&amp;'EB1'!$G$3</f>
-        <v>Demand Technologies Industry Sector - Existing Other Appliance - Diesel oil</v>
+        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$22&amp;" - "&amp;'EB1'!$U$3</f>
+        <v>Demand Technologies Industry Sector - Existing Compressor - Electricity</v>
       </c>
       <c r="Q23" s="112" t="str">
         <f t="shared" si="2"/>
@@ -8165,22 +8165,22 @@
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B24" s="112" t="str">
-        <f t="shared" si="0"/>
-        <v>ICOMPEELC</v>
+        <f>O24</f>
+        <v>IPUMPEELC</v>
       </c>
       <c r="C24" t="s">
         <v>179</v>
       </c>
       <c r="D24" s="112" t="str">
-        <f>$O$7</f>
-        <v>DICOMP</v>
+        <f>$O$8</f>
+        <v>DIPUMP</v>
       </c>
       <c r="E24" s="73">
-        <f>'EB1'!$U$7*'EB1'!$U$22/(G24*H24)*1.01</f>
-        <v>0.19653866251141555</v>
+        <f>'EB1'!$U$7*'EB1'!$U$23/(G24*H24)*1.01</f>
+        <v>0.24567332813926943</v>
       </c>
       <c r="F24" s="121">
-        <v>0.95</v>
+        <v>0.6</v>
       </c>
       <c r="G24" s="121">
         <v>0.5</v>
@@ -8191,20 +8191,21 @@
       <c r="I24" s="42">
         <v>10</v>
       </c>
+      <c r="J24" s="103"/>
       <c r="K24" s="122">
         <f t="shared" si="1"/>
-        <v>3.0990216304800007</v>
+        <v>3.8737770381000005</v>
       </c>
       <c r="M24" s="108" t="s">
         <v>97</v>
       </c>
       <c r="O24" s="112" t="str">
-        <f>LEFT($B$2)&amp;'EB1'!$C$22&amp;$I$2&amp;'EB1'!U$2</f>
-        <v>ICOMPEELC</v>
+        <f>LEFT($B$2)&amp;'EB1'!$C$23&amp;$I$2&amp;'EB1'!U$2</f>
+        <v>IPUMPEELC</v>
       </c>
       <c r="P24" s="112" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$22&amp;" - "&amp;'EB1'!$U$3</f>
-        <v>Demand Technologies Industry Sector - Existing Compressor - Electricity</v>
+        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$23&amp;" - "&amp;'EB1'!$U$3</f>
+        <v>Demand Technologies Industry Sector - Existing Pump - Electricity</v>
       </c>
       <c r="Q24" s="112" t="str">
         <f t="shared" si="2"/>
@@ -8218,46 +8219,46 @@
     <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" s="112" t="str">
         <f>O25</f>
-        <v>IPUMPEELC</v>
+        <v>IMOTOEELC</v>
       </c>
       <c r="C25" t="s">
         <v>179</v>
       </c>
       <c r="D25" s="112" t="str">
-        <f>$O$8</f>
-        <v>DIPUMP</v>
+        <f>$O$9</f>
+        <v>DIMOTO</v>
       </c>
       <c r="E25" s="73">
-        <f>'EB1'!$U$7*'EB1'!$U$23/(G25*H25)*1.01</f>
-        <v>0.24567332813926943</v>
+        <f>'EB1'!$U$7*'EB1'!$U$24/(G25*H25)*1.01</f>
+        <v>0.28574701535038105</v>
       </c>
       <c r="F25" s="121">
-        <v>0.6</v>
+        <v>0.9</v>
       </c>
       <c r="G25" s="121">
         <v>0.5</v>
       </c>
       <c r="H25" s="119">
-        <v>31.536000000000001</v>
+        <v>32.536000000000001</v>
       </c>
       <c r="I25" s="42">
         <v>10</v>
       </c>
       <c r="J25" s="103"/>
       <c r="K25" s="122">
-        <f t="shared" si="1"/>
-        <v>3.8737770381000005</v>
+        <f t="shared" ref="K25" si="4">E25*G25*H25</f>
+        <v>4.648532445719999</v>
       </c>
       <c r="M25" s="108" t="s">
         <v>97</v>
       </c>
       <c r="O25" s="112" t="str">
-        <f>LEFT($B$2)&amp;'EB1'!$C$23&amp;$I$2&amp;'EB1'!U$2</f>
-        <v>IPUMPEELC</v>
+        <f>LEFT($B$2)&amp;'EB1'!$C$24&amp;$I$2&amp;'EB1'!U$2</f>
+        <v>IMOTOEELC</v>
       </c>
       <c r="P25" s="112" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$23&amp;" - "&amp;'EB1'!$U$3</f>
-        <v>Demand Technologies Industry Sector - Existing Pump - Electricity</v>
+        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$24&amp;" - "&amp;'EB1'!$U$3</f>
+        <v>Demand Technologies Industry Sector - Existing Heavy Motor - Electricity</v>
       </c>
       <c r="Q25" s="112" t="str">
         <f t="shared" si="2"/>
@@ -8269,57 +8270,9 @@
       </c>
     </row>
     <row r="26" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B26" s="112" t="str">
-        <f>O26</f>
-        <v>IMOTOEELC</v>
-      </c>
-      <c r="C26" t="s">
-        <v>179</v>
-      </c>
-      <c r="D26" s="112" t="str">
-        <f>$O$9</f>
-        <v>DIMOTO</v>
-      </c>
-      <c r="E26" s="73">
-        <f>'EB1'!$U$7*'EB1'!$U$24/(G26*H26)*1.01</f>
-        <v>0.28574701535038105</v>
-      </c>
-      <c r="F26" s="121">
-        <v>0.9</v>
-      </c>
-      <c r="G26" s="121">
-        <v>0.5</v>
-      </c>
-      <c r="H26" s="119">
-        <v>32.536000000000001</v>
-      </c>
-      <c r="I26" s="42">
-        <v>10</v>
-      </c>
+      <c r="I26" s="103"/>
       <c r="J26" s="103"/>
-      <c r="K26" s="122">
-        <f t="shared" ref="K26" si="4">E26*G26*H26</f>
-        <v>4.648532445719999</v>
-      </c>
-      <c r="M26" s="108" t="s">
-        <v>97</v>
-      </c>
-      <c r="O26" s="112" t="str">
-        <f>LEFT($B$2)&amp;'EB1'!$C$24&amp;$I$2&amp;'EB1'!U$2</f>
-        <v>IMOTOEELC</v>
-      </c>
-      <c r="P26" s="112" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$24&amp;" - "&amp;'EB1'!$U$3</f>
-        <v>Demand Technologies Industry Sector - Existing Heavy Motor - Electricity</v>
-      </c>
-      <c r="Q26" s="112" t="str">
-        <f t="shared" si="2"/>
-        <v>PJ</v>
-      </c>
-      <c r="R26" s="112" t="str">
-        <f t="shared" si="3"/>
-        <v>PJa</v>
-      </c>
+      <c r="K26" s="17"/>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="I27" s="103"/>
@@ -8327,40 +8280,35 @@
       <c r="K27" s="17"/>
     </row>
     <row r="28" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B28" s="42"/>
+      <c r="C28" s="1" t="s">
+        <v>143</v>
+      </c>
       <c r="I28" s="103"/>
       <c r="J28" s="103"/>
-      <c r="K28" s="17"/>
     </row>
     <row r="29" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B29" s="42"/>
+      <c r="B29" s="72"/>
       <c r="C29" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="I29" s="103"/>
       <c r="J29" s="103"/>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B30" s="72"/>
-      <c r="C30" s="1" t="s">
-        <v>144</v>
-      </c>
       <c r="I30" s="103"/>
       <c r="J30" s="103"/>
+      <c r="L30" s="1"/>
     </row>
     <row r="31" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I31" s="103"/>
-      <c r="J31" s="103"/>
       <c r="L31" s="1"/>
     </row>
     <row r="32" spans="2:21" x14ac:dyDescent="0.25">
       <c r="L32" s="1"/>
     </row>
     <row r="33" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E33" s="7"/>
       <c r="L33" s="1"/>
-    </row>
-    <row r="34" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E34" s="7"/>
-      <c r="L34" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8509,7 +8457,7 @@
         <v>78</v>
       </c>
       <c r="E9" s="76">
-        <f>SUM(DemTechs_IND!K18:K21)</f>
+        <f>SUM(DemTechs_IND!K18:K20)</f>
         <v>81.149407520400004</v>
       </c>
       <c r="G9" s="1" t="s">
@@ -8567,7 +8515,7 @@
         <v>78</v>
       </c>
       <c r="E11" s="76">
-        <f>DemTechs_IND!K24</f>
+        <f>DemTechs_IND!K23</f>
         <v>3.0990216304800007</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -8597,7 +8545,7 @@
         <v>78</v>
       </c>
       <c r="E12" s="76">
-        <f>DemTechs_IND!K25</f>
+        <f>DemTechs_IND!K24</f>
         <v>3.8737770381000005</v>
       </c>
       <c r="G12" s="28" t="s">
@@ -8626,7 +8574,7 @@
         <v>78</v>
       </c>
       <c r="E13" s="76">
-        <f>DemTechs_IND!K26</f>
+        <f>DemTechs_IND!K25</f>
         <v>4.648532445719999</v>
       </c>
       <c r="G13" s="1" t="s">

--- a/VT_REG1_IND_V12_New.xlsx
+++ b/VT_REG1_IND_V12_New.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261016\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78A015CA-6DB9-44DE-860A-7F003358A36D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CCFDF28-F405-4E6B-B8EC-1005B2C62C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -1539,7 +1539,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="187">
   <si>
     <t>CommName</t>
   </si>
@@ -2091,6 +2091,15 @@
   </si>
   <si>
     <t>Other Appliance</t>
+  </si>
+  <si>
+    <t>IBOILEHFO</t>
+  </si>
+  <si>
+    <t>INDHFO</t>
+  </si>
+  <si>
+    <t>Demand Technologies Industry Sector - Existing Boiler - HFO</t>
   </si>
 </sst>
 </file>
@@ -2405,7 +2414,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="22">
     <border>
       <left/>
       <right/>
@@ -2617,6 +2626,43 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFFF0000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFFF0000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFF0000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFF0000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2648,7 +2694,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2897,6 +2943,22 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="15" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="0" fillId="13" borderId="20" xfId="16" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="20" xfId="9" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="29" fillId="18" borderId="21" xfId="27" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="28">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -3333,13 +3395,13 @@
     <xdr:from>
       <xdr:col>12</xdr:col>
       <xdr:colOff>25212</xdr:colOff>
-      <xdr:row>31</xdr:row>
+      <xdr:row>32</xdr:row>
       <xdr:rowOff>8965</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>15</xdr:col>
       <xdr:colOff>3847831</xdr:colOff>
-      <xdr:row>36</xdr:row>
+      <xdr:row>37</xdr:row>
       <xdr:rowOff>85165</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
@@ -7341,7 +7403,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="B1:U33"/>
+  <dimension ref="B1:U34"/>
   <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
@@ -7526,15 +7588,15 @@
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
-      <c r="M6" s="108" t="s">
+      <c r="M6" s="138" t="s">
         <v>85</v>
       </c>
-      <c r="N6" s="112"/>
-      <c r="O6" s="108" t="str">
+      <c r="N6" s="132"/>
+      <c r="O6" s="140" t="str">
         <f>LEFT($M$5,1)&amp;LEFT(B2,1)&amp;'EB1'!$C$21</f>
         <v>DIOAPP</v>
       </c>
-      <c r="P6" s="108" t="str">
+      <c r="P6" s="141" t="str">
         <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB1'!$X$21</f>
         <v>Demand Industry Sector - Other Appliance</v>
       </c>
@@ -7605,7 +7667,9 @@
     <row r="9" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
+      <c r="D9" s="9" t="s">
+        <v>177</v>
+      </c>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
@@ -7852,7 +7916,7 @@
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B18" s="112" t="str">
-        <f t="shared" ref="B18:B23" si="0">O18</f>
+        <f t="shared" ref="B18:B24" si="0">O18</f>
         <v>IBOILECOA</v>
       </c>
       <c r="C18" t="s">
@@ -7880,7 +7944,7 @@
       </c>
       <c r="J18" s="17"/>
       <c r="K18" s="122">
-        <f t="shared" ref="K18:K24" si="1">E18*G18*H18</f>
+        <f t="shared" ref="K18:K25" si="1">E18*G18*H18</f>
         <v>20.533143207600002</v>
       </c>
       <c r="M18" s="108" t="s">
@@ -7895,11 +7959,11 @@
         <v>Demand Technologies Industry Sector - Existing Boiler - Solid Fuels</v>
       </c>
       <c r="Q18" s="112" t="str">
-        <f t="shared" ref="Q18:Q25" si="2">$E$2</f>
+        <f t="shared" ref="Q18:Q26" si="2">$E$2</f>
         <v>PJ</v>
       </c>
       <c r="R18" s="112" t="str">
-        <f t="shared" ref="R18:R25" si="3">$E$2&amp;"a"</f>
+        <f t="shared" ref="R18:R26" si="3">$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
     </row>
@@ -8008,23 +8072,22 @@
       </c>
     </row>
     <row r="21" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B21" s="112" t="str">
-        <f>O21</f>
-        <v>IOAPPEDSL</v>
-      </c>
-      <c r="C21" t="s">
-        <v>177</v>
+      <c r="B21" s="142" t="s">
+        <v>184</v>
+      </c>
+      <c r="C21" s="143" t="s">
+        <v>185</v>
       </c>
       <c r="D21" s="112" t="str">
-        <f>$O$6</f>
-        <v>DIOAPP</v>
+        <f>$O$5</f>
+        <v>DIBOIL</v>
       </c>
       <c r="E21" s="73">
-        <f>'EB1'!$G$7*'EB1'!$G$21/(G21*H21)*1.01</f>
-        <v>0.60185037579908673</v>
+        <f>'EB1'!$L$7*'EB1'!$L$20/(G21*H21)*1.01</f>
+        <v>3.2449824200913241E-3</v>
       </c>
       <c r="F21" s="121">
-        <v>0.2</v>
+        <v>0.8</v>
       </c>
       <c r="G21" s="121">
         <v>0.5</v>
@@ -8033,22 +8096,21 @@
         <v>31.536000000000001</v>
       </c>
       <c r="I21" s="42">
-        <v>10</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="J21" s="17"/>
       <c r="K21" s="122">
-        <f>E21*G21*H21</f>
-        <v>9.4899767256000001</v>
-      </c>
-      <c r="M21" s="108" t="s">
+        <f t="shared" ref="K21" si="4">E21*G21*H21</f>
+        <v>5.1166882800000001E-2</v>
+      </c>
+      <c r="M21" s="142" t="s">
         <v>97</v>
       </c>
-      <c r="O21" s="112" t="str">
-        <f>LEFT($B$2)&amp;'EB1'!$C$21&amp;$I$2&amp;'EB1'!G$2</f>
-        <v>IOAPPEDSL</v>
-      </c>
-      <c r="P21" s="112" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$21&amp;" - "&amp;'EB1'!$G$3</f>
-        <v>Demand Technologies Industry Sector - Existing Other Appliance - Diesel oil</v>
+      <c r="O21" s="142" t="s">
+        <v>184</v>
+      </c>
+      <c r="P21" s="142" t="s">
+        <v>186</v>
       </c>
       <c r="Q21" s="112" t="str">
         <f t="shared" si="2"/>
@@ -8060,53 +8122,55 @@
       </c>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B22" s="112" t="str">
-        <f t="shared" si="0"/>
-        <v>IOAPPEELC</v>
-      </c>
-      <c r="C22" t="s">
-        <v>179</v>
-      </c>
-      <c r="D22" s="112" t="str">
+      <c r="B22" s="130" t="str">
+        <f>O22</f>
+        <v>IOAPPEDSL</v>
+      </c>
+      <c r="C22" s="131" t="s">
+        <v>177</v>
+      </c>
+      <c r="D22" s="132" t="str">
         <f>$O$6</f>
         <v>DIOAPP</v>
       </c>
-      <c r="E22" s="73">
-        <f>'EB1'!$U$7*'EB1'!$U$21/(G22*H22)*1.01</f>
-        <v>0.24567332813926943</v>
-      </c>
-      <c r="F22" s="121">
-        <v>0.95</v>
-      </c>
-      <c r="G22" s="121">
+      <c r="E22" s="133">
+        <f>'EB1'!$G$7*'EB1'!$G$21/(G22*H22)*1.01</f>
+        <v>0.60185037579908673</v>
+      </c>
+      <c r="F22" s="134">
+        <v>0.2</v>
+      </c>
+      <c r="G22" s="134">
         <v>0.5</v>
       </c>
-      <c r="H22" s="119">
+      <c r="H22" s="135">
         <v>31.536000000000001</v>
       </c>
-      <c r="I22" s="42">
+      <c r="I22" s="136">
         <v>10</v>
       </c>
-      <c r="K22" s="122">
-        <f t="shared" si="1"/>
-        <v>3.8737770381000005</v>
-      </c>
-      <c r="M22" s="108" t="s">
+      <c r="J22" s="131"/>
+      <c r="K22" s="137">
+        <f>E22*G22*H22</f>
+        <v>9.4899767256000001</v>
+      </c>
+      <c r="M22" s="138" t="s">
         <v>97</v>
       </c>
-      <c r="O22" s="112" t="str">
-        <f>LEFT($B$2)&amp;'EB1'!$C$21&amp;$I$2&amp;'EB1'!U$2</f>
-        <v>IOAPPEELC</v>
-      </c>
-      <c r="P22" s="112" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$21&amp;" - "&amp;'EB1'!$U$3</f>
-        <v>Demand Technologies Industry Sector - Existing Other Appliance - Electricity</v>
-      </c>
-      <c r="Q22" s="112" t="str">
+      <c r="N22" s="131"/>
+      <c r="O22" s="132" t="str">
+        <f>LEFT($B$2)&amp;'EB1'!$C$21&amp;$I$2&amp;'EB1'!G$2</f>
+        <v>IOAPPEDSL</v>
+      </c>
+      <c r="P22" s="132" t="str">
+        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$21&amp;" - "&amp;'EB1'!$G$3</f>
+        <v>Demand Technologies Industry Sector - Existing Other Appliance - Diesel oil</v>
+      </c>
+      <c r="Q22" s="132" t="str">
         <f t="shared" si="2"/>
         <v>PJ</v>
       </c>
-      <c r="R22" s="112" t="str">
+      <c r="R22" s="139" t="str">
         <f t="shared" si="3"/>
         <v>PJa</v>
       </c>
@@ -8114,18 +8178,18 @@
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B23" s="112" t="str">
         <f t="shared" si="0"/>
-        <v>ICOMPEELC</v>
+        <v>IOAPPEELC</v>
       </c>
       <c r="C23" t="s">
         <v>179</v>
       </c>
       <c r="D23" s="112" t="str">
-        <f>$O$7</f>
-        <v>DICOMP</v>
+        <f>$O$6</f>
+        <v>DIOAPP</v>
       </c>
       <c r="E23" s="73">
-        <f>'EB1'!$U$7*'EB1'!$U$22/(G23*H23)*1.01</f>
-        <v>0.19653866251141555</v>
+        <f>'EB1'!$U$7*'EB1'!$U$21/(G23*H23)*1.01</f>
+        <v>0.24567332813926943</v>
       </c>
       <c r="F23" s="121">
         <v>0.95</v>
@@ -8141,18 +8205,18 @@
       </c>
       <c r="K23" s="122">
         <f t="shared" si="1"/>
-        <v>3.0990216304800007</v>
+        <v>3.8737770381000005</v>
       </c>
       <c r="M23" s="108" t="s">
         <v>97</v>
       </c>
       <c r="O23" s="112" t="str">
-        <f>LEFT($B$2)&amp;'EB1'!$C$22&amp;$I$2&amp;'EB1'!U$2</f>
-        <v>ICOMPEELC</v>
+        <f>LEFT($B$2)&amp;'EB1'!$C$21&amp;$I$2&amp;'EB1'!U$2</f>
+        <v>IOAPPEELC</v>
       </c>
       <c r="P23" s="112" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$22&amp;" - "&amp;'EB1'!$U$3</f>
-        <v>Demand Technologies Industry Sector - Existing Compressor - Electricity</v>
+        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$21&amp;" - "&amp;'EB1'!$U$3</f>
+        <v>Demand Technologies Industry Sector - Existing Other Appliance - Electricity</v>
       </c>
       <c r="Q23" s="112" t="str">
         <f t="shared" si="2"/>
@@ -8165,22 +8229,22 @@
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B24" s="112" t="str">
-        <f>O24</f>
-        <v>IPUMPEELC</v>
+        <f t="shared" si="0"/>
+        <v>ICOMPEELC</v>
       </c>
       <c r="C24" t="s">
         <v>179</v>
       </c>
       <c r="D24" s="112" t="str">
-        <f>$O$8</f>
-        <v>DIPUMP</v>
+        <f>$O$7</f>
+        <v>DICOMP</v>
       </c>
       <c r="E24" s="73">
-        <f>'EB1'!$U$7*'EB1'!$U$23/(G24*H24)*1.01</f>
-        <v>0.24567332813926943</v>
+        <f>'EB1'!$U$7*'EB1'!$U$22/(G24*H24)*1.01</f>
+        <v>0.19653866251141555</v>
       </c>
       <c r="F24" s="121">
-        <v>0.6</v>
+        <v>0.95</v>
       </c>
       <c r="G24" s="121">
         <v>0.5</v>
@@ -8191,21 +8255,20 @@
       <c r="I24" s="42">
         <v>10</v>
       </c>
-      <c r="J24" s="103"/>
       <c r="K24" s="122">
         <f t="shared" si="1"/>
-        <v>3.8737770381000005</v>
+        <v>3.0990216304800007</v>
       </c>
       <c r="M24" s="108" t="s">
         <v>97</v>
       </c>
       <c r="O24" s="112" t="str">
-        <f>LEFT($B$2)&amp;'EB1'!$C$23&amp;$I$2&amp;'EB1'!U$2</f>
-        <v>IPUMPEELC</v>
+        <f>LEFT($B$2)&amp;'EB1'!$C$22&amp;$I$2&amp;'EB1'!U$2</f>
+        <v>ICOMPEELC</v>
       </c>
       <c r="P24" s="112" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$23&amp;" - "&amp;'EB1'!$U$3</f>
-        <v>Demand Technologies Industry Sector - Existing Pump - Electricity</v>
+        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$22&amp;" - "&amp;'EB1'!$U$3</f>
+        <v>Demand Technologies Industry Sector - Existing Compressor - Electricity</v>
       </c>
       <c r="Q24" s="112" t="str">
         <f t="shared" si="2"/>
@@ -8219,46 +8282,46 @@
     <row r="25" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B25" s="112" t="str">
         <f>O25</f>
-        <v>IMOTOEELC</v>
+        <v>IPUMPEELC</v>
       </c>
       <c r="C25" t="s">
         <v>179</v>
       </c>
       <c r="D25" s="112" t="str">
-        <f>$O$9</f>
-        <v>DIMOTO</v>
+        <f>$O$8</f>
+        <v>DIPUMP</v>
       </c>
       <c r="E25" s="73">
-        <f>'EB1'!$U$7*'EB1'!$U$24/(G25*H25)*1.01</f>
-        <v>0.28574701535038105</v>
+        <f>'EB1'!$U$7*'EB1'!$U$23/(G25*H25)*1.01</f>
+        <v>0.24567332813926943</v>
       </c>
       <c r="F25" s="121">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G25" s="121">
         <v>0.5</v>
       </c>
       <c r="H25" s="119">
-        <v>32.536000000000001</v>
+        <v>31.536000000000001</v>
       </c>
       <c r="I25" s="42">
         <v>10</v>
       </c>
       <c r="J25" s="103"/>
       <c r="K25" s="122">
-        <f t="shared" ref="K25" si="4">E25*G25*H25</f>
-        <v>4.648532445719999</v>
+        <f t="shared" si="1"/>
+        <v>3.8737770381000005</v>
       </c>
       <c r="M25" s="108" t="s">
         <v>97</v>
       </c>
       <c r="O25" s="112" t="str">
-        <f>LEFT($B$2)&amp;'EB1'!$C$24&amp;$I$2&amp;'EB1'!U$2</f>
-        <v>IMOTOEELC</v>
+        <f>LEFT($B$2)&amp;'EB1'!$C$23&amp;$I$2&amp;'EB1'!U$2</f>
+        <v>IPUMPEELC</v>
       </c>
       <c r="P25" s="112" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$24&amp;" - "&amp;'EB1'!$U$3</f>
-        <v>Demand Technologies Industry Sector - Existing Heavy Motor - Electricity</v>
+        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$23&amp;" - "&amp;'EB1'!$U$3</f>
+        <v>Demand Technologies Industry Sector - Existing Pump - Electricity</v>
       </c>
       <c r="Q25" s="112" t="str">
         <f t="shared" si="2"/>
@@ -8270,9 +8333,57 @@
       </c>
     </row>
     <row r="26" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I26" s="103"/>
+      <c r="B26" s="112" t="str">
+        <f>O26</f>
+        <v>IMOTOEELC</v>
+      </c>
+      <c r="C26" t="s">
+        <v>179</v>
+      </c>
+      <c r="D26" s="112" t="str">
+        <f>$O$9</f>
+        <v>DIMOTO</v>
+      </c>
+      <c r="E26" s="73">
+        <f>'EB1'!$U$7*'EB1'!$U$24/(G26*H26)*1.01</f>
+        <v>0.28574701535038105</v>
+      </c>
+      <c r="F26" s="121">
+        <v>0.9</v>
+      </c>
+      <c r="G26" s="121">
+        <v>0.5</v>
+      </c>
+      <c r="H26" s="119">
+        <v>32.536000000000001</v>
+      </c>
+      <c r="I26" s="42">
+        <v>10</v>
+      </c>
       <c r="J26" s="103"/>
-      <c r="K26" s="17"/>
+      <c r="K26" s="122">
+        <f t="shared" ref="K26" si="5">E26*G26*H26</f>
+        <v>4.648532445719999</v>
+      </c>
+      <c r="M26" s="108" t="s">
+        <v>97</v>
+      </c>
+      <c r="O26" s="112" t="str">
+        <f>LEFT($B$2)&amp;'EB1'!$C$24&amp;$I$2&amp;'EB1'!U$2</f>
+        <v>IMOTOEELC</v>
+      </c>
+      <c r="P26" s="112" t="str">
+        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$24&amp;" - "&amp;'EB1'!$U$3</f>
+        <v>Demand Technologies Industry Sector - Existing Heavy Motor - Electricity</v>
+      </c>
+      <c r="Q26" s="112" t="str">
+        <f t="shared" si="2"/>
+        <v>PJ</v>
+      </c>
+      <c r="R26" s="112" t="str">
+        <f t="shared" si="3"/>
+        <v>PJa</v>
+      </c>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
       <c r="I27" s="103"/>
@@ -8280,35 +8391,40 @@
       <c r="K27" s="17"/>
     </row>
     <row r="28" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B28" s="42"/>
-      <c r="C28" s="1" t="s">
-        <v>143</v>
-      </c>
       <c r="I28" s="103"/>
       <c r="J28" s="103"/>
+      <c r="K28" s="17"/>
     </row>
     <row r="29" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B29" s="72"/>
+      <c r="B29" s="42"/>
       <c r="C29" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="I29" s="103"/>
       <c r="J29" s="103"/>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="B30" s="72"/>
+      <c r="C30" s="1" t="s">
+        <v>144</v>
+      </c>
       <c r="I30" s="103"/>
       <c r="J30" s="103"/>
-      <c r="L30" s="1"/>
     </row>
     <row r="31" spans="2:21" x14ac:dyDescent="0.25">
+      <c r="I31" s="103"/>
+      <c r="J31" s="103"/>
       <c r="L31" s="1"/>
     </row>
     <row r="32" spans="2:21" x14ac:dyDescent="0.25">
       <c r="L32" s="1"/>
     </row>
     <row r="33" spans="5:12" x14ac:dyDescent="0.25">
-      <c r="E33" s="7"/>
       <c r="L33" s="1"/>
+    </row>
+    <row r="34" spans="5:12" x14ac:dyDescent="0.25">
+      <c r="E34" s="7"/>
+      <c r="L34" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8486,8 +8602,8 @@
         <v>78</v>
       </c>
       <c r="E10" s="76">
-        <f>DemTechs_IND!K22</f>
-        <v>3.8737770381000005</v>
+        <f>DemTechs_IND!K23+DemTechs_IND!K22</f>
+        <v>13.3637537637</v>
       </c>
       <c r="G10" s="1" t="s">
         <v>118</v>
@@ -8515,7 +8631,7 @@
         <v>78</v>
       </c>
       <c r="E11" s="76">
-        <f>DemTechs_IND!K23</f>
+        <f>DemTechs_IND!K24</f>
         <v>3.0990216304800007</v>
       </c>
       <c r="G11" s="1" t="s">
@@ -8545,7 +8661,7 @@
         <v>78</v>
       </c>
       <c r="E12" s="76">
-        <f>DemTechs_IND!K24</f>
+        <f>DemTechs_IND!K25</f>
         <v>3.8737770381000005</v>
       </c>
       <c r="G12" s="28" t="s">
@@ -8574,7 +8690,7 @@
         <v>78</v>
       </c>
       <c r="E13" s="76">
-        <f>DemTechs_IND!K25</f>
+        <f>DemTechs_IND!K26</f>
         <v>4.648532445719999</v>
       </c>
       <c r="G13" s="1" t="s">

--- a/VT_REG1_IND_V12_New.xlsx
+++ b/VT_REG1_IND_V12_New.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261016\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CCFDF28-F405-4E6B-B8EC-1005B2C62C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EF516F-C38E-4C69-8E4C-7D45234A4A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -1539,7 +1539,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="419" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="184">
   <si>
     <t>CommName</t>
   </si>
@@ -1649,9 +1649,6 @@
     <t>Demand</t>
   </si>
   <si>
-    <t>Demand Value</t>
-  </si>
-  <si>
     <t>*Commodity Set Membership</t>
   </si>
   <si>
@@ -1950,12 +1947,6 @@
   </si>
   <si>
     <t>~COMEMI</t>
-  </si>
-  <si>
-    <t>*Unit</t>
-  </si>
-  <si>
-    <t>Demand Unit</t>
   </si>
   <si>
     <t>Input Share</t>
@@ -2694,7 +2685,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2843,16 +2834,10 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="2"/>
@@ -2959,6 +2944,7 @@
     <xf numFmtId="166" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="28">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -4802,246 +4788,246 @@
   <sheetData>
     <row r="1" spans="2:45" x14ac:dyDescent="0.25">
       <c r="X1" s="21" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y1" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="Y1" s="1" t="s">
+      <c r="Z1" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="Z1" s="1" t="s">
-        <v>96</v>
-      </c>
       <c r="AA1" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" spans="2:45" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D2" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="E2" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="F2" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="G2" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="I2" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="J2" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="K2" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="L2" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="M2" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="N2" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="G2" s="39" t="s">
+      <c r="O2" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="P2" s="39" t="s">
+        <v>149</v>
+      </c>
+      <c r="Q2" s="39" t="s">
+        <v>150</v>
+      </c>
+      <c r="R2" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="S2" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="T2" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="U2" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="V2" s="39" t="s">
+        <v>145</v>
+      </c>
+      <c r="Y2" s="38" t="s">
+        <v>157</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="AA2" s="10" t="s">
+        <v>103</v>
+      </c>
+      <c r="AE2" s="39" t="s">
+        <v>43</v>
+      </c>
+      <c r="AF2" s="39" t="s">
+        <v>44</v>
+      </c>
+      <c r="AG2" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="AH2" s="39" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI2" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="H2" s="39" t="s">
+      <c r="AJ2" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="I2" s="39" t="s">
+      <c r="AK2" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="J2" s="39" t="s">
+      <c r="AL2" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="K2" s="39" t="s">
+      <c r="AM2" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="AN2" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="M2" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="N2" s="39" t="s">
+      <c r="AO2" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="AP2" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="O2" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="P2" s="39" t="s">
-        <v>152</v>
-      </c>
-      <c r="Q2" s="39" t="s">
-        <v>153</v>
-      </c>
-      <c r="R2" s="39" t="s">
-        <v>154</v>
-      </c>
-      <c r="S2" s="39" t="s">
+      <c r="AQ2" s="39" t="s">
+        <v>48</v>
+      </c>
+      <c r="AR2" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="T2" s="39" t="s">
+      <c r="AS2" s="39" t="s">
         <v>50</v>
-      </c>
-      <c r="U2" s="39" t="s">
-        <v>51</v>
-      </c>
-      <c r="V2" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="Y2" s="38" t="s">
-        <v>160</v>
-      </c>
-      <c r="Z2" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="AA2" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="AE2" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="AF2" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="AG2" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="AH2" s="39" t="s">
-        <v>123</v>
-      </c>
-      <c r="AI2" s="39" t="s">
-        <v>124</v>
-      </c>
-      <c r="AJ2" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK2" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="AL2" s="39" t="s">
-        <v>127</v>
-      </c>
-      <c r="AM2" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="AN2" s="39" t="s">
-        <v>129</v>
-      </c>
-      <c r="AO2" s="39" t="s">
-        <v>47</v>
-      </c>
-      <c r="AP2" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="AQ2" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="AR2" s="39" t="s">
-        <v>50</v>
-      </c>
-      <c r="AS2" s="39" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="3" spans="2:45" ht="39.6" x14ac:dyDescent="0.25">
       <c r="C3" s="71" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D3" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="E3" s="40" t="s">
+      <c r="F3" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="G3" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="H3" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="I3" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="J3" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="K3" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="L3" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="M3" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="N3" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="F3" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="G3" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="H3" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="I3" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="J3" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="K3" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="L3" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="M3" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="N3" s="40" t="s">
-        <v>54</v>
-      </c>
       <c r="O3" s="40" t="s">
+        <v>152</v>
+      </c>
+      <c r="P3" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q3" s="40" t="s">
+        <v>154</v>
+      </c>
+      <c r="R3" s="40" t="s">
         <v>155</v>
       </c>
-      <c r="P3" s="40" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q3" s="40" t="s">
-        <v>157</v>
-      </c>
-      <c r="R3" s="40" t="s">
-        <v>158</v>
-      </c>
       <c r="S3" s="40" t="s">
+        <v>55</v>
+      </c>
+      <c r="T3" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="T3" s="40" t="s">
+      <c r="U3" s="40" t="s">
+        <v>88</v>
+      </c>
+      <c r="V3" s="40" t="s">
         <v>57</v>
       </c>
-      <c r="U3" s="40" t="s">
-        <v>89</v>
-      </c>
-      <c r="V3" s="40" t="s">
-        <v>58</v>
-      </c>
       <c r="AC3" s="21" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="AD3" s="5"/>
       <c r="AE3" s="40" t="s">
+        <v>51</v>
+      </c>
+      <c r="AF3" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="AF3" s="40" t="s">
+      <c r="AG3" s="40" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH3" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="AI3" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="AJ3" s="40" t="s">
+        <v>124</v>
+      </c>
+      <c r="AK3" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="AL3" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="AM3" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="AN3" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="AO3" s="40" t="s">
         <v>53</v>
       </c>
-      <c r="AG3" s="40" t="s">
-        <v>122</v>
-      </c>
-      <c r="AH3" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="AI3" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="AJ3" s="40" t="s">
-        <v>125</v>
-      </c>
-      <c r="AK3" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="AL3" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="AM3" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="AN3" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="AO3" s="40" t="s">
+      <c r="AP3" s="40" t="s">
         <v>54</v>
       </c>
-      <c r="AP3" s="40" t="s">
+      <c r="AQ3" s="40" t="s">
         <v>55</v>
       </c>
-      <c r="AQ3" s="40" t="s">
+      <c r="AR3" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="AR3" s="40" t="s">
-        <v>57</v>
-      </c>
       <c r="AS3" s="40" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="4" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B4" s="37"/>
-      <c r="C4" s="87" t="s">
-        <v>59</v>
+      <c r="C4" s="85" t="s">
+        <v>58</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
@@ -5061,10 +5047,10 @@
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
-      <c r="V4" s="88"/>
+      <c r="V4" s="86"/>
       <c r="AC4" s="37"/>
       <c r="AD4" s="6" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="AO4" s="27">
         <v>0</v>
@@ -5072,92 +5058,92 @@
     </row>
     <row r="5" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B5" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="C5" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="C5" s="48" t="s">
-        <v>61</v>
-      </c>
-      <c r="D5" s="89">
+      <c r="D5" s="87">
         <f>[2]EB1!D16</f>
         <v>0</v>
       </c>
-      <c r="E5" s="89">
+      <c r="E5" s="87">
         <f>[2]EB1!E16</f>
         <v>0</v>
       </c>
-      <c r="F5" s="89">
+      <c r="F5" s="87">
         <f>[2]EB1!F16</f>
         <v>0</v>
       </c>
-      <c r="G5" s="89">
+      <c r="G5" s="87">
         <f>[2]EB1!G16</f>
         <v>0</v>
       </c>
-      <c r="H5" s="89">
+      <c r="H5" s="87">
         <f>[2]EB1!H16</f>
         <v>0</v>
       </c>
-      <c r="I5" s="89">
+      <c r="I5" s="87">
         <f>[2]EB1!I16</f>
         <v>8.7784635600000005</v>
       </c>
-      <c r="J5" s="89">
+      <c r="J5" s="87">
         <f>[2]EB1!J16</f>
         <v>0</v>
       </c>
-      <c r="K5" s="89">
+      <c r="K5" s="87">
         <f>[2]EB1!K16</f>
         <v>0</v>
       </c>
-      <c r="L5" s="89">
+      <c r="L5" s="87">
         <f>[2]EB1!L16</f>
         <v>0</v>
       </c>
-      <c r="M5" s="89">
+      <c r="M5" s="87">
         <f>[2]EB1!M16</f>
         <v>0</v>
       </c>
-      <c r="N5" s="90">
+      <c r="N5" s="88">
         <f>[2]EB1!N16</f>
         <v>0</v>
       </c>
-      <c r="O5" s="89">
+      <c r="O5" s="87">
         <f>[2]EB1!O16</f>
         <v>29.606118840000001</v>
       </c>
-      <c r="P5" s="89">
+      <c r="P5" s="87">
         <f>[2]EB1!P16</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="89">
+      <c r="Q5" s="87">
         <f>[2]EB1!Q16</f>
         <v>0</v>
       </c>
-      <c r="R5" s="89">
+      <c r="R5" s="87">
         <f>[2]EB1!R16</f>
         <v>0</v>
       </c>
-      <c r="S5" s="89">
+      <c r="S5" s="87">
         <f>[2]EB1!S16</f>
         <v>0</v>
       </c>
-      <c r="T5" s="89">
+      <c r="T5" s="87">
         <f>[2]EB1!T16</f>
         <v>0</v>
       </c>
-      <c r="U5" s="89">
+      <c r="U5" s="87">
         <f>[2]EB1!U16</f>
         <v>15.231997080000001</v>
       </c>
-      <c r="V5" s="91">
+      <c r="V5" s="89">
         <f>SUM(D5:U5)</f>
         <v>53.616579479999999</v>
       </c>
       <c r="AC5" s="41" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD5" s="51" t="s">
         <v>60</v>
-      </c>
-      <c r="AD5" s="51" t="s">
-        <v>61</v>
       </c>
       <c r="AE5" s="63">
         <v>1</v>
@@ -5207,92 +5193,92 @@
     </row>
     <row r="6" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B6" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="C6" s="49" t="s">
         <v>62</v>
       </c>
-      <c r="C6" s="49" t="s">
-        <v>63</v>
-      </c>
-      <c r="D6" s="89">
+      <c r="D6" s="87">
         <f>[2]EB1!D17</f>
         <v>0</v>
       </c>
-      <c r="E6" s="89">
+      <c r="E6" s="87">
         <f>[2]EB1!E17</f>
         <v>0</v>
       </c>
-      <c r="F6" s="89">
+      <c r="F6" s="87">
         <f>[2]EB1!F17</f>
         <v>0</v>
       </c>
-      <c r="G6" s="89">
+      <c r="G6" s="87">
         <f>[2]EB1!G17</f>
         <v>0</v>
       </c>
-      <c r="H6" s="89">
+      <c r="H6" s="87">
         <f>[2]EB1!H17</f>
         <v>0</v>
       </c>
-      <c r="I6" s="89">
+      <c r="I6" s="87">
         <f>[2]EB1!I17</f>
         <v>5.3591040000000003</v>
       </c>
-      <c r="J6" s="89">
+      <c r="J6" s="87">
         <f>[2]EB1!J17</f>
         <v>0</v>
       </c>
-      <c r="K6" s="89">
+      <c r="K6" s="87">
         <f>[2]EB1!K17</f>
         <v>0</v>
       </c>
-      <c r="L6" s="89">
+      <c r="L6" s="87">
         <f>[2]EB1!L17</f>
         <v>0</v>
       </c>
-      <c r="M6" s="89">
+      <c r="M6" s="87">
         <f>[2]EB1!M17</f>
         <v>2.0264112000000001E-2</v>
       </c>
-      <c r="N6" s="90">
+      <c r="N6" s="88">
         <f>[2]EB1!N17</f>
         <v>0</v>
       </c>
-      <c r="O6" s="89">
+      <c r="O6" s="87">
         <f>[2]EB1!O17</f>
         <v>0</v>
       </c>
-      <c r="P6" s="89">
+      <c r="P6" s="87">
         <f>[2]EB1!P17</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="89">
+      <c r="Q6" s="87">
         <f>[2]EB1!Q17</f>
         <v>0</v>
       </c>
-      <c r="R6" s="89">
+      <c r="R6" s="87">
         <f>[2]EB1!R17</f>
         <v>0</v>
       </c>
-      <c r="S6" s="89">
+      <c r="S6" s="87">
         <f>[2]EB1!S17</f>
         <v>0</v>
       </c>
-      <c r="T6" s="89">
+      <c r="T6" s="87">
         <f>[2]EB1!T17</f>
         <v>0</v>
       </c>
-      <c r="U6" s="89">
+      <c r="U6" s="87">
         <f>[2]EB1!U17</f>
         <v>11.973410640000001</v>
       </c>
-      <c r="V6" s="91">
+      <c r="V6" s="89">
         <f t="shared" ref="V6:V12" si="0">SUM(D6:U6)</f>
         <v>17.352778751999999</v>
       </c>
       <c r="AC6" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD6" s="52" t="s">
         <v>62</v>
-      </c>
-      <c r="AD6" s="52" t="s">
-        <v>63</v>
       </c>
       <c r="AE6" s="66">
         <v>1</v>
@@ -5342,93 +5328,93 @@
     </row>
     <row r="7" spans="2:45" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B7" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" s="49" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="49" t="s">
-        <v>65</v>
-      </c>
-      <c r="D7" s="123">
+      <c r="D7" s="121">
         <f>[2]EB1!D18</f>
         <v>20.32984476</v>
       </c>
-      <c r="E7" s="123">
+      <c r="E7" s="121">
         <f>[2]EB1!E18</f>
         <v>0</v>
       </c>
-      <c r="F7" s="123">
+      <c r="F7" s="121">
         <f>[2]EB1!F18</f>
         <v>0</v>
       </c>
-      <c r="G7" s="123">
+      <c r="G7" s="121">
         <f>[2]EB1!G18</f>
         <v>9.3960165599999996</v>
       </c>
-      <c r="H7" s="123">
+      <c r="H7" s="121">
         <f>[2]EB1!H18</f>
         <v>0</v>
       </c>
-      <c r="I7" s="123">
+      <c r="I7" s="121">
         <f>[2]EB1!I18</f>
         <v>2.8470240000000004E-2</v>
       </c>
-      <c r="J7" s="123">
+      <c r="J7" s="121">
         <f>[2]EB1!J18</f>
         <v>0</v>
       </c>
-      <c r="K7" s="123">
+      <c r="K7" s="121">
         <f>[2]EB1!K18</f>
         <v>0</v>
       </c>
-      <c r="L7" s="123">
+      <c r="L7" s="121">
         <f>[2]EB1!L18</f>
         <v>5.0660280000000002E-2</v>
       </c>
-      <c r="M7" s="123">
+      <c r="M7" s="121">
         <f>[2]EB1!M18</f>
         <v>0</v>
       </c>
-      <c r="N7" s="123">
+      <c r="N7" s="121">
         <f>[2]EB1!N18</f>
         <v>0</v>
       </c>
-      <c r="O7" s="123">
+      <c r="O7" s="121">
         <f>[2]EB1!O18</f>
         <v>60.016103280000003</v>
       </c>
-      <c r="P7" s="123">
+      <c r="P7" s="121">
         <f>[2]EB1!P18</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="123">
+      <c r="Q7" s="121">
         <f>[2]EB1!Q18</f>
         <v>0</v>
       </c>
-      <c r="R7" s="123">
+      <c r="R7" s="121">
         <f>[2]EB1!R18</f>
         <v>0</v>
       </c>
-      <c r="S7" s="124">
+      <c r="S7" s="122">
         <f>[2]EB1!S18</f>
         <v>0</v>
       </c>
-      <c r="T7" s="124">
+      <c r="T7" s="122">
         <f>[2]EB1!T18</f>
         <v>0</v>
       </c>
-      <c r="U7" s="123">
+      <c r="U7" s="121">
         <f>[2]EB1!U18</f>
         <v>15.341691240000001</v>
       </c>
-      <c r="V7" s="91">
+      <c r="V7" s="142">
         <f>SUM(D7:U7)</f>
         <v>105.16278636</v>
       </c>
       <c r="X7" s="7"/>
       <c r="AC7" s="41" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD7" s="52" t="s">
         <v>64</v>
-      </c>
-      <c r="AD7" s="52" t="s">
-        <v>65</v>
       </c>
       <c r="AE7" s="70">
         <v>1</v>
@@ -5472,98 +5458,98 @@
       <c r="AR7" s="67">
         <v>0.5</v>
       </c>
-      <c r="AS7" s="98">
+      <c r="AS7" s="96">
         <v>0.44</v>
       </c>
     </row>
     <row r="8" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B8" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="49" t="s">
         <v>66</v>
       </c>
-      <c r="C8" s="49" t="s">
-        <v>67</v>
-      </c>
-      <c r="D8" s="89">
+      <c r="D8" s="87">
         <f>[2]EB1!D19</f>
         <v>0</v>
       </c>
-      <c r="E8" s="89">
+      <c r="E8" s="87">
         <f>[2]EB1!E19</f>
         <v>0</v>
       </c>
-      <c r="F8" s="89">
+      <c r="F8" s="87">
         <f>[2]EB1!F19</f>
         <v>0</v>
       </c>
-      <c r="G8" s="89">
+      <c r="G8" s="87">
         <f>[2]EB1!G19</f>
         <v>8.9932464000000003</v>
       </c>
-      <c r="H8" s="89">
+      <c r="H8" s="87">
         <f>[2]EB1!H19</f>
         <v>0</v>
       </c>
-      <c r="I8" s="89">
+      <c r="I8" s="87">
         <f>[2]EB1!I19</f>
         <v>0</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="87">
         <f>[2]EB1!J19</f>
         <v>0</v>
       </c>
-      <c r="K8" s="89">
+      <c r="K8" s="87">
         <f>[2]EB1!K19</f>
         <v>0</v>
       </c>
-      <c r="L8" s="89">
+      <c r="L8" s="87">
         <f>[2]EB1!L19</f>
         <v>0</v>
       </c>
-      <c r="M8" s="89">
+      <c r="M8" s="87">
         <f>[2]EB1!M19</f>
         <v>0</v>
       </c>
-      <c r="N8" s="90">
+      <c r="N8" s="88">
         <f>[2]EB1!N19</f>
         <v>0</v>
       </c>
-      <c r="O8" s="89">
+      <c r="O8" s="87">
         <f>[2]EB1!O19</f>
         <v>0</v>
       </c>
-      <c r="P8" s="89">
+      <c r="P8" s="87">
         <f>[2]EB1!P19</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="89">
+      <c r="Q8" s="87">
         <f>[2]EB1!Q19</f>
         <v>0</v>
       </c>
-      <c r="R8" s="89">
+      <c r="R8" s="87">
         <f>[2]EB1!R19</f>
         <v>0</v>
       </c>
-      <c r="S8" s="89">
+      <c r="S8" s="87">
         <f>[2]EB1!S19</f>
         <v>4.1868000000000006E-5</v>
       </c>
-      <c r="T8" s="89">
+      <c r="T8" s="87">
         <f>[2]EB1!T19</f>
         <v>0</v>
       </c>
-      <c r="U8" s="89">
+      <c r="U8" s="87">
         <f>[2]EB1!U19</f>
         <v>0</v>
       </c>
-      <c r="V8" s="91">
+      <c r="V8" s="89">
         <f t="shared" si="0"/>
         <v>8.9932882680000006</v>
       </c>
       <c r="AC8" s="41" t="s">
+        <v>65</v>
+      </c>
+      <c r="AD8" s="52" t="s">
         <v>66</v>
-      </c>
-      <c r="AD8" s="52" t="s">
-        <v>67</v>
       </c>
       <c r="AE8" s="66">
         <v>1</v>
@@ -5613,92 +5599,92 @@
     </row>
     <row r="9" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B9" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="49" t="s">
         <v>68</v>
       </c>
-      <c r="C9" s="49" t="s">
-        <v>69</v>
-      </c>
-      <c r="D9" s="89">
+      <c r="D9" s="87">
         <f>[2]EB1!D20</f>
         <v>0</v>
       </c>
-      <c r="E9" s="89">
+      <c r="E9" s="87">
         <f>[2]EB1!E20</f>
         <v>0</v>
       </c>
-      <c r="F9" s="89">
+      <c r="F9" s="87">
         <f>[2]EB1!F20</f>
         <v>0</v>
       </c>
-      <c r="G9" s="89">
+      <c r="G9" s="87">
         <f>[2]EB1!G20</f>
         <v>59.234009040000004</v>
       </c>
-      <c r="H9" s="89">
+      <c r="H9" s="87">
         <f>[2]EB1!H20</f>
         <v>2.9927246400000005</v>
       </c>
-      <c r="I9" s="89">
+      <c r="I9" s="87">
         <f>[2]EB1!I20</f>
         <v>1.2346873199999999</v>
       </c>
-      <c r="J9" s="89">
+      <c r="J9" s="87">
         <f>[2]EB1!J20</f>
         <v>28.510014600000005</v>
       </c>
-      <c r="K9" s="89">
+      <c r="K9" s="87">
         <f>[2]EB1!K20</f>
         <v>0</v>
       </c>
-      <c r="L9" s="89">
+      <c r="L9" s="87">
         <f>[2]EB1!L20</f>
         <v>1.2556213199999999</v>
       </c>
-      <c r="M9" s="89">
+      <c r="M9" s="87">
         <f>[2]EB1!M20</f>
         <v>8.1692841600000001</v>
       </c>
-      <c r="N9" s="90">
+      <c r="N9" s="88">
         <f>[2]EB1!N20</f>
         <v>0</v>
       </c>
-      <c r="O9" s="89">
+      <c r="O9" s="87">
         <f>[2]EB1!O20</f>
         <v>0</v>
       </c>
-      <c r="P9" s="89">
+      <c r="P9" s="87">
         <f>[2]EB1!P20</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="89">
+      <c r="Q9" s="87">
         <f>[2]EB1!Q20</f>
         <v>0</v>
       </c>
-      <c r="R9" s="89">
+      <c r="R9" s="87">
         <f>[2]EB1!R20</f>
         <v>0</v>
       </c>
-      <c r="S9" s="89">
+      <c r="S9" s="87">
         <f>[2]EB1!S20</f>
         <v>0</v>
       </c>
-      <c r="T9" s="89">
+      <c r="T9" s="87">
         <f>[2]EB1!T20</f>
         <v>0</v>
       </c>
-      <c r="U9" s="89">
+      <c r="U9" s="87">
         <f>[2]EB1!U20</f>
         <v>0</v>
       </c>
-      <c r="V9" s="91">
+      <c r="V9" s="89">
         <f t="shared" si="0"/>
         <v>101.39634108000001</v>
       </c>
       <c r="AC9" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="AD9" s="52" t="s">
         <v>68</v>
-      </c>
-      <c r="AD9" s="52" t="s">
-        <v>69</v>
       </c>
       <c r="AE9" s="66">
         <v>1</v>
@@ -5748,10 +5734,10 @@
     </row>
     <row r="10" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B10" s="41" t="s">
+        <v>69</v>
+      </c>
+      <c r="C10" s="50" t="s">
         <v>70</v>
-      </c>
-      <c r="C10" s="50" t="s">
-        <v>71</v>
       </c>
       <c r="D10" s="43">
         <f>[2]EB1!D21</f>
@@ -5825,15 +5811,15 @@
         <f>[2]EB1!U21</f>
         <v>0</v>
       </c>
-      <c r="V10" s="92">
+      <c r="V10" s="90">
         <f t="shared" si="0"/>
         <v>9.4588185599999992</v>
       </c>
       <c r="AC10" s="41" t="s">
+        <v>69</v>
+      </c>
+      <c r="AD10" s="53" t="s">
         <v>70</v>
-      </c>
-      <c r="AD10" s="53" t="s">
-        <v>71</v>
       </c>
       <c r="AE10" s="61">
         <v>1</v>
@@ -5883,92 +5869,92 @@
     </row>
     <row r="11" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B11" s="41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="D11" s="89">
+        <v>71</v>
+      </c>
+      <c r="D11" s="87">
         <f>[2]EB1!D22</f>
         <v>0</v>
       </c>
-      <c r="E11" s="89">
+      <c r="E11" s="87">
         <f>[2]EB1!E22</f>
         <v>0</v>
       </c>
-      <c r="F11" s="89">
+      <c r="F11" s="87">
         <f>[2]EB1!F22</f>
         <v>0</v>
       </c>
-      <c r="G11" s="89">
+      <c r="G11" s="87">
         <f>[2]EB1!G22</f>
         <v>0</v>
       </c>
-      <c r="H11" s="89">
+      <c r="H11" s="87">
         <f>[2]EB1!H22</f>
         <v>0</v>
       </c>
-      <c r="I11" s="89">
+      <c r="I11" s="87">
         <f>[2]EB1!I22</f>
         <v>0</v>
       </c>
-      <c r="J11" s="89">
+      <c r="J11" s="87">
         <f>[2]EB1!J22</f>
         <v>0</v>
       </c>
-      <c r="K11" s="89">
+      <c r="K11" s="87">
         <f>[2]EB1!K22</f>
         <v>0</v>
       </c>
-      <c r="L11" s="89">
+      <c r="L11" s="87">
         <f>[2]EB1!L22</f>
         <v>0</v>
       </c>
-      <c r="M11" s="89">
+      <c r="M11" s="87">
         <f>[2]EB1!M22</f>
         <v>0</v>
       </c>
-      <c r="N11" s="90">
+      <c r="N11" s="88">
         <f>[2]EB1!N22</f>
         <v>0</v>
       </c>
-      <c r="O11" s="89">
+      <c r="O11" s="87">
         <f>[2]EB1!O22</f>
         <v>0</v>
       </c>
-      <c r="P11" s="89">
+      <c r="P11" s="87">
         <f>[2]EB1!P22</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="89">
+      <c r="Q11" s="87">
         <f>[2]EB1!Q22</f>
         <v>0</v>
       </c>
-      <c r="R11" s="89">
+      <c r="R11" s="87">
         <f>[2]EB1!R22</f>
         <v>0</v>
       </c>
-      <c r="S11" s="89">
+      <c r="S11" s="87">
         <f>[2]EB1!S22</f>
         <v>0</v>
       </c>
-      <c r="T11" s="89">
+      <c r="T11" s="87">
         <f>[2]EB1!T22</f>
         <v>0</v>
       </c>
-      <c r="U11" s="89">
+      <c r="U11" s="87">
         <f>[2]EB1!U22</f>
         <v>0</v>
       </c>
-      <c r="V11" s="91">
+      <c r="V11" s="89">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC11" s="41" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="AD11" s="52" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="AE11" s="66">
         <v>1</v>
@@ -6018,52 +6004,52 @@
     </row>
     <row r="12" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B12" s="41" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>73</v>
-      </c>
-      <c r="D12" s="89">
+        <v>72</v>
+      </c>
+      <c r="D12" s="87">
         <f>[2]EB1!D23</f>
         <v>0</v>
       </c>
-      <c r="E12" s="89">
+      <c r="E12" s="87">
         <f>[2]EB1!E23</f>
         <v>0</v>
       </c>
-      <c r="F12" s="89">
+      <c r="F12" s="87">
         <f>[2]EB1!F23</f>
         <v>0</v>
       </c>
-      <c r="G12" s="89">
+      <c r="G12" s="87">
         <f>[2]EB1!G23</f>
         <v>0</v>
       </c>
-      <c r="H12" s="89">
+      <c r="H12" s="87">
         <f>[2]EB1!H23</f>
         <v>0</v>
       </c>
-      <c r="I12" s="89">
+      <c r="I12" s="87">
         <f>[2]EB1!I23</f>
         <v>0</v>
       </c>
-      <c r="J12" s="89">
+      <c r="J12" s="87">
         <f>[2]EB1!J23</f>
         <v>0</v>
       </c>
-      <c r="K12" s="89">
+      <c r="K12" s="87">
         <f>[2]EB1!K23</f>
         <v>0</v>
       </c>
-      <c r="L12" s="89">
+      <c r="L12" s="87">
         <f>[2]EB1!L23</f>
         <v>0</v>
       </c>
-      <c r="M12" s="89">
+      <c r="M12" s="87">
         <f>[2]EB1!M23</f>
         <v>0</v>
       </c>
-      <c r="N12" s="90">
+      <c r="N12" s="88">
         <f>[2]EB1!N23</f>
         <v>0</v>
       </c>
@@ -6083,27 +6069,27 @@
         <f>[2]EB1!R23</f>
         <v>0</v>
       </c>
-      <c r="S12" s="89">
+      <c r="S12" s="87">
         <f>[2]EB1!S23</f>
         <v>0</v>
       </c>
-      <c r="T12" s="89">
+      <c r="T12" s="87">
         <f>[2]EB1!T23</f>
         <v>0</v>
       </c>
-      <c r="U12" s="89">
+      <c r="U12" s="87">
         <f>[2]EB1!U23</f>
         <v>0</v>
       </c>
-      <c r="V12" s="91">
+      <c r="V12" s="89">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC12" s="41" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="AD12" s="52" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AE12" s="66">
         <v>1</v>
@@ -6152,11 +6138,11 @@
       </c>
     </row>
     <row r="13" spans="2:45" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B13" s="86" t="s">
-        <v>90</v>
+      <c r="B13" s="84" t="s">
+        <v>89</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D13" s="45">
         <f t="shared" ref="D13:V13" si="1">SUM(D5:D12)</f>
@@ -6223,7 +6209,7 @@
         <v>295.9805925</v>
       </c>
       <c r="AC13" s="41" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="AD13" s="58"/>
       <c r="AE13" s="58"/>
@@ -6266,7 +6252,7 @@
     </row>
     <row r="16" spans="2:45" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C16" s="44" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="D16" s="44"/>
       <c r="E16" s="44"/>
@@ -6296,273 +6282,271 @@
     </row>
     <row r="19" spans="2:24" ht="39.6" x14ac:dyDescent="0.25">
       <c r="B19" s="23" t="s">
-        <v>102</v>
-      </c>
-      <c r="C19" s="126" t="s">
-        <v>115</v>
-      </c>
-      <c r="D19" s="127" t="s">
+        <v>101</v>
+      </c>
+      <c r="C19" s="124" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="125" t="s">
+        <v>51</v>
+      </c>
+      <c r="E19" s="126" t="s">
         <v>52</v>
       </c>
-      <c r="E19" s="128" t="s">
+      <c r="F19" s="126" t="s">
+        <v>121</v>
+      </c>
+      <c r="G19" s="126" t="s">
+        <v>134</v>
+      </c>
+      <c r="H19" s="126" t="s">
+        <v>131</v>
+      </c>
+      <c r="I19" s="126" t="s">
+        <v>124</v>
+      </c>
+      <c r="J19" s="126" t="s">
+        <v>132</v>
+      </c>
+      <c r="K19" s="126" t="s">
+        <v>133</v>
+      </c>
+      <c r="L19" s="126" t="s">
+        <v>129</v>
+      </c>
+      <c r="M19" s="126" t="s">
+        <v>130</v>
+      </c>
+      <c r="N19" s="126" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="128" t="s">
-        <v>122</v>
-      </c>
-      <c r="G19" s="128" t="s">
-        <v>135</v>
-      </c>
-      <c r="H19" s="128" t="s">
-        <v>132</v>
-      </c>
-      <c r="I19" s="128" t="s">
-        <v>125</v>
-      </c>
-      <c r="J19" s="128" t="s">
-        <v>133</v>
-      </c>
-      <c r="K19" s="128" t="s">
-        <v>134</v>
-      </c>
-      <c r="L19" s="128" t="s">
-        <v>130</v>
-      </c>
-      <c r="M19" s="128" t="s">
-        <v>131</v>
-      </c>
-      <c r="N19" s="128" t="s">
-        <v>54</v>
-      </c>
-      <c r="O19" s="128" t="s">
+      <c r="O19" s="126" t="s">
+        <v>152</v>
+      </c>
+      <c r="P19" s="126" t="s">
+        <v>153</v>
+      </c>
+      <c r="Q19" s="126" t="s">
+        <v>154</v>
+      </c>
+      <c r="R19" s="126" t="s">
         <v>155</v>
       </c>
-      <c r="P19" s="128" t="s">
-        <v>156</v>
-      </c>
-      <c r="Q19" s="128" t="s">
-        <v>157</v>
-      </c>
-      <c r="R19" s="128" t="s">
-        <v>158</v>
-      </c>
-      <c r="S19" s="128" t="s">
+      <c r="S19" s="126" t="s">
+        <v>55</v>
+      </c>
+      <c r="T19" s="126" t="s">
         <v>56</v>
       </c>
-      <c r="T19" s="128" t="s">
+      <c r="U19" s="126" t="s">
+        <v>88</v>
+      </c>
+      <c r="V19" s="127" t="s">
         <v>57</v>
       </c>
-      <c r="U19" s="128" t="s">
-        <v>89</v>
-      </c>
-      <c r="V19" s="129" t="s">
-        <v>58</v>
-      </c>
     </row>
     <row r="20" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B20" s="97" t="s">
-        <v>64</v>
-      </c>
-      <c r="C20" s="94" t="s">
+      <c r="B20" s="95" t="s">
+        <v>63</v>
+      </c>
+      <c r="C20" s="92" t="s">
+        <v>162</v>
+      </c>
+      <c r="D20" s="116">
+        <v>1</v>
+      </c>
+      <c r="E20" s="123"/>
+      <c r="F20" s="123"/>
+      <c r="G20" s="123"/>
+      <c r="H20" s="123"/>
+      <c r="I20" s="123"/>
+      <c r="J20" s="123"/>
+      <c r="K20" s="123"/>
+      <c r="L20" s="115">
+        <v>1</v>
+      </c>
+      <c r="M20" s="123"/>
+      <c r="N20" s="123"/>
+      <c r="O20" s="115">
+        <v>1</v>
+      </c>
+      <c r="P20" s="123"/>
+      <c r="Q20" s="123"/>
+      <c r="R20" s="123"/>
+      <c r="S20" s="123"/>
+      <c r="T20" s="123"/>
+      <c r="U20" s="123"/>
+      <c r="V20" s="49"/>
+      <c r="X20" s="114" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="21" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B21" s="95" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="92" t="s">
+        <v>179</v>
+      </c>
+      <c r="D21" s="52"/>
+      <c r="E21" s="123"/>
+      <c r="F21" s="123"/>
+      <c r="G21" s="115">
+        <v>1</v>
+      </c>
+      <c r="H21" s="123"/>
+      <c r="I21" s="115">
+        <v>1</v>
+      </c>
+      <c r="J21" s="123"/>
+      <c r="K21" s="123"/>
+      <c r="L21" s="123"/>
+      <c r="M21" s="123"/>
+      <c r="N21" s="123"/>
+      <c r="O21" s="123"/>
+      <c r="P21" s="123"/>
+      <c r="Q21" s="123"/>
+      <c r="R21" s="123"/>
+      <c r="S21" s="123"/>
+      <c r="T21" s="123"/>
+      <c r="U21" s="115">
+        <v>0.25</v>
+      </c>
+      <c r="V21" s="49"/>
+      <c r="X21" s="114" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="22" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B22" s="95" t="s">
+        <v>63</v>
+      </c>
+      <c r="C22" s="92" t="s">
+        <v>163</v>
+      </c>
+      <c r="D22" s="52"/>
+      <c r="E22" s="123"/>
+      <c r="F22" s="123"/>
+      <c r="G22" s="123"/>
+      <c r="H22" s="123"/>
+      <c r="I22" s="123"/>
+      <c r="J22" s="123"/>
+      <c r="K22" s="123"/>
+      <c r="L22" s="123"/>
+      <c r="M22" s="123"/>
+      <c r="N22" s="123"/>
+      <c r="O22" s="123"/>
+      <c r="P22" s="123"/>
+      <c r="Q22" s="123"/>
+      <c r="R22" s="123"/>
+      <c r="S22" s="123"/>
+      <c r="T22" s="123"/>
+      <c r="U22" s="115">
+        <v>0.2</v>
+      </c>
+      <c r="V22" s="49"/>
+      <c r="X22" s="114" t="s">
         <v>165</v>
       </c>
-      <c r="D20" s="118">
-        <v>1</v>
-      </c>
-      <c r="E20" s="125"/>
-      <c r="F20" s="125"/>
-      <c r="G20" s="117">
-        <v>0</v>
-      </c>
-      <c r="H20" s="125"/>
-      <c r="I20" s="125"/>
-      <c r="J20" s="125"/>
-      <c r="K20" s="125"/>
-      <c r="L20" s="117">
-        <v>1</v>
-      </c>
-      <c r="M20" s="125"/>
-      <c r="N20" s="125"/>
-      <c r="O20" s="117">
-        <v>1</v>
-      </c>
-      <c r="P20" s="125"/>
-      <c r="Q20" s="125"/>
-      <c r="R20" s="125"/>
-      <c r="S20" s="125"/>
-      <c r="T20" s="125"/>
-      <c r="U20" s="125"/>
-      <c r="V20" s="49"/>
-      <c r="X20" s="116" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="21" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B21" s="97" t="s">
-        <v>64</v>
-      </c>
-      <c r="C21" s="94" t="s">
-        <v>182</v>
-      </c>
-      <c r="D21" s="52"/>
-      <c r="E21" s="125"/>
-      <c r="F21" s="125"/>
-      <c r="G21" s="117">
-        <v>1</v>
-      </c>
-      <c r="H21" s="125"/>
-      <c r="I21" s="117">
-        <v>1</v>
-      </c>
-      <c r="J21" s="125"/>
-      <c r="K21" s="125"/>
-      <c r="L21" s="125"/>
-      <c r="M21" s="125"/>
-      <c r="N21" s="125"/>
-      <c r="O21" s="125"/>
-      <c r="P21" s="125"/>
-      <c r="Q21" s="125"/>
-      <c r="R21" s="125"/>
-      <c r="S21" s="125"/>
-      <c r="T21" s="125"/>
-      <c r="U21" s="117">
-        <v>0.25</v>
-      </c>
-      <c r="V21" s="49"/>
-      <c r="X21" s="116" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="22" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B22" s="97" t="s">
-        <v>64</v>
-      </c>
-      <c r="C22" s="94" t="s">
+    </row>
+    <row r="23" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
+      <c r="B23" s="95" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="92" t="s">
         <v>166</v>
       </c>
-      <c r="D22" s="52"/>
-      <c r="E22" s="125"/>
-      <c r="F22" s="125"/>
-      <c r="G22" s="125"/>
-      <c r="H22" s="125"/>
-      <c r="I22" s="125"/>
-      <c r="J22" s="125"/>
-      <c r="K22" s="125"/>
-      <c r="L22" s="125"/>
-      <c r="M22" s="125"/>
-      <c r="N22" s="125"/>
-      <c r="O22" s="125"/>
-      <c r="P22" s="125"/>
-      <c r="Q22" s="125"/>
-      <c r="R22" s="125"/>
-      <c r="S22" s="125"/>
-      <c r="T22" s="125"/>
-      <c r="U22" s="117">
-        <v>0.2</v>
-      </c>
-      <c r="V22" s="49"/>
-      <c r="X22" s="116" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="23" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B23" s="97" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="94" t="s">
-        <v>169</v>
-      </c>
       <c r="D23" s="52"/>
-      <c r="E23" s="125"/>
-      <c r="F23" s="125"/>
-      <c r="G23" s="125"/>
-      <c r="H23" s="125"/>
-      <c r="I23" s="125"/>
-      <c r="J23" s="125"/>
-      <c r="K23" s="125"/>
-      <c r="L23" s="125"/>
-      <c r="M23" s="125"/>
-      <c r="N23" s="125"/>
-      <c r="O23" s="125"/>
-      <c r="P23" s="125"/>
-      <c r="Q23" s="125"/>
-      <c r="R23" s="125"/>
-      <c r="S23" s="125"/>
-      <c r="T23" s="125"/>
-      <c r="U23" s="117">
+      <c r="E23" s="123"/>
+      <c r="F23" s="123"/>
+      <c r="G23" s="123"/>
+      <c r="H23" s="123"/>
+      <c r="I23" s="123"/>
+      <c r="J23" s="123"/>
+      <c r="K23" s="123"/>
+      <c r="L23" s="123"/>
+      <c r="M23" s="123"/>
+      <c r="N23" s="123"/>
+      <c r="O23" s="123"/>
+      <c r="P23" s="123"/>
+      <c r="Q23" s="123"/>
+      <c r="R23" s="123"/>
+      <c r="S23" s="123"/>
+      <c r="T23" s="123"/>
+      <c r="U23" s="115">
         <v>0.25</v>
       </c>
       <c r="V23" s="49"/>
       <c r="X23" s="50" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
     </row>
     <row r="24" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B24" s="97" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="94" t="s">
-        <v>171</v>
+      <c r="B24" s="95" t="s">
+        <v>63</v>
+      </c>
+      <c r="C24" s="92" t="s">
+        <v>168</v>
       </c>
       <c r="D24" s="52"/>
-      <c r="E24" s="125"/>
-      <c r="F24" s="125"/>
-      <c r="G24" s="125"/>
-      <c r="H24" s="125"/>
-      <c r="I24" s="125"/>
-      <c r="J24" s="125"/>
-      <c r="K24" s="125"/>
-      <c r="L24" s="125"/>
-      <c r="M24" s="125"/>
-      <c r="N24" s="125"/>
-      <c r="O24" s="125"/>
-      <c r="P24" s="125"/>
-      <c r="Q24" s="125"/>
-      <c r="R24" s="125"/>
-      <c r="S24" s="125"/>
-      <c r="T24" s="125"/>
-      <c r="U24" s="117">
+      <c r="E24" s="123"/>
+      <c r="F24" s="123"/>
+      <c r="G24" s="123"/>
+      <c r="H24" s="123"/>
+      <c r="I24" s="123"/>
+      <c r="J24" s="123"/>
+      <c r="K24" s="123"/>
+      <c r="L24" s="123"/>
+      <c r="M24" s="123"/>
+      <c r="N24" s="123"/>
+      <c r="O24" s="123"/>
+      <c r="P24" s="123"/>
+      <c r="Q24" s="123"/>
+      <c r="R24" s="123"/>
+      <c r="S24" s="123"/>
+      <c r="T24" s="123"/>
+      <c r="U24" s="115">
         <v>0.3</v>
       </c>
       <c r="V24" s="49"/>
-      <c r="X24" s="116" t="s">
-        <v>172</v>
+      <c r="X24" s="114" t="s">
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C27" s="54" t="s">
+        <v>105</v>
+      </c>
+      <c r="D27" s="56" t="s">
         <v>106</v>
       </c>
-      <c r="D27" s="56" t="s">
+      <c r="E27" s="55" t="s">
         <v>107</v>
-      </c>
-      <c r="E27" s="55" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B28" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="C28" s="95" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" s="93" t="s">
+        <v>108</v>
+      </c>
+      <c r="D28" s="93" t="s">
         <v>109</v>
       </c>
-      <c r="D28" s="95" t="s">
-        <v>110</v>
-      </c>
-      <c r="E28" s="96" t="s">
-        <v>108</v>
+      <c r="E28" s="94" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B29" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="C29" s="104">
+        <v>63</v>
+      </c>
+      <c r="C29" s="102">
         <v>1</v>
       </c>
-      <c r="D29" s="105"/>
-      <c r="E29" s="106"/>
+      <c r="D29" s="103"/>
+      <c r="E29" s="104"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6583,26 +6567,26 @@
   <sheetData>
     <row r="2" spans="2:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B2" s="79" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
+      <c r="E4" s="97"/>
+      <c r="F4" s="97"/>
+      <c r="G4" s="97"/>
+      <c r="H4" s="97"/>
+      <c r="I4" s="97"/>
+      <c r="J4" s="97"/>
     </row>
     <row r="5" spans="2:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E5" s="80" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="F5" s="80"/>
       <c r="G5" s="80"/>
       <c r="H5" s="80"/>
-      <c r="I5" s="100"/>
-      <c r="J5" s="100"/>
+      <c r="I5" s="98"/>
+      <c r="J5" s="98"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6638,22 +6622,22 @@
   <sheetData>
     <row r="1" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="E1" s="8" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H1" s="30"/>
     </row>
@@ -6667,7 +6651,7 @@
         <v>Industry</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E2" s="10" t="str">
         <f>'EB1'!Z2</f>
@@ -6678,47 +6662,47 @@
         <v>M$2021</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="H2" s="9"/>
-      <c r="J2" s="107" t="s">
+      <c r="J2" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="107"/>
-      <c r="L2" s="108"/>
-      <c r="M2" s="108"/>
-      <c r="N2" s="108"/>
-      <c r="O2" s="108"/>
-      <c r="P2" s="108"/>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="108"/>
+      <c r="K2" s="105"/>
+      <c r="L2" s="106"/>
+      <c r="M2" s="106"/>
+      <c r="N2" s="106"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="106"/>
+      <c r="Q2" s="106"/>
+      <c r="R2" s="106"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="J3" s="109" t="s">
+      <c r="J3" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="110" t="s">
+      <c r="K3" s="108" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="M3" s="109" t="s">
+      <c r="L3" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="M3" s="107" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="109" t="s">
+      <c r="N3" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="109" t="s">
+      <c r="O3" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="109" t="s">
+      <c r="P3" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="109" t="s">
+      <c r="Q3" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="R3" s="109" t="s">
+      <c r="R3" s="107" t="s">
         <v>12</v>
       </c>
     </row>
@@ -6728,31 +6712,31 @@
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
       <c r="G4" s="9"/>
-      <c r="J4" s="111" t="s">
-        <v>37</v>
-      </c>
-      <c r="K4" s="111" t="s">
+      <c r="J4" s="109" t="s">
+        <v>36</v>
+      </c>
+      <c r="K4" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="111" t="s">
+      <c r="L4" s="109" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="111" t="s">
+      <c r="M4" s="109" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="111" t="s">
+      <c r="N4" s="109" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="111" t="s">
+      <c r="O4" s="109" t="s">
+        <v>39</v>
+      </c>
+      <c r="P4" s="109" t="s">
         <v>40</v>
       </c>
-      <c r="P4" s="111" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q4" s="111" t="s">
+      <c r="Q4" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="R4" s="111" t="s">
+      <c r="R4" s="109" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6761,122 +6745,122 @@
       <c r="F5" s="12"/>
       <c r="G5" s="78"/>
       <c r="H5" s="11"/>
-      <c r="J5" s="112" t="s">
-        <v>74</v>
-      </c>
-      <c r="K5" s="112"/>
-      <c r="L5" s="112" t="str">
+      <c r="J5" s="110" t="s">
+        <v>73</v>
+      </c>
+      <c r="K5" s="110"/>
+      <c r="L5" s="110" t="str">
         <f>$B$2&amp;[3]EB2!$D$2</f>
         <v>INDCOA</v>
       </c>
-      <c r="M5" s="113" t="str">
+      <c r="M5" s="111" t="str">
         <f>$C$2&amp;" "&amp;[3]EB2!$D$3</f>
         <v>Industry Solid Fuels</v>
       </c>
-      <c r="N5" s="112" t="str">
+      <c r="N5" s="110" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O5" s="112"/>
-      <c r="P5" s="112"/>
-      <c r="Q5" s="112"/>
-      <c r="R5" s="112"/>
+      <c r="O5" s="110"/>
+      <c r="P5" s="110"/>
+      <c r="Q5" s="110"/>
+      <c r="R5" s="110"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="78"/>
       <c r="H6" s="11"/>
-      <c r="J6" s="112"/>
-      <c r="K6" s="112"/>
-      <c r="L6" s="112" t="str">
+      <c r="J6" s="110"/>
+      <c r="K6" s="110"/>
+      <c r="L6" s="110" t="str">
         <f>$B$2&amp;[3]EB2!$E$2</f>
         <v>INDGAS</v>
       </c>
-      <c r="M6" s="113" t="str">
+      <c r="M6" s="111" t="str">
         <f>$C$2&amp;" "&amp;[3]EB2!$E$3</f>
         <v>Industry Natural Gas</v>
       </c>
-      <c r="N6" s="112" t="str">
+      <c r="N6" s="110" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O6" s="112"/>
-      <c r="P6" s="112"/>
-      <c r="Q6" s="112"/>
-      <c r="R6" s="112"/>
+      <c r="O6" s="110"/>
+      <c r="P6" s="110"/>
+      <c r="Q6" s="110"/>
+      <c r="R6" s="110"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
       <c r="G7" s="78"/>
       <c r="H7" s="11"/>
-      <c r="J7" s="112"/>
-      <c r="K7" s="112"/>
-      <c r="L7" s="112" t="str">
+      <c r="J7" s="110"/>
+      <c r="K7" s="110"/>
+      <c r="L7" s="110" t="str">
         <f>$B$2&amp;[3]EB2!$F$2</f>
         <v>INDOIL</v>
       </c>
-      <c r="M7" s="113" t="str">
+      <c r="M7" s="111" t="str">
         <f>$C$2&amp;" "&amp;[3]EB2!$F$3</f>
         <v>Industry Crude Oil</v>
       </c>
-      <c r="N7" s="112" t="str">
+      <c r="N7" s="110" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O7" s="112"/>
-      <c r="P7" s="112"/>
-      <c r="Q7" s="112"/>
-      <c r="R7" s="112"/>
+      <c r="O7" s="110"/>
+      <c r="P7" s="110"/>
+      <c r="Q7" s="110"/>
+      <c r="R7" s="110"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="78"/>
       <c r="H8" s="11"/>
-      <c r="J8" s="112"/>
-      <c r="K8" s="112"/>
-      <c r="L8" s="112" t="str">
+      <c r="J8" s="110"/>
+      <c r="K8" s="110"/>
+      <c r="L8" s="110" t="str">
         <f>$B$2&amp;[3]EB2!$O$2</f>
         <v>INDBIO</v>
       </c>
-      <c r="M8" s="113" t="str">
+      <c r="M8" s="111" t="str">
         <f>$C$2&amp;" "&amp;[3]EB2!$O$3</f>
         <v>Industry Biomass</v>
       </c>
-      <c r="N8" s="112" t="str">
+      <c r="N8" s="110" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O8" s="112"/>
-      <c r="P8" s="112"/>
-      <c r="Q8" s="112"/>
-      <c r="R8" s="112"/>
+      <c r="O8" s="110"/>
+      <c r="P8" s="110"/>
+      <c r="Q8" s="110"/>
+      <c r="R8" s="110"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
       <c r="G9" s="78"/>
       <c r="H9" s="11"/>
-      <c r="J9" s="112"/>
-      <c r="K9" s="112"/>
-      <c r="L9" s="112" t="str">
+      <c r="J9" s="110"/>
+      <c r="K9" s="110"/>
+      <c r="L9" s="110" t="str">
         <f>$B$2&amp;[3]EB2!$U$2</f>
         <v>INDELC</v>
       </c>
-      <c r="M9" s="113" t="str">
+      <c r="M9" s="111" t="str">
         <f>$C$2&amp;" "&amp;[3]EB2!$U$3</f>
         <v>Industry Electricity</v>
       </c>
-      <c r="N9" s="112" t="str">
+      <c r="N9" s="110" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O9" s="112"/>
-      <c r="P9" s="112"/>
-      <c r="Q9" s="112"/>
-      <c r="R9" s="112"/>
+      <c r="O9" s="110"/>
+      <c r="P9" s="110"/>
+      <c r="Q9" s="110"/>
+      <c r="R9" s="110"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E10" s="12"/>
@@ -6899,17 +6883,17 @@
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
-      <c r="J12" s="107" t="s">
+      <c r="J12" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="107"/>
-      <c r="L12" s="112"/>
-      <c r="M12" s="112"/>
-      <c r="N12" s="112"/>
-      <c r="O12" s="112"/>
-      <c r="P12" s="112"/>
-      <c r="Q12" s="112"/>
-      <c r="R12" s="112"/>
+      <c r="K12" s="105"/>
+      <c r="L12" s="110"/>
+      <c r="M12" s="110"/>
+      <c r="N12" s="110"/>
+      <c r="O12" s="110"/>
+      <c r="P12" s="110"/>
+      <c r="Q12" s="110"/>
+      <c r="R12" s="110"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18" t="s">
@@ -6921,49 +6905,49 @@
       <c r="D13" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="84" t="s">
-        <v>140</v>
+      <c r="E13" s="83" t="s">
+        <v>137</v>
       </c>
       <c r="F13" s="81" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G13" s="81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H13" s="81" t="s">
-        <v>81</v>
-      </c>
-      <c r="J13" s="109" t="s">
+        <v>80</v>
+      </c>
+      <c r="J13" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="K13" s="110" t="s">
+      <c r="K13" s="108" t="s">
         <v>30</v>
       </c>
-      <c r="L13" s="109" t="s">
+      <c r="L13" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="M13" s="109" t="s">
+      <c r="M13" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="N13" s="109" t="s">
+      <c r="N13" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="O13" s="109" t="s">
+      <c r="O13" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="P13" s="109" t="s">
+      <c r="P13" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="Q13" s="109" t="s">
+      <c r="Q13" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="R13" s="109" t="s">
+      <c r="R13" s="107" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="14" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>32</v>
@@ -6972,48 +6956,48 @@
         <v>33</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>34</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="J14" s="111" t="s">
-        <v>38</v>
-      </c>
-      <c r="K14" s="111" t="s">
+        <v>156</v>
+      </c>
+      <c r="J14" s="109" t="s">
+        <v>37</v>
+      </c>
+      <c r="K14" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="L14" s="111" t="s">
+      <c r="L14" s="109" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="111" t="s">
+      <c r="M14" s="109" t="s">
         <v>22</v>
       </c>
-      <c r="N14" s="111" t="s">
+      <c r="N14" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="O14" s="111" t="s">
+      <c r="O14" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="P14" s="111" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q14" s="111" t="s">
+      <c r="P14" s="109" t="s">
         <v>42</v>
       </c>
-      <c r="R14" s="111" t="s">
+      <c r="Q14" s="109" t="s">
+        <v>41</v>
+      </c>
+      <c r="R14" s="109" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
@@ -7024,19 +7008,19 @@
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="J15" s="111" t="s">
-        <v>83</v>
-      </c>
-      <c r="K15" s="114"/>
-      <c r="L15" s="114"/>
-      <c r="M15" s="114"/>
-      <c r="N15" s="114"/>
-      <c r="O15" s="114"/>
-      <c r="P15" s="114"/>
-      <c r="Q15" s="114"/>
-      <c r="R15" s="114"/>
+        <v>92</v>
+      </c>
+      <c r="J15" s="109" t="s">
+        <v>82</v>
+      </c>
+      <c r="K15" s="112"/>
+      <c r="L15" s="112"/>
+      <c r="M15" s="112"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="112"/>
+      <c r="P15" s="112"/>
+      <c r="Q15" s="112"/>
+      <c r="R15" s="112"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" t="str">
@@ -7059,29 +7043,29 @@
       <c r="H16" s="75">
         <v>50</v>
       </c>
-      <c r="J16" s="108" t="s">
-        <v>112</v>
-      </c>
-      <c r="K16" s="112"/>
-      <c r="L16" s="112" t="str">
+      <c r="J16" s="106" t="s">
+        <v>111</v>
+      </c>
+      <c r="K16" s="110"/>
+      <c r="L16" s="110" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L5</f>
         <v>FTE-INDCOA</v>
       </c>
-      <c r="M16" s="113" t="str">
+      <c r="M16" s="111" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
         <v>Sector Fuel Technology Existing Industry Solid Fuels</v>
       </c>
-      <c r="N16" s="112" t="str">
+      <c r="N16" s="110" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O16" s="112" t="str">
+      <c r="O16" s="110" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="P16" s="112"/>
-      <c r="Q16" s="112"/>
-      <c r="R16" s="112"/>
+      <c r="P16" s="110"/>
+      <c r="Q16" s="110"/>
+      <c r="R16" s="110"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" t="str">
@@ -7104,27 +7088,27 @@
       <c r="H17" s="75">
         <v>50</v>
       </c>
-      <c r="J17" s="112"/>
-      <c r="K17" s="112"/>
-      <c r="L17" s="112" t="str">
+      <c r="J17" s="110"/>
+      <c r="K17" s="110"/>
+      <c r="L17" s="110" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L6</f>
         <v>FTE-INDGAS</v>
       </c>
-      <c r="M17" s="113" t="str">
+      <c r="M17" s="111" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M6</f>
         <v>Sector Fuel Technology Existing Industry Natural Gas</v>
       </c>
-      <c r="N17" s="112" t="str">
+      <c r="N17" s="110" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O17" s="112" t="str">
+      <c r="O17" s="110" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="P17" s="112"/>
-      <c r="Q17" s="112"/>
-      <c r="R17" s="112"/>
+      <c r="P17" s="110"/>
+      <c r="Q17" s="110"/>
+      <c r="R17" s="110"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" t="str">
@@ -7139,7 +7123,7 @@
         <f>L7</f>
         <v>INDOIL</v>
       </c>
-      <c r="E18" s="115">
+      <c r="E18" s="113">
         <f>-'EB1'!G$7/-SUM('EB1'!$G$7:$M$7)</f>
         <v>0.99164862356943995</v>
       </c>
@@ -7150,104 +7134,104 @@
       <c r="H18" s="75">
         <v>50</v>
       </c>
-      <c r="J18" s="112"/>
-      <c r="K18" s="112"/>
-      <c r="L18" s="112" t="str">
+      <c r="J18" s="110"/>
+      <c r="K18" s="110"/>
+      <c r="L18" s="110" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L7</f>
         <v>FTE-INDOIL</v>
       </c>
-      <c r="M18" s="113" t="str">
+      <c r="M18" s="111" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M7</f>
         <v>Sector Fuel Technology Existing Industry Crude Oil</v>
       </c>
-      <c r="N18" s="112" t="str">
+      <c r="N18" s="110" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O18" s="112" t="str">
+      <c r="O18" s="110" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="P18" s="112"/>
-      <c r="Q18" s="112"/>
-      <c r="R18" s="112"/>
+      <c r="P18" s="110"/>
+      <c r="Q18" s="110"/>
+      <c r="R18" s="110"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C19" t="str">
         <f>'EB1'!H$2</f>
         <v>KER</v>
       </c>
-      <c r="E19" s="115">
+      <c r="E19" s="113">
         <f>-'EB1'!H$7/-SUM('EB1'!$G$7:$M$7)</f>
         <v>0</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="74"/>
       <c r="H19" s="75"/>
-      <c r="J19" s="112"/>
-      <c r="K19" s="112"/>
-      <c r="L19" s="112" t="str">
+      <c r="J19" s="110"/>
+      <c r="K19" s="110"/>
+      <c r="L19" s="110" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L8</f>
         <v>FTE-INDBIO</v>
       </c>
-      <c r="M19" s="113" t="str">
+      <c r="M19" s="111" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M8</f>
         <v>Sector Fuel Technology Existing Industry Biomass</v>
       </c>
-      <c r="N19" s="112" t="str">
+      <c r="N19" s="110" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O19" s="112" t="str">
+      <c r="O19" s="110" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="P19" s="112"/>
-      <c r="Q19" s="112"/>
-      <c r="R19" s="112"/>
+      <c r="P19" s="110"/>
+      <c r="Q19" s="110"/>
+      <c r="R19" s="110"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C20" t="str">
         <f>'EB1'!I$2</f>
         <v>LPG</v>
       </c>
-      <c r="E20" s="115">
+      <c r="E20" s="113">
         <f>-'EB1'!I$7/-SUM('EB1'!$G$7:$M$7)</f>
         <v>3.0047280279262957E-3</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="74"/>
       <c r="H20" s="75"/>
-      <c r="J20" s="112"/>
-      <c r="K20" s="112"/>
-      <c r="L20" s="112" t="str">
+      <c r="J20" s="110"/>
+      <c r="K20" s="110"/>
+      <c r="L20" s="110" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L9</f>
         <v>FTE-INDELC</v>
       </c>
-      <c r="M20" s="113" t="str">
+      <c r="M20" s="111" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M9</f>
         <v>Sector Fuel Technology Existing Industry Electricity</v>
       </c>
-      <c r="N20" s="112" t="str">
+      <c r="N20" s="110" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O20" s="112" t="str">
+      <c r="O20" s="110" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="P20" s="112" t="s">
-        <v>147</v>
-      </c>
-      <c r="Q20" s="112"/>
-      <c r="R20" s="112"/>
+      <c r="P20" s="110" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q20" s="110"/>
+      <c r="R20" s="110"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C21" t="str">
         <f>'EB1'!J$2</f>
         <v>GSL</v>
       </c>
-      <c r="E21" s="115">
+      <c r="E21" s="113">
         <f>-'EB1'!J$7/-SUM('EB1'!$G$7:$M$7)</f>
         <v>0</v>
       </c>
@@ -7261,7 +7245,7 @@
         <f>'EB1'!K$2</f>
         <v>NAP</v>
       </c>
-      <c r="E22" s="115">
+      <c r="E22" s="113">
         <f>-'EB1'!K$7/-SUM('EB1'!$G$7:$M$7)</f>
         <v>0</v>
       </c>
@@ -7277,7 +7261,7 @@
         <f>'EB1'!L$2</f>
         <v>HFO</v>
       </c>
-      <c r="E23" s="115">
+      <c r="E23" s="113">
         <f>-'EB1'!L$7/-SUM('EB1'!$G$7:$M$7)</f>
         <v>5.3466484026335557E-3</v>
       </c>
@@ -7293,7 +7277,7 @@
         <f>'EB1'!M$2</f>
         <v>OPP</v>
       </c>
-      <c r="E24" s="115">
+      <c r="E24" s="113">
         <f>-'EB1'!M$7/-SUM('EB1'!$G$7:$M$7)</f>
         <v>0</v>
       </c>
@@ -7356,7 +7340,7 @@
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="24"/>
       <c r="D28" s="24"/>
-      <c r="E28" s="101"/>
+      <c r="E28" s="99"/>
       <c r="F28" s="12"/>
       <c r="G28" s="78"/>
       <c r="H28" s="11"/>
@@ -7364,7 +7348,7 @@
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="24"/>
       <c r="D29" s="24"/>
-      <c r="E29" s="101"/>
+      <c r="E29" s="99"/>
       <c r="F29" s="12"/>
       <c r="G29" s="78"/>
       <c r="H29" s="11"/>
@@ -7384,13 +7368,13 @@
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="42"/>
       <c r="C34" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="72"/>
       <c r="C35" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -7431,23 +7415,23 @@
   <sheetData>
     <row r="1" spans="2:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E1" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>80</v>
       </c>
       <c r="G1" s="8"/>
       <c r="I1" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
@@ -7473,46 +7457,46 @@
       </c>
       <c r="G2" s="10"/>
       <c r="I2" s="10" t="s">
-        <v>101</v>
-      </c>
-      <c r="M2" s="107" t="s">
+        <v>100</v>
+      </c>
+      <c r="M2" s="105" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="107"/>
-      <c r="O2" s="108"/>
-      <c r="P2" s="108"/>
-      <c r="Q2" s="108"/>
-      <c r="R2" s="108"/>
-      <c r="S2" s="108"/>
-      <c r="T2" s="108"/>
-      <c r="U2" s="108"/>
+      <c r="N2" s="105"/>
+      <c r="O2" s="106"/>
+      <c r="P2" s="106"/>
+      <c r="Q2" s="106"/>
+      <c r="R2" s="106"/>
+      <c r="S2" s="106"/>
+      <c r="T2" s="106"/>
+      <c r="U2" s="106"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="M3" s="109" t="s">
+      <c r="M3" s="107" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="110" t="s">
+      <c r="N3" s="108" t="s">
         <v>30</v>
       </c>
-      <c r="O3" s="109" t="s">
-        <v>0</v>
-      </c>
-      <c r="P3" s="109" t="s">
+      <c r="O3" s="107" t="s">
+        <v>0</v>
+      </c>
+      <c r="P3" s="107" t="s">
         <v>3</v>
       </c>
-      <c r="Q3" s="109" t="s">
+      <c r="Q3" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="R3" s="109" t="s">
+      <c r="R3" s="107" t="s">
         <v>8</v>
       </c>
-      <c r="S3" s="109" t="s">
+      <c r="S3" s="107" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="109" t="s">
+      <c r="T3" s="107" t="s">
         <v>10</v>
       </c>
-      <c r="U3" s="109" t="s">
+      <c r="U3" s="107" t="s">
         <v>12</v>
       </c>
     </row>
@@ -7524,31 +7508,31 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
-      <c r="M4" s="111" t="s">
-        <v>37</v>
-      </c>
-      <c r="N4" s="111" t="s">
+      <c r="M4" s="109" t="s">
+        <v>36</v>
+      </c>
+      <c r="N4" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="O4" s="111" t="s">
+      <c r="O4" s="109" t="s">
         <v>26</v>
       </c>
-      <c r="P4" s="111" t="s">
+      <c r="P4" s="109" t="s">
         <v>27</v>
       </c>
-      <c r="Q4" s="111" t="s">
+      <c r="Q4" s="109" t="s">
         <v>4</v>
       </c>
-      <c r="R4" s="111" t="s">
+      <c r="R4" s="109" t="s">
+        <v>39</v>
+      </c>
+      <c r="S4" s="109" t="s">
         <v>40</v>
       </c>
-      <c r="S4" s="111" t="s">
-        <v>41</v>
-      </c>
-      <c r="T4" s="111" t="s">
+      <c r="T4" s="109" t="s">
         <v>28</v>
       </c>
-      <c r="U4" s="111" t="s">
+      <c r="U4" s="109" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7560,25 +7544,25 @@
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
-      <c r="M5" s="108" t="s">
-        <v>85</v>
-      </c>
-      <c r="N5" s="112"/>
-      <c r="O5" s="108" t="str">
+      <c r="M5" s="106" t="s">
+        <v>84</v>
+      </c>
+      <c r="N5" s="110"/>
+      <c r="O5" s="106" t="str">
         <f>LEFT($M$5,1)&amp;LEFT(B2,1)&amp;'EB1'!$C$20</f>
         <v>DIBOIL</v>
       </c>
-      <c r="P5" s="108" t="str">
+      <c r="P5" s="106" t="str">
         <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB1'!$X$20</f>
         <v>Demand Industry Sector - Boiler</v>
       </c>
-      <c r="Q5" s="108" t="s">
-        <v>78</v>
-      </c>
-      <c r="R5" s="108"/>
-      <c r="S5" s="108"/>
-      <c r="T5" s="108"/>
-      <c r="U5" s="108"/>
+      <c r="Q5" s="106" t="s">
+        <v>77</v>
+      </c>
+      <c r="R5" s="106"/>
+      <c r="S5" s="106"/>
+      <c r="T5" s="106"/>
+      <c r="U5" s="106"/>
     </row>
     <row r="6" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="9"/>
@@ -7588,25 +7572,25 @@
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
-      <c r="M6" s="138" t="s">
-        <v>85</v>
-      </c>
-      <c r="N6" s="132"/>
-      <c r="O6" s="140" t="str">
+      <c r="M6" s="136" t="s">
+        <v>84</v>
+      </c>
+      <c r="N6" s="130"/>
+      <c r="O6" s="138" t="str">
         <f>LEFT($M$5,1)&amp;LEFT(B2,1)&amp;'EB1'!$C$21</f>
         <v>DIOAPP</v>
       </c>
-      <c r="P6" s="141" t="str">
+      <c r="P6" s="139" t="str">
         <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB1'!$X$21</f>
         <v>Demand Industry Sector - Other Appliance</v>
       </c>
-      <c r="Q6" s="108" t="s">
-        <v>78</v>
-      </c>
-      <c r="R6" s="108"/>
-      <c r="S6" s="108"/>
-      <c r="T6" s="108"/>
-      <c r="U6" s="108"/>
+      <c r="Q6" s="106" t="s">
+        <v>77</v>
+      </c>
+      <c r="R6" s="106"/>
+      <c r="S6" s="106"/>
+      <c r="T6" s="106"/>
+      <c r="U6" s="106"/>
     </row>
     <row r="7" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="9"/>
@@ -7616,25 +7600,25 @@
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
-      <c r="M7" s="108" t="s">
-        <v>85</v>
-      </c>
-      <c r="N7" s="112"/>
-      <c r="O7" s="108" t="str">
+      <c r="M7" s="106" t="s">
+        <v>84</v>
+      </c>
+      <c r="N7" s="110"/>
+      <c r="O7" s="106" t="str">
         <f>LEFT($M$5,1)&amp;LEFT(B2,1)&amp;'EB1'!$C$22</f>
         <v>DICOMP</v>
       </c>
-      <c r="P7" s="108" t="str">
+      <c r="P7" s="106" t="str">
         <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB1'!$X$22</f>
         <v>Demand Industry Sector - Compressor</v>
       </c>
-      <c r="Q7" s="108" t="s">
-        <v>78</v>
-      </c>
-      <c r="R7" s="108"/>
-      <c r="S7" s="108"/>
-      <c r="T7" s="108"/>
-      <c r="U7" s="108"/>
+      <c r="Q7" s="106" t="s">
+        <v>77</v>
+      </c>
+      <c r="R7" s="106"/>
+      <c r="S7" s="106"/>
+      <c r="T7" s="106"/>
+      <c r="U7" s="106"/>
     </row>
     <row r="8" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="9"/>
@@ -7644,55 +7628,55 @@
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
-      <c r="M8" s="108" t="s">
-        <v>85</v>
-      </c>
-      <c r="N8" s="112"/>
-      <c r="O8" s="108" t="str">
+      <c r="M8" s="106" t="s">
+        <v>84</v>
+      </c>
+      <c r="N8" s="110"/>
+      <c r="O8" s="106" t="str">
         <f>LEFT($M$5,1)&amp;LEFT(B2,1)&amp;'EB1'!$C$23</f>
         <v>DIPUMP</v>
       </c>
-      <c r="P8" s="108" t="str">
+      <c r="P8" s="106" t="str">
         <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB1'!$X$23</f>
         <v>Demand Industry Sector - Pump</v>
       </c>
-      <c r="Q8" s="108" t="s">
-        <v>78</v>
-      </c>
-      <c r="R8" s="108"/>
-      <c r="S8" s="108"/>
-      <c r="T8" s="108"/>
-      <c r="U8" s="108"/>
+      <c r="Q8" s="106" t="s">
+        <v>77</v>
+      </c>
+      <c r="R8" s="106"/>
+      <c r="S8" s="106"/>
+      <c r="T8" s="106"/>
+      <c r="U8" s="106"/>
     </row>
     <row r="9" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="9" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
-      <c r="M9" s="108" t="s">
-        <v>85</v>
-      </c>
-      <c r="N9" s="112"/>
-      <c r="O9" s="108" t="str">
+      <c r="M9" s="106" t="s">
+        <v>84</v>
+      </c>
+      <c r="N9" s="110"/>
+      <c r="O9" s="106" t="str">
         <f>LEFT($M$5,1)&amp;LEFT(B2,1)&amp;'EB1'!$C$24</f>
         <v>DIMOTO</v>
       </c>
-      <c r="P9" s="108" t="str">
+      <c r="P9" s="106" t="str">
         <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB1'!$X$24</f>
         <v>Demand Industry Sector - Heavy Motor</v>
       </c>
-      <c r="Q9" s="108" t="s">
-        <v>78</v>
-      </c>
-      <c r="R9" s="108"/>
-      <c r="S9" s="108"/>
-      <c r="T9" s="108"/>
-      <c r="U9" s="108"/>
+      <c r="Q9" s="106" t="s">
+        <v>77</v>
+      </c>
+      <c r="R9" s="106"/>
+      <c r="S9" s="106"/>
+      <c r="T9" s="106"/>
+      <c r="U9" s="106"/>
     </row>
     <row r="10" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" s="9"/>
@@ -7702,32 +7686,32 @@
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
-      <c r="M10" s="112" t="s">
-        <v>105</v>
-      </c>
-      <c r="N10" s="112"/>
-      <c r="O10" s="112" t="str">
+      <c r="M10" s="110" t="s">
+        <v>104</v>
+      </c>
+      <c r="N10" s="110"/>
+      <c r="O10" s="110" t="str">
         <f>$B$2&amp;'EB1'!$C$27</f>
         <v>INDCO2</v>
       </c>
-      <c r="P10" s="112" t="str">
+      <c r="P10" s="110" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$C$28</f>
         <v>Industry Carbon dioxide</v>
       </c>
-      <c r="Q10" s="112" t="str">
+      <c r="Q10" s="110" t="str">
         <f>'EB1'!$AA$2</f>
         <v>kt</v>
       </c>
-      <c r="R10" s="108"/>
-      <c r="S10" s="108"/>
-      <c r="T10" s="108"/>
-      <c r="U10" s="108"/>
+      <c r="R10" s="106"/>
+      <c r="S10" s="106"/>
+      <c r="T10" s="106"/>
+      <c r="U10" s="106"/>
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="R11" s="112"/>
-      <c r="S11" s="112"/>
-      <c r="T11" s="112"/>
-      <c r="U11" s="112"/>
+      <c r="R11" s="110"/>
+      <c r="S11" s="110"/>
+      <c r="T11" s="110"/>
+      <c r="U11" s="110"/>
     </row>
     <row r="12" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B12" s="9"/>
@@ -7737,15 +7721,15 @@
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
-      <c r="M12" s="108"/>
-      <c r="N12" s="112"/>
-      <c r="O12" s="108"/>
-      <c r="P12" s="108"/>
-      <c r="Q12" s="108"/>
-      <c r="R12" s="108"/>
-      <c r="S12" s="108"/>
-      <c r="T12" s="108"/>
-      <c r="U12" s="108"/>
+      <c r="M12" s="106"/>
+      <c r="N12" s="110"/>
+      <c r="O12" s="106"/>
+      <c r="P12" s="106"/>
+      <c r="Q12" s="106"/>
+      <c r="R12" s="106"/>
+      <c r="S12" s="106"/>
+      <c r="T12" s="106"/>
+      <c r="U12" s="106"/>
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="D14" s="4" t="s">
@@ -7757,17 +7741,17 @@
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="14"/>
-      <c r="M14" s="107" t="s">
+      <c r="M14" s="105" t="s">
         <v>15</v>
       </c>
-      <c r="N14" s="107"/>
-      <c r="O14" s="112"/>
-      <c r="P14" s="112"/>
-      <c r="Q14" s="112"/>
-      <c r="R14" s="112"/>
-      <c r="S14" s="112"/>
-      <c r="T14" s="112"/>
-      <c r="U14" s="112"/>
+      <c r="N14" s="105"/>
+      <c r="O14" s="110"/>
+      <c r="P14" s="110"/>
+      <c r="Q14" s="110"/>
+      <c r="R14" s="110"/>
+      <c r="S14" s="110"/>
+      <c r="T14" s="110"/>
+      <c r="U14" s="110"/>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B15" s="18" t="s">
@@ -7780,55 +7764,55 @@
         <v>6</v>
       </c>
       <c r="E15" s="81" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F15" s="81" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G15" s="81" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="H15" s="81" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="I15" s="81" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="J15" s="4"/>
-      <c r="K15" s="120" t="s">
+      <c r="K15" s="118" t="s">
         <v>35</v>
       </c>
-      <c r="M15" s="109" t="s">
+      <c r="M15" s="107" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="110" t="s">
+      <c r="N15" s="108" t="s">
         <v>30</v>
       </c>
-      <c r="O15" s="109" t="s">
+      <c r="O15" s="107" t="s">
         <v>1</v>
       </c>
-      <c r="P15" s="109" t="s">
+      <c r="P15" s="107" t="s">
         <v>2</v>
       </c>
-      <c r="Q15" s="109" t="s">
+      <c r="Q15" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="R15" s="109" t="s">
+      <c r="R15" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="S15" s="109" t="s">
+      <c r="S15" s="107" t="s">
         <v>18</v>
       </c>
-      <c r="T15" s="109" t="s">
+      <c r="T15" s="107" t="s">
         <v>19</v>
       </c>
-      <c r="U15" s="109" t="s">
+      <c r="U15" s="107" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="16" spans="2:21" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="16" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>32</v>
@@ -7840,89 +7824,89 @@
         <v>34</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="G16" s="93" t="s">
-        <v>99</v>
+        <v>90</v>
+      </c>
+      <c r="G16" s="91" t="s">
+        <v>98</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="J16" s="4"/>
-      <c r="K16" s="120" t="s">
-        <v>180</v>
-      </c>
-      <c r="M16" s="111" t="s">
-        <v>38</v>
-      </c>
-      <c r="N16" s="111" t="s">
+      <c r="K16" s="118" t="s">
+        <v>177</v>
+      </c>
+      <c r="M16" s="109" t="s">
+        <v>37</v>
+      </c>
+      <c r="N16" s="109" t="s">
         <v>31</v>
       </c>
-      <c r="O16" s="111" t="s">
+      <c r="O16" s="109" t="s">
         <v>21</v>
       </c>
-      <c r="P16" s="111" t="s">
+      <c r="P16" s="109" t="s">
         <v>22</v>
       </c>
-      <c r="Q16" s="111" t="s">
+      <c r="Q16" s="109" t="s">
         <v>23</v>
       </c>
-      <c r="R16" s="111" t="s">
+      <c r="R16" s="109" t="s">
         <v>24</v>
       </c>
-      <c r="S16" s="111" t="s">
-        <v>43</v>
-      </c>
-      <c r="T16" s="111" t="s">
+      <c r="S16" s="109" t="s">
         <v>42</v>
       </c>
-      <c r="U16" s="111" t="s">
+      <c r="T16" s="109" t="s">
+        <v>41</v>
+      </c>
+      <c r="U16" s="109" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="13" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F17" s="13"/>
-      <c r="G17" s="83"/>
+      <c r="G17" s="82"/>
       <c r="H17" s="13" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="13"/>
-      <c r="M17" s="111" t="s">
-        <v>83</v>
-      </c>
-      <c r="N17" s="111"/>
-      <c r="O17" s="111"/>
-      <c r="P17" s="111"/>
-      <c r="Q17" s="111"/>
-      <c r="R17" s="111"/>
-      <c r="S17" s="111"/>
-      <c r="T17" s="111"/>
-      <c r="U17" s="111"/>
+      <c r="M17" s="109" t="s">
+        <v>82</v>
+      </c>
+      <c r="N17" s="109"/>
+      <c r="O17" s="109"/>
+      <c r="P17" s="109"/>
+      <c r="Q17" s="109"/>
+      <c r="R17" s="109"/>
+      <c r="S17" s="109"/>
+      <c r="T17" s="109"/>
+      <c r="U17" s="109"/>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B18" s="112" t="str">
+      <c r="B18" s="110" t="str">
         <f t="shared" ref="B18:B24" si="0">O18</f>
         <v>IBOILECOA</v>
       </c>
       <c r="C18" t="s">
-        <v>176</v>
-      </c>
-      <c r="D18" s="112" t="str">
+        <v>173</v>
+      </c>
+      <c r="D18" s="110" t="str">
         <f>$O$5</f>
         <v>DIBOIL</v>
       </c>
@@ -7930,52 +7914,52 @@
         <f>'EB1'!$D$7*'EB1'!$D$20/(G18*H18)*1.01</f>
         <v>1.3022033997716895</v>
       </c>
-      <c r="F18" s="121">
+      <c r="F18" s="119">
         <v>0.8</v>
       </c>
-      <c r="G18" s="121">
+      <c r="G18" s="119">
         <v>0.5</v>
       </c>
-      <c r="H18" s="119">
+      <c r="H18" s="117">
         <v>31.536000000000001</v>
       </c>
       <c r="I18" s="42">
         <v>30</v>
       </c>
       <c r="J18" s="17"/>
-      <c r="K18" s="122">
+      <c r="K18" s="120">
         <f t="shared" ref="K18:K25" si="1">E18*G18*H18</f>
         <v>20.533143207600002</v>
       </c>
-      <c r="M18" s="108" t="s">
-        <v>97</v>
-      </c>
-      <c r="O18" s="112" t="str">
+      <c r="M18" s="106" t="s">
+        <v>96</v>
+      </c>
+      <c r="O18" s="110" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$20&amp;$I$2&amp;'EB1'!D$2</f>
         <v>IBOILECOA</v>
       </c>
-      <c r="P18" s="112" t="str">
+      <c r="P18" s="110" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$20&amp;" - "&amp;'EB1'!$D$3</f>
         <v>Demand Technologies Industry Sector - Existing Boiler - Solid Fuels</v>
       </c>
-      <c r="Q18" s="112" t="str">
+      <c r="Q18" s="110" t="str">
         <f t="shared" ref="Q18:Q26" si="2">$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="R18" s="112" t="str">
+      <c r="R18" s="110" t="str">
         <f t="shared" ref="R18:R26" si="3">$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B19" s="112" t="str">
+      <c r="B19" s="110" t="str">
         <f t="shared" si="0"/>
         <v>IBOILEBIO</v>
       </c>
       <c r="C19" t="s">
-        <v>178</v>
-      </c>
-      <c r="D19" s="112" t="str">
+        <v>175</v>
+      </c>
+      <c r="D19" s="110" t="str">
         <f>$O$5</f>
         <v>DIBOIL</v>
       </c>
@@ -7983,51 +7967,51 @@
         <f>'EB1'!$O$7*'EB1'!$O$20/(G19*H19)*1.01</f>
         <v>3.8442582643835617</v>
       </c>
-      <c r="F19" s="121">
+      <c r="F19" s="119">
         <v>0.85</v>
       </c>
-      <c r="G19" s="121">
+      <c r="G19" s="119">
         <v>0.5</v>
       </c>
-      <c r="H19" s="119">
+      <c r="H19" s="117">
         <v>31.536000000000001</v>
       </c>
       <c r="I19" s="42">
         <v>30</v>
       </c>
-      <c r="K19" s="122">
+      <c r="K19" s="120">
         <f t="shared" si="1"/>
         <v>60.616264312800006</v>
       </c>
-      <c r="M19" s="108" t="s">
-        <v>97</v>
-      </c>
-      <c r="O19" s="112" t="str">
+      <c r="M19" s="106" t="s">
+        <v>96</v>
+      </c>
+      <c r="O19" s="110" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$20&amp;$I$2&amp;'EB1'!O$2</f>
         <v>IBOILEBIO</v>
       </c>
-      <c r="P19" s="112" t="str">
+      <c r="P19" s="110" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$20&amp;" - "&amp;'EB1'!$O$3</f>
         <v>Demand Technologies Industry Sector - Existing Boiler - Biomass</v>
       </c>
-      <c r="Q19" s="112" t="str">
+      <c r="Q19" s="110" t="str">
         <f t="shared" si="2"/>
         <v>PJ</v>
       </c>
-      <c r="R19" s="112" t="str">
+      <c r="R19" s="110" t="str">
         <f t="shared" si="3"/>
         <v>PJa</v>
       </c>
     </row>
     <row r="20" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B20" s="112" t="str">
+      <c r="B20" s="110" t="str">
         <f t="shared" si="0"/>
         <v>IBOILEELC</v>
       </c>
       <c r="C20" t="s">
-        <v>179</v>
-      </c>
-      <c r="D20" s="112" t="str">
+        <v>176</v>
+      </c>
+      <c r="D20" s="110" t="str">
         <f>$O$5</f>
         <v>DIBOIL</v>
       </c>
@@ -8035,50 +8019,50 @@
         <f>'EB1'!$U$7*'EB1'!$U$20/(G20*H20)*1.01</f>
         <v>0</v>
       </c>
-      <c r="F20" s="121">
+      <c r="F20" s="119">
         <v>0.8</v>
       </c>
-      <c r="G20" s="121">
+      <c r="G20" s="119">
         <v>0.5</v>
       </c>
-      <c r="H20" s="119">
+      <c r="H20" s="117">
         <v>31.536000000000001</v>
       </c>
       <c r="I20" s="42">
         <v>30</v>
       </c>
-      <c r="K20" s="122">
+      <c r="K20" s="120">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M20" s="108" t="s">
-        <v>97</v>
-      </c>
-      <c r="O20" s="112" t="str">
+      <c r="M20" s="106" t="s">
+        <v>96</v>
+      </c>
+      <c r="O20" s="110" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$20&amp;$I$2&amp;'EB1'!U$2</f>
         <v>IBOILEELC</v>
       </c>
-      <c r="P20" s="112" t="str">
+      <c r="P20" s="110" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$20&amp;" - "&amp;'EB1'!$U$3</f>
         <v>Demand Technologies Industry Sector - Existing Boiler - Electricity</v>
       </c>
-      <c r="Q20" s="112" t="str">
+      <c r="Q20" s="110" t="str">
         <f t="shared" si="2"/>
         <v>PJ</v>
       </c>
-      <c r="R20" s="112" t="str">
+      <c r="R20" s="110" t="str">
         <f t="shared" si="3"/>
         <v>PJa</v>
       </c>
     </row>
     <row r="21" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B21" s="142" t="s">
-        <v>184</v>
-      </c>
-      <c r="C21" s="143" t="s">
-        <v>185</v>
-      </c>
-      <c r="D21" s="112" t="str">
+      <c r="B21" s="140" t="s">
+        <v>181</v>
+      </c>
+      <c r="C21" s="141" t="s">
+        <v>182</v>
+      </c>
+      <c r="D21" s="110" t="str">
         <f>$O$5</f>
         <v>DIBOIL</v>
       </c>
@@ -8086,104 +8070,104 @@
         <f>'EB1'!$L$7*'EB1'!$L$20/(G21*H21)*1.01</f>
         <v>3.2449824200913241E-3</v>
       </c>
-      <c r="F21" s="121">
+      <c r="F21" s="119">
         <v>0.8</v>
       </c>
-      <c r="G21" s="121">
+      <c r="G21" s="119">
         <v>0.5</v>
       </c>
-      <c r="H21" s="119">
+      <c r="H21" s="117">
         <v>31.536000000000001</v>
       </c>
       <c r="I21" s="42">
         <v>30</v>
       </c>
       <c r="J21" s="17"/>
-      <c r="K21" s="122">
+      <c r="K21" s="120">
         <f t="shared" ref="K21" si="4">E21*G21*H21</f>
         <v>5.1166882800000001E-2</v>
       </c>
-      <c r="M21" s="142" t="s">
-        <v>97</v>
-      </c>
-      <c r="O21" s="142" t="s">
-        <v>184</v>
-      </c>
-      <c r="P21" s="142" t="s">
-        <v>186</v>
-      </c>
-      <c r="Q21" s="112" t="str">
+      <c r="M21" s="140" t="s">
+        <v>96</v>
+      </c>
+      <c r="O21" s="140" t="s">
+        <v>181</v>
+      </c>
+      <c r="P21" s="140" t="s">
+        <v>183</v>
+      </c>
+      <c r="Q21" s="110" t="str">
         <f t="shared" si="2"/>
         <v>PJ</v>
       </c>
-      <c r="R21" s="112" t="str">
+      <c r="R21" s="110" t="str">
         <f t="shared" si="3"/>
         <v>PJa</v>
       </c>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B22" s="130" t="str">
+      <c r="B22" s="128" t="str">
         <f>O22</f>
         <v>IOAPPEDSL</v>
       </c>
-      <c r="C22" s="131" t="s">
-        <v>177</v>
-      </c>
-      <c r="D22" s="132" t="str">
+      <c r="C22" s="129" t="s">
+        <v>174</v>
+      </c>
+      <c r="D22" s="130" t="str">
         <f>$O$6</f>
         <v>DIOAPP</v>
       </c>
-      <c r="E22" s="133">
+      <c r="E22" s="131">
         <f>'EB1'!$G$7*'EB1'!$G$21/(G22*H22)*1.01</f>
         <v>0.60185037579908673</v>
       </c>
-      <c r="F22" s="134">
+      <c r="F22" s="132">
         <v>0.2</v>
       </c>
-      <c r="G22" s="134">
+      <c r="G22" s="132">
         <v>0.5</v>
       </c>
-      <c r="H22" s="135">
+      <c r="H22" s="133">
         <v>31.536000000000001</v>
       </c>
-      <c r="I22" s="136">
+      <c r="I22" s="134">
         <v>10</v>
       </c>
-      <c r="J22" s="131"/>
-      <c r="K22" s="137">
+      <c r="J22" s="129"/>
+      <c r="K22" s="135">
         <f>E22*G22*H22</f>
         <v>9.4899767256000001</v>
       </c>
-      <c r="M22" s="138" t="s">
-        <v>97</v>
-      </c>
-      <c r="N22" s="131"/>
-      <c r="O22" s="132" t="str">
+      <c r="M22" s="136" t="s">
+        <v>96</v>
+      </c>
+      <c r="N22" s="129"/>
+      <c r="O22" s="130" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$21&amp;$I$2&amp;'EB1'!G$2</f>
         <v>IOAPPEDSL</v>
       </c>
-      <c r="P22" s="132" t="str">
+      <c r="P22" s="130" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$21&amp;" - "&amp;'EB1'!$G$3</f>
         <v>Demand Technologies Industry Sector - Existing Other Appliance - Diesel oil</v>
       </c>
-      <c r="Q22" s="132" t="str">
+      <c r="Q22" s="130" t="str">
         <f t="shared" si="2"/>
         <v>PJ</v>
       </c>
-      <c r="R22" s="139" t="str">
+      <c r="R22" s="137" t="str">
         <f t="shared" si="3"/>
         <v>PJa</v>
       </c>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B23" s="112" t="str">
+      <c r="B23" s="110" t="str">
         <f t="shared" si="0"/>
         <v>IOAPPEELC</v>
       </c>
       <c r="C23" t="s">
-        <v>179</v>
-      </c>
-      <c r="D23" s="112" t="str">
+        <v>176</v>
+      </c>
+      <c r="D23" s="110" t="str">
         <f>$O$6</f>
         <v>DIOAPP</v>
       </c>
@@ -8191,51 +8175,51 @@
         <f>'EB1'!$U$7*'EB1'!$U$21/(G23*H23)*1.01</f>
         <v>0.24567332813926943</v>
       </c>
-      <c r="F23" s="121">
+      <c r="F23" s="119">
         <v>0.95</v>
       </c>
-      <c r="G23" s="121">
+      <c r="G23" s="119">
         <v>0.5</v>
       </c>
-      <c r="H23" s="119">
+      <c r="H23" s="117">
         <v>31.536000000000001</v>
       </c>
       <c r="I23" s="42">
         <v>10</v>
       </c>
-      <c r="K23" s="122">
+      <c r="K23" s="120">
         <f t="shared" si="1"/>
         <v>3.8737770381000005</v>
       </c>
-      <c r="M23" s="108" t="s">
-        <v>97</v>
-      </c>
-      <c r="O23" s="112" t="str">
+      <c r="M23" s="106" t="s">
+        <v>96</v>
+      </c>
+      <c r="O23" s="110" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$21&amp;$I$2&amp;'EB1'!U$2</f>
         <v>IOAPPEELC</v>
       </c>
-      <c r="P23" s="112" t="str">
+      <c r="P23" s="110" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$21&amp;" - "&amp;'EB1'!$U$3</f>
         <v>Demand Technologies Industry Sector - Existing Other Appliance - Electricity</v>
       </c>
-      <c r="Q23" s="112" t="str">
+      <c r="Q23" s="110" t="str">
         <f t="shared" si="2"/>
         <v>PJ</v>
       </c>
-      <c r="R23" s="112" t="str">
+      <c r="R23" s="110" t="str">
         <f t="shared" si="3"/>
         <v>PJa</v>
       </c>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B24" s="112" t="str">
+      <c r="B24" s="110" t="str">
         <f t="shared" si="0"/>
         <v>ICOMPEELC</v>
       </c>
       <c r="C24" t="s">
-        <v>179</v>
-      </c>
-      <c r="D24" s="112" t="str">
+        <v>176</v>
+      </c>
+      <c r="D24" s="110" t="str">
         <f>$O$7</f>
         <v>DICOMP</v>
       </c>
@@ -8243,51 +8227,51 @@
         <f>'EB1'!$U$7*'EB1'!$U$22/(G24*H24)*1.01</f>
         <v>0.19653866251141555</v>
       </c>
-      <c r="F24" s="121">
+      <c r="F24" s="119">
         <v>0.95</v>
       </c>
-      <c r="G24" s="121">
+      <c r="G24" s="119">
         <v>0.5</v>
       </c>
-      <c r="H24" s="119">
+      <c r="H24" s="117">
         <v>31.536000000000001</v>
       </c>
       <c r="I24" s="42">
         <v>10</v>
       </c>
-      <c r="K24" s="122">
+      <c r="K24" s="120">
         <f t="shared" si="1"/>
         <v>3.0990216304800007</v>
       </c>
-      <c r="M24" s="108" t="s">
-        <v>97</v>
-      </c>
-      <c r="O24" s="112" t="str">
+      <c r="M24" s="106" t="s">
+        <v>96</v>
+      </c>
+      <c r="O24" s="110" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$22&amp;$I$2&amp;'EB1'!U$2</f>
         <v>ICOMPEELC</v>
       </c>
-      <c r="P24" s="112" t="str">
+      <c r="P24" s="110" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$22&amp;" - "&amp;'EB1'!$U$3</f>
         <v>Demand Technologies Industry Sector - Existing Compressor - Electricity</v>
       </c>
-      <c r="Q24" s="112" t="str">
+      <c r="Q24" s="110" t="str">
         <f t="shared" si="2"/>
         <v>PJ</v>
       </c>
-      <c r="R24" s="112" t="str">
+      <c r="R24" s="110" t="str">
         <f t="shared" si="3"/>
         <v>PJa</v>
       </c>
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B25" s="112" t="str">
+      <c r="B25" s="110" t="str">
         <f>O25</f>
         <v>IPUMPEELC</v>
       </c>
       <c r="C25" t="s">
-        <v>179</v>
-      </c>
-      <c r="D25" s="112" t="str">
+        <v>176</v>
+      </c>
+      <c r="D25" s="110" t="str">
         <f>$O$8</f>
         <v>DIPUMP</v>
       </c>
@@ -8295,52 +8279,52 @@
         <f>'EB1'!$U$7*'EB1'!$U$23/(G25*H25)*1.01</f>
         <v>0.24567332813926943</v>
       </c>
-      <c r="F25" s="121">
+      <c r="F25" s="119">
         <v>0.6</v>
       </c>
-      <c r="G25" s="121">
+      <c r="G25" s="119">
         <v>0.5</v>
       </c>
-      <c r="H25" s="119">
+      <c r="H25" s="117">
         <v>31.536000000000001</v>
       </c>
       <c r="I25" s="42">
         <v>10</v>
       </c>
-      <c r="J25" s="103"/>
-      <c r="K25" s="122">
+      <c r="J25" s="101"/>
+      <c r="K25" s="120">
         <f t="shared" si="1"/>
         <v>3.8737770381000005</v>
       </c>
-      <c r="M25" s="108" t="s">
-        <v>97</v>
-      </c>
-      <c r="O25" s="112" t="str">
+      <c r="M25" s="106" t="s">
+        <v>96</v>
+      </c>
+      <c r="O25" s="110" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$23&amp;$I$2&amp;'EB1'!U$2</f>
         <v>IPUMPEELC</v>
       </c>
-      <c r="P25" s="112" t="str">
+      <c r="P25" s="110" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$23&amp;" - "&amp;'EB1'!$U$3</f>
         <v>Demand Technologies Industry Sector - Existing Pump - Electricity</v>
       </c>
-      <c r="Q25" s="112" t="str">
+      <c r="Q25" s="110" t="str">
         <f t="shared" si="2"/>
         <v>PJ</v>
       </c>
-      <c r="R25" s="112" t="str">
+      <c r="R25" s="110" t="str">
         <f t="shared" si="3"/>
         <v>PJa</v>
       </c>
     </row>
     <row r="26" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B26" s="112" t="str">
+      <c r="B26" s="110" t="str">
         <f>O26</f>
         <v>IMOTOEELC</v>
       </c>
       <c r="C26" t="s">
-        <v>179</v>
-      </c>
-      <c r="D26" s="112" t="str">
+        <v>176</v>
+      </c>
+      <c r="D26" s="110" t="str">
         <f>$O$9</f>
         <v>DIMOTO</v>
       </c>
@@ -8348,72 +8332,72 @@
         <f>'EB1'!$U$7*'EB1'!$U$24/(G26*H26)*1.01</f>
         <v>0.28574701535038105</v>
       </c>
-      <c r="F26" s="121">
+      <c r="F26" s="119">
         <v>0.9</v>
       </c>
-      <c r="G26" s="121">
+      <c r="G26" s="119">
         <v>0.5</v>
       </c>
-      <c r="H26" s="119">
+      <c r="H26" s="117">
         <v>32.536000000000001</v>
       </c>
       <c r="I26" s="42">
         <v>10</v>
       </c>
-      <c r="J26" s="103"/>
-      <c r="K26" s="122">
+      <c r="J26" s="101"/>
+      <c r="K26" s="120">
         <f t="shared" ref="K26" si="5">E26*G26*H26</f>
         <v>4.648532445719999</v>
       </c>
-      <c r="M26" s="108" t="s">
-        <v>97</v>
-      </c>
-      <c r="O26" s="112" t="str">
+      <c r="M26" s="106" t="s">
+        <v>96</v>
+      </c>
+      <c r="O26" s="110" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$24&amp;$I$2&amp;'EB1'!U$2</f>
         <v>IMOTOEELC</v>
       </c>
-      <c r="P26" s="112" t="str">
+      <c r="P26" s="110" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$24&amp;" - "&amp;'EB1'!$U$3</f>
         <v>Demand Technologies Industry Sector - Existing Heavy Motor - Electricity</v>
       </c>
-      <c r="Q26" s="112" t="str">
+      <c r="Q26" s="110" t="str">
         <f t="shared" si="2"/>
         <v>PJ</v>
       </c>
-      <c r="R26" s="112" t="str">
+      <c r="R26" s="110" t="str">
         <f t="shared" si="3"/>
         <v>PJa</v>
       </c>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I27" s="103"/>
-      <c r="J27" s="103"/>
+      <c r="I27" s="101"/>
+      <c r="J27" s="101"/>
       <c r="K27" s="17"/>
     </row>
     <row r="28" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I28" s="103"/>
-      <c r="J28" s="103"/>
+      <c r="I28" s="101"/>
+      <c r="J28" s="101"/>
       <c r="K28" s="17"/>
     </row>
     <row r="29" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B29" s="42"/>
       <c r="C29" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="I29" s="103"/>
-      <c r="J29" s="103"/>
+        <v>140</v>
+      </c>
+      <c r="I29" s="101"/>
+      <c r="J29" s="101"/>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B30" s="72"/>
       <c r="C30" s="1" t="s">
-        <v>144</v>
-      </c>
-      <c r="I30" s="103"/>
-      <c r="J30" s="103"/>
+        <v>141</v>
+      </c>
+      <c r="I30" s="101"/>
+      <c r="J30" s="101"/>
     </row>
     <row r="31" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I31" s="103"/>
-      <c r="J31" s="103"/>
+      <c r="I31" s="101"/>
+      <c r="J31" s="101"/>
       <c r="L31" s="1"/>
     </row>
     <row r="32" spans="2:21" x14ac:dyDescent="0.25">
@@ -8455,24 +8439,24 @@
   <sheetData>
     <row r="1" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="8" t="s">
+        <v>74</v>
+      </c>
+      <c r="C1" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>76</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>77</v>
-      </c>
       <c r="E1" s="8" t="s">
+        <v>78</v>
+      </c>
+      <c r="F1" s="8" t="s">
         <v>79</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="2" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="10" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
@@ -8486,163 +8470,83 @@
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="C5" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="3"/>
-      <c r="E5" s="1"/>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B6" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E6" s="85">
-        <v>2021</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="J6" s="2">
         <v>2021</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="31.2" x14ac:dyDescent="0.25">
-      <c r="B7" s="16" t="s">
+      <c r="G7" s="16" t="s">
+        <v>82</v>
+      </c>
+      <c r="H7" s="16" t="s">
         <v>83</v>
-      </c>
-      <c r="C7" s="16" t="s">
-        <v>84</v>
-      </c>
-      <c r="D7" s="16" t="s">
-        <v>138</v>
-      </c>
-      <c r="E7" s="82" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="H7" s="16" t="s">
-        <v>84</v>
       </c>
       <c r="I7" s="16"/>
       <c r="J7" s="16"/>
     </row>
     <row r="8" spans="2:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="16" t="s">
-        <v>92</v>
-      </c>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="82" t="str">
-        <f>E2</f>
-        <v>PJ</v>
-      </c>
       <c r="G8" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" t="str">
-        <f>DemTechs_IND!$O5</f>
-        <v>DIBOIL</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="76">
-        <f>SUM(DemTechs_IND!K18:K20)</f>
-        <v>81.149407520400004</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H9" s="1" t="str">
         <f>DemTechs_IND!$O$5</f>
         <v>DIBOIL</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J9" s="73">
         <v>0.35</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" t="str">
-        <f>DemTechs_IND!$O6</f>
-        <v>DIOAPP</v>
-      </c>
-      <c r="D10" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E10" s="76">
-        <f>DemTechs_IND!K23+DemTechs_IND!K22</f>
-        <v>13.3637537637</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H10" s="1" t="str">
         <f>DemTechs_IND!$O$5</f>
         <v>DIBOIL</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J10" s="73">
         <v>0.15</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" t="str">
-        <f>DemTechs_IND!$O7</f>
-        <v>DICOMP</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E11" s="76">
-        <f>DemTechs_IND!K24</f>
-        <v>3.0990216304800007</v>
-      </c>
       <c r="G11" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H11" s="1" t="str">
         <f>DemTechs_IND!$O$5</f>
         <v>DIBOIL</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J11" s="73">
         <f>1-J9-J10-J12</f>
@@ -8650,90 +8554,60 @@
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" t="str">
-        <f>DemTechs_IND!$O8</f>
-        <v>DIPUMP</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E12" s="76">
-        <f>DemTechs_IND!K25</f>
-        <v>3.8737770381000005</v>
-      </c>
       <c r="G12" s="28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H12" s="28" t="str">
         <f>DemTechs_IND!$O$5</f>
         <v>DIBOIL</v>
       </c>
       <c r="I12" s="29" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J12" s="77">
         <v>0.15</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B13" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" t="str">
-        <f>DemTechs_IND!$O9</f>
-        <v>DIMOTO</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="E13" s="76">
-        <f>DemTechs_IND!K26</f>
-        <v>4.648532445719999</v>
-      </c>
       <c r="G13" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H13" s="1" t="str">
         <f>DemTechs_IND!$O$6</f>
         <v>DIOAPP</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J13" s="73">
         <v>0.35</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E14" s="26"/>
       <c r="G14" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H14" s="1" t="str">
         <f>DemTechs_IND!$O$6</f>
         <v>DIOAPP</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J14" s="73">
         <v>0.15</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E15" s="26"/>
       <c r="G15" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H15" s="1" t="str">
         <f>DemTechs_IND!$O$6</f>
         <v>DIOAPP</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J15" s="73">
         <f>1-J13-J14-J16</f>
@@ -8741,48 +8615,45 @@
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E16" s="26"/>
       <c r="G16" s="28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H16" s="28" t="str">
         <f>DemTechs_IND!$O$6</f>
         <v>DIOAPP</v>
       </c>
       <c r="I16" s="29" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J16" s="77">
         <v>0.15</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E17" s="26"/>
       <c r="G17" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H17" s="1" t="str">
         <f>DemTechs_IND!$O$7</f>
         <v>DICOMP</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J17" s="73">
         <v>0.35</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="E18" s="26"/>
       <c r="G18" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H18" s="1" t="str">
         <f>DemTechs_IND!$O$7</f>
         <v>DICOMP</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J18" s="73">
         <v>0.15</v>
@@ -8791,14 +8662,14 @@
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E19" s="26"/>
       <c r="G19" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H19" s="1" t="str">
         <f>DemTechs_IND!$O$7</f>
         <v>DICOMP</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J19" s="73">
         <f>1-J17-J18-J20</f>
@@ -8808,14 +8679,14 @@
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E20" s="26"/>
       <c r="G20" s="28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H20" s="28" t="str">
         <f>DemTechs_IND!$O$7</f>
         <v>DICOMP</v>
       </c>
       <c r="I20" s="29" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J20" s="77">
         <v>0.15</v>
@@ -8824,14 +8695,14 @@
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E21" s="26"/>
       <c r="G21" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H21" s="1" t="str">
         <f>DemTechs_IND!$O$8</f>
         <v>DIPUMP</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J21" s="73">
         <v>0.35</v>
@@ -8840,14 +8711,14 @@
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E22" s="26"/>
       <c r="G22" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H22" s="1" t="str">
         <f>DemTechs_IND!$O$8</f>
         <v>DIPUMP</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J22" s="73">
         <v>0.15</v>
@@ -8856,14 +8727,14 @@
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E23" s="26"/>
       <c r="G23" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H23" s="1" t="str">
         <f>DemTechs_IND!$O$8</f>
         <v>DIPUMP</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J23" s="73">
         <f>1-J21-J22-J24</f>
@@ -8873,14 +8744,14 @@
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E24" s="7"/>
       <c r="G24" s="28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H24" s="28" t="str">
         <f>DemTechs_IND!$O$8</f>
         <v>DIPUMP</v>
       </c>
       <c r="I24" s="29" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J24" s="77">
         <v>0.15</v>
@@ -8888,14 +8759,14 @@
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G25" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H25" s="1" t="str">
         <f>DemTechs_IND!$O$9</f>
         <v>DIMOTO</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="J25" s="73">
         <v>0.35</v>
@@ -8904,14 +8775,14 @@
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E26" s="7"/>
       <c r="G26" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H26" s="1" t="str">
         <f>DemTechs_IND!$O$9</f>
         <v>DIMOTO</v>
       </c>
       <c r="I26" s="24" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J26" s="73">
         <v>0.15</v>
@@ -8919,14 +8790,14 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G27" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H27" s="1" t="str">
         <f>DemTechs_IND!$O$9</f>
         <v>DIMOTO</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="J27" s="73">
         <f>1-J25-J26-J28</f>
@@ -8935,14 +8806,14 @@
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G28" s="28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H28" s="28" t="str">
         <f>DemTechs_IND!$O$9</f>
         <v>DIMOTO</v>
       </c>
       <c r="I28" s="29" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="J28" s="77">
         <v>0.15</v>
@@ -8951,13 +8822,13 @@
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="42"/>
       <c r="C32" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="72"/>
       <c r="C33" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -8976,7 +8847,7 @@
   <sheetData>
     <row r="3" spans="2:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="33" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -8996,7 +8867,7 @@
     </row>
     <row r="5" spans="2:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B5" s="31" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C5" s="32"/>
     </row>
@@ -9017,28 +8888,28 @@
         <v>INDOIL</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="G6" s="35"/>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="2:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="15" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>142</v>
-      </c>
-      <c r="G7" s="102"/>
+        <v>139</v>
+      </c>
+      <c r="G7" s="100"/>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
@@ -9064,13 +8935,13 @@
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="42"/>
       <c r="C23" s="1" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="72"/>
       <c r="C24" s="1" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
   </sheetData>

--- a/VT_REG1_IND_V12_New.xlsx
+++ b/VT_REG1_IND_V12_New.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr showObjects="placeholders" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\My Drive\001_Dissertation_WORKING\003_TIMES_WORKING\005_Cambodia-TIMES-Model-main_20261016\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="I:\My Drive\001_Academic\002_Course_Works\003_2026_Sping_Semester\003_Low-Carbon Technologies and Policies\000_ICP_BL\006_Cambodia_TIMES_Model_V002\KHM_TIMES_V002_20260606\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78EF516F-C38E-4C69-8E4C-7D45234A4A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E35902F0-8912-449D-856B-1C5909F5CE92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EB1" sheetId="133" r:id="rId1"/>
@@ -1539,7 +1539,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="184">
   <si>
     <t>CommName</t>
   </si>
@@ -1649,6 +1649,9 @@
     <t>Demand</t>
   </si>
   <si>
+    <t>Demand Value</t>
+  </si>
+  <si>
     <t>*Commodity Set Membership</t>
   </si>
   <si>
@@ -1949,6 +1952,12 @@
     <t>~COMEMI</t>
   </si>
   <si>
+    <t>*Unit</t>
+  </si>
+  <si>
+    <t>Demand Unit</t>
+  </si>
+  <si>
     <t>Input Share</t>
   </si>
   <si>
@@ -2082,15 +2091,6 @@
   </si>
   <si>
     <t>Other Appliance</t>
-  </si>
-  <si>
-    <t>IBOILEHFO</t>
-  </si>
-  <si>
-    <t>INDHFO</t>
-  </si>
-  <si>
-    <t>Demand Technologies Industry Sector - Existing Boiler - HFO</t>
   </si>
 </sst>
 </file>
@@ -2405,7 +2405,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -2617,43 +2617,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFFF0000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FFFF0000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFF0000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FFFF0000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFF0000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FFFF0000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFFF0000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFFF0000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -2685,7 +2648,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2834,10 +2797,16 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="11" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="23" fillId="4" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="4" borderId="17" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="12" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="5" borderId="0" xfId="2"/>
@@ -2928,23 +2897,6 @@
     <xf numFmtId="0" fontId="4" fillId="12" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="15" borderId="20" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="0" fillId="13" borderId="20" xfId="16" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="20" xfId="9" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="20" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="29" fillId="18" borderId="21" xfId="27" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="5" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="4" fillId="14" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="28">
     <cellStyle name="20% - Accent5" xfId="1" builtinId="46"/>
@@ -3924,6 +3876,11 @@
     <sheetDataSet>
       <sheetData sheetId="0"/>
       <sheetData sheetId="1">
+        <row r="5">
+          <cell r="D5">
+            <v>0.49906656000000005</v>
+          </cell>
+        </row>
         <row r="16">
           <cell r="D16">
             <v>0</v>
@@ -4788,246 +4745,246 @@
   <sheetData>
     <row r="1" spans="2:45" x14ac:dyDescent="0.25">
       <c r="X1" s="21" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="2:45" ht="15.6" x14ac:dyDescent="0.3">
       <c r="D2" s="39" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E2" s="39" t="s">
+        <v>45</v>
+      </c>
+      <c r="F2" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="G2" s="39" t="s">
+        <v>123</v>
+      </c>
+      <c r="H2" s="39" t="s">
+        <v>124</v>
+      </c>
+      <c r="I2" s="39" t="s">
+        <v>125</v>
+      </c>
+      <c r="J2" s="39" t="s">
+        <v>126</v>
+      </c>
+      <c r="K2" s="39" t="s">
+        <v>127</v>
+      </c>
+      <c r="L2" s="39" t="s">
+        <v>128</v>
+      </c>
+      <c r="M2" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="N2" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="O2" s="39" t="s">
+        <v>151</v>
+      </c>
+      <c r="P2" s="39" t="s">
+        <v>152</v>
+      </c>
+      <c r="Q2" s="39" t="s">
+        <v>153</v>
+      </c>
+      <c r="R2" s="39" t="s">
+        <v>154</v>
+      </c>
+      <c r="S2" s="39" t="s">
+        <v>49</v>
+      </c>
+      <c r="T2" s="39" t="s">
+        <v>50</v>
+      </c>
+      <c r="U2" s="39" t="s">
+        <v>51</v>
+      </c>
+      <c r="V2" s="39" t="s">
+        <v>148</v>
+      </c>
+      <c r="Y2" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z2" s="10" t="s">
+        <v>78</v>
+      </c>
+      <c r="AA2" s="10" t="s">
+        <v>104</v>
+      </c>
+      <c r="AE2" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="F2" s="39" t="s">
+      <c r="AF2" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="G2" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="H2" s="39" t="s">
+      <c r="AG2" s="39" t="s">
+        <v>46</v>
+      </c>
+      <c r="AH2" s="39" t="s">
         <v>123</v>
       </c>
-      <c r="I2" s="39" t="s">
+      <c r="AI2" s="39" t="s">
         <v>124</v>
       </c>
-      <c r="J2" s="39" t="s">
+      <c r="AJ2" s="39" t="s">
         <v>125</v>
       </c>
-      <c r="K2" s="39" t="s">
+      <c r="AK2" s="39" t="s">
         <v>126</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="AL2" s="39" t="s">
         <v>127</v>
       </c>
-      <c r="M2" s="39" t="s">
+      <c r="AM2" s="39" t="s">
         <v>128</v>
       </c>
-      <c r="N2" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="O2" s="39" t="s">
-        <v>148</v>
-      </c>
-      <c r="P2" s="39" t="s">
-        <v>149</v>
-      </c>
-      <c r="Q2" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="R2" s="39" t="s">
-        <v>151</v>
-      </c>
-      <c r="S2" s="39" t="s">
+      <c r="AN2" s="39" t="s">
+        <v>129</v>
+      </c>
+      <c r="AO2" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="AP2" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="T2" s="39" t="s">
+      <c r="AQ2" s="39" t="s">
         <v>49</v>
       </c>
-      <c r="U2" s="39" t="s">
+      <c r="AR2" s="39" t="s">
         <v>50</v>
       </c>
-      <c r="V2" s="39" t="s">
-        <v>145</v>
-      </c>
-      <c r="Y2" s="38" t="s">
-        <v>157</v>
-      </c>
-      <c r="Z2" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="AA2" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="AE2" s="39" t="s">
-        <v>43</v>
-      </c>
-      <c r="AF2" s="39" t="s">
-        <v>44</v>
-      </c>
-      <c r="AG2" s="39" t="s">
-        <v>45</v>
-      </c>
-      <c r="AH2" s="39" t="s">
-        <v>122</v>
-      </c>
-      <c r="AI2" s="39" t="s">
-        <v>123</v>
-      </c>
-      <c r="AJ2" s="39" t="s">
-        <v>124</v>
-      </c>
-      <c r="AK2" s="39" t="s">
-        <v>125</v>
-      </c>
-      <c r="AL2" s="39" t="s">
-        <v>126</v>
-      </c>
-      <c r="AM2" s="39" t="s">
-        <v>127</v>
-      </c>
-      <c r="AN2" s="39" t="s">
-        <v>128</v>
-      </c>
-      <c r="AO2" s="39" t="s">
-        <v>46</v>
-      </c>
-      <c r="AP2" s="39" t="s">
-        <v>47</v>
-      </c>
-      <c r="AQ2" s="39" t="s">
-        <v>48</v>
-      </c>
-      <c r="AR2" s="39" t="s">
-        <v>49</v>
-      </c>
       <c r="AS2" s="39" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3" spans="2:45" ht="39.6" x14ac:dyDescent="0.25">
       <c r="C3" s="71" t="s">
+        <v>120</v>
+      </c>
+      <c r="D3" s="40" t="s">
+        <v>52</v>
+      </c>
+      <c r="E3" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" s="40" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="H3" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="I3" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="J3" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="K3" s="40" t="s">
+        <v>134</v>
+      </c>
+      <c r="L3" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="M3" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="N3" s="40" t="s">
+        <v>54</v>
+      </c>
+      <c r="O3" s="40" t="s">
+        <v>155</v>
+      </c>
+      <c r="P3" s="40" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q3" s="40" t="s">
+        <v>157</v>
+      </c>
+      <c r="R3" s="40" t="s">
+        <v>158</v>
+      </c>
+      <c r="S3" s="40" t="s">
+        <v>56</v>
+      </c>
+      <c r="T3" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="U3" s="40" t="s">
+        <v>89</v>
+      </c>
+      <c r="V3" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC3" s="21" t="s">
         <v>119</v>
-      </c>
-      <c r="D3" s="40" t="s">
-        <v>51</v>
-      </c>
-      <c r="E3" s="40" t="s">
-        <v>52</v>
-      </c>
-      <c r="F3" s="40" t="s">
-        <v>121</v>
-      </c>
-      <c r="G3" s="40" t="s">
-        <v>134</v>
-      </c>
-      <c r="H3" s="40" t="s">
-        <v>131</v>
-      </c>
-      <c r="I3" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="J3" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="K3" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="L3" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="M3" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="N3" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="O3" s="40" t="s">
-        <v>152</v>
-      </c>
-      <c r="P3" s="40" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q3" s="40" t="s">
-        <v>154</v>
-      </c>
-      <c r="R3" s="40" t="s">
-        <v>155</v>
-      </c>
-      <c r="S3" s="40" t="s">
-        <v>55</v>
-      </c>
-      <c r="T3" s="40" t="s">
-        <v>56</v>
-      </c>
-      <c r="U3" s="40" t="s">
-        <v>88</v>
-      </c>
-      <c r="V3" s="40" t="s">
-        <v>57</v>
-      </c>
-      <c r="AC3" s="21" t="s">
-        <v>118</v>
       </c>
       <c r="AD3" s="5"/>
       <c r="AE3" s="40" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AF3" s="40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="AG3" s="40" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AH3" s="40" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI3" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="AJ3" s="40" t="s">
+        <v>125</v>
+      </c>
+      <c r="AK3" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="AL3" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="AI3" s="40" t="s">
+      <c r="AM3" s="40" t="s">
+        <v>130</v>
+      </c>
+      <c r="AN3" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="AJ3" s="40" t="s">
-        <v>124</v>
-      </c>
-      <c r="AK3" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="AL3" s="40" t="s">
-        <v>133</v>
-      </c>
-      <c r="AM3" s="40" t="s">
-        <v>129</v>
-      </c>
-      <c r="AN3" s="40" t="s">
-        <v>130</v>
-      </c>
       <c r="AO3" s="40" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="AP3" s="40" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="AQ3" s="40" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="AR3" s="40" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="AS3" s="40" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="4" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B4" s="37"/>
-      <c r="C4" s="85" t="s">
-        <v>58</v>
+      <c r="C4" s="87" t="s">
+        <v>59</v>
       </c>
       <c r="D4" s="5"/>
       <c r="E4" s="5"/>
@@ -5047,10 +5004,10 @@
       <c r="S4" s="5"/>
       <c r="T4" s="5"/>
       <c r="U4" s="5"/>
-      <c r="V4" s="86"/>
+      <c r="V4" s="88"/>
       <c r="AC4" s="37"/>
       <c r="AD4" s="6" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AO4" s="27">
         <v>0</v>
@@ -5058,92 +5015,92 @@
     </row>
     <row r="5" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B5" s="41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C5" s="48" t="s">
-        <v>60</v>
-      </c>
-      <c r="D5" s="87">
+        <v>61</v>
+      </c>
+      <c r="D5" s="89">
         <f>[2]EB1!D16</f>
         <v>0</v>
       </c>
-      <c r="E5" s="87">
+      <c r="E5" s="89">
         <f>[2]EB1!E16</f>
         <v>0</v>
       </c>
-      <c r="F5" s="87">
+      <c r="F5" s="89">
         <f>[2]EB1!F16</f>
         <v>0</v>
       </c>
-      <c r="G5" s="87">
+      <c r="G5" s="89">
         <f>[2]EB1!G16</f>
         <v>0</v>
       </c>
-      <c r="H5" s="87">
+      <c r="H5" s="89">
         <f>[2]EB1!H16</f>
         <v>0</v>
       </c>
-      <c r="I5" s="87">
+      <c r="I5" s="89">
         <f>[2]EB1!I16</f>
         <v>8.7784635600000005</v>
       </c>
-      <c r="J5" s="87">
+      <c r="J5" s="89">
         <f>[2]EB1!J16</f>
         <v>0</v>
       </c>
-      <c r="K5" s="87">
+      <c r="K5" s="89">
         <f>[2]EB1!K16</f>
         <v>0</v>
       </c>
-      <c r="L5" s="87">
+      <c r="L5" s="89">
         <f>[2]EB1!L16</f>
         <v>0</v>
       </c>
-      <c r="M5" s="87">
+      <c r="M5" s="89">
         <f>[2]EB1!M16</f>
         <v>0</v>
       </c>
-      <c r="N5" s="88">
+      <c r="N5" s="90">
         <f>[2]EB1!N16</f>
         <v>0</v>
       </c>
-      <c r="O5" s="87">
+      <c r="O5" s="89">
         <f>[2]EB1!O16</f>
         <v>29.606118840000001</v>
       </c>
-      <c r="P5" s="87">
+      <c r="P5" s="89">
         <f>[2]EB1!P16</f>
         <v>0</v>
       </c>
-      <c r="Q5" s="87">
+      <c r="Q5" s="89">
         <f>[2]EB1!Q16</f>
         <v>0</v>
       </c>
-      <c r="R5" s="87">
+      <c r="R5" s="89">
         <f>[2]EB1!R16</f>
         <v>0</v>
       </c>
-      <c r="S5" s="87">
+      <c r="S5" s="89">
         <f>[2]EB1!S16</f>
         <v>0</v>
       </c>
-      <c r="T5" s="87">
+      <c r="T5" s="89">
         <f>[2]EB1!T16</f>
         <v>0</v>
       </c>
-      <c r="U5" s="87">
+      <c r="U5" s="89">
         <f>[2]EB1!U16</f>
         <v>15.231997080000001</v>
       </c>
-      <c r="V5" s="89">
+      <c r="V5" s="91">
         <f>SUM(D5:U5)</f>
         <v>53.616579479999999</v>
       </c>
       <c r="AC5" s="41" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="AD5" s="51" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="AE5" s="63">
         <v>1</v>
@@ -5193,92 +5150,92 @@
     </row>
     <row r="6" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B6" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C6" s="49" t="s">
-        <v>62</v>
-      </c>
-      <c r="D6" s="87">
+        <v>63</v>
+      </c>
+      <c r="D6" s="89">
         <f>[2]EB1!D17</f>
         <v>0</v>
       </c>
-      <c r="E6" s="87">
+      <c r="E6" s="89">
         <f>[2]EB1!E17</f>
         <v>0</v>
       </c>
-      <c r="F6" s="87">
+      <c r="F6" s="89">
         <f>[2]EB1!F17</f>
         <v>0</v>
       </c>
-      <c r="G6" s="87">
+      <c r="G6" s="89">
         <f>[2]EB1!G17</f>
         <v>0</v>
       </c>
-      <c r="H6" s="87">
+      <c r="H6" s="89">
         <f>[2]EB1!H17</f>
         <v>0</v>
       </c>
-      <c r="I6" s="87">
+      <c r="I6" s="89">
         <f>[2]EB1!I17</f>
         <v>5.3591040000000003</v>
       </c>
-      <c r="J6" s="87">
+      <c r="J6" s="89">
         <f>[2]EB1!J17</f>
         <v>0</v>
       </c>
-      <c r="K6" s="87">
+      <c r="K6" s="89">
         <f>[2]EB1!K17</f>
         <v>0</v>
       </c>
-      <c r="L6" s="87">
+      <c r="L6" s="89">
         <f>[2]EB1!L17</f>
         <v>0</v>
       </c>
-      <c r="M6" s="87">
+      <c r="M6" s="89">
         <f>[2]EB1!M17</f>
         <v>2.0264112000000001E-2</v>
       </c>
-      <c r="N6" s="88">
+      <c r="N6" s="90">
         <f>[2]EB1!N17</f>
         <v>0</v>
       </c>
-      <c r="O6" s="87">
+      <c r="O6" s="89">
         <f>[2]EB1!O17</f>
         <v>0</v>
       </c>
-      <c r="P6" s="87">
+      <c r="P6" s="89">
         <f>[2]EB1!P17</f>
         <v>0</v>
       </c>
-      <c r="Q6" s="87">
+      <c r="Q6" s="89">
         <f>[2]EB1!Q17</f>
         <v>0</v>
       </c>
-      <c r="R6" s="87">
+      <c r="R6" s="89">
         <f>[2]EB1!R17</f>
         <v>0</v>
       </c>
-      <c r="S6" s="87">
+      <c r="S6" s="89">
         <f>[2]EB1!S17</f>
         <v>0</v>
       </c>
-      <c r="T6" s="87">
+      <c r="T6" s="89">
         <f>[2]EB1!T17</f>
         <v>0</v>
       </c>
-      <c r="U6" s="87">
+      <c r="U6" s="89">
         <f>[2]EB1!U17</f>
         <v>11.973410640000001</v>
       </c>
-      <c r="V6" s="89">
+      <c r="V6" s="91">
         <f t="shared" ref="V6:V12" si="0">SUM(D6:U6)</f>
         <v>17.352778751999999</v>
       </c>
       <c r="AC6" s="41" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="AD6" s="52" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AE6" s="66">
         <v>1</v>
@@ -5328,93 +5285,93 @@
     </row>
     <row r="7" spans="2:45" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B7" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C7" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="D7" s="121">
+        <v>65</v>
+      </c>
+      <c r="D7" s="123">
         <f>[2]EB1!D18</f>
         <v>20.32984476</v>
       </c>
-      <c r="E7" s="121">
+      <c r="E7" s="123">
         <f>[2]EB1!E18</f>
         <v>0</v>
       </c>
-      <c r="F7" s="121">
+      <c r="F7" s="123">
         <f>[2]EB1!F18</f>
         <v>0</v>
       </c>
-      <c r="G7" s="121">
+      <c r="G7" s="123">
         <f>[2]EB1!G18</f>
         <v>9.3960165599999996</v>
       </c>
-      <c r="H7" s="121">
+      <c r="H7" s="123">
         <f>[2]EB1!H18</f>
         <v>0</v>
       </c>
-      <c r="I7" s="121">
+      <c r="I7" s="123">
         <f>[2]EB1!I18</f>
         <v>2.8470240000000004E-2</v>
       </c>
-      <c r="J7" s="121">
+      <c r="J7" s="123">
         <f>[2]EB1!J18</f>
         <v>0</v>
       </c>
-      <c r="K7" s="121">
+      <c r="K7" s="123">
         <f>[2]EB1!K18</f>
         <v>0</v>
       </c>
-      <c r="L7" s="121">
+      <c r="L7" s="123">
         <f>[2]EB1!L18</f>
         <v>5.0660280000000002E-2</v>
       </c>
-      <c r="M7" s="121">
+      <c r="M7" s="123">
         <f>[2]EB1!M18</f>
         <v>0</v>
       </c>
-      <c r="N7" s="121">
+      <c r="N7" s="123">
         <f>[2]EB1!N18</f>
         <v>0</v>
       </c>
-      <c r="O7" s="121">
+      <c r="O7" s="123">
         <f>[2]EB1!O18</f>
         <v>60.016103280000003</v>
       </c>
-      <c r="P7" s="121">
+      <c r="P7" s="123">
         <f>[2]EB1!P18</f>
         <v>0</v>
       </c>
-      <c r="Q7" s="121">
+      <c r="Q7" s="123">
         <f>[2]EB1!Q18</f>
         <v>0</v>
       </c>
-      <c r="R7" s="121">
+      <c r="R7" s="123">
         <f>[2]EB1!R18</f>
         <v>0</v>
       </c>
-      <c r="S7" s="122">
+      <c r="S7" s="124">
         <f>[2]EB1!S18</f>
         <v>0</v>
       </c>
-      <c r="T7" s="122">
+      <c r="T7" s="124">
         <f>[2]EB1!T18</f>
         <v>0</v>
       </c>
-      <c r="U7" s="121">
+      <c r="U7" s="123">
         <f>[2]EB1!U18</f>
         <v>15.341691240000001</v>
       </c>
-      <c r="V7" s="142">
+      <c r="V7" s="91">
         <f>SUM(D7:U7)</f>
         <v>105.16278636</v>
       </c>
       <c r="X7" s="7"/>
       <c r="AC7" s="41" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AD7" s="52" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AE7" s="70">
         <v>1</v>
@@ -5458,98 +5415,98 @@
       <c r="AR7" s="67">
         <v>0.5</v>
       </c>
-      <c r="AS7" s="96">
+      <c r="AS7" s="98">
         <v>0.44</v>
       </c>
     </row>
     <row r="8" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B8" s="41" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>66</v>
-      </c>
-      <c r="D8" s="87">
+        <v>67</v>
+      </c>
+      <c r="D8" s="89">
         <f>[2]EB1!D19</f>
         <v>0</v>
       </c>
-      <c r="E8" s="87">
+      <c r="E8" s="89">
         <f>[2]EB1!E19</f>
         <v>0</v>
       </c>
-      <c r="F8" s="87">
+      <c r="F8" s="89">
         <f>[2]EB1!F19</f>
         <v>0</v>
       </c>
-      <c r="G8" s="87">
+      <c r="G8" s="89">
         <f>[2]EB1!G19</f>
         <v>8.9932464000000003</v>
       </c>
-      <c r="H8" s="87">
+      <c r="H8" s="89">
         <f>[2]EB1!H19</f>
         <v>0</v>
       </c>
-      <c r="I8" s="87">
+      <c r="I8" s="89">
         <f>[2]EB1!I19</f>
         <v>0</v>
       </c>
-      <c r="J8" s="87">
+      <c r="J8" s="89">
         <f>[2]EB1!J19</f>
         <v>0</v>
       </c>
-      <c r="K8" s="87">
+      <c r="K8" s="89">
         <f>[2]EB1!K19</f>
         <v>0</v>
       </c>
-      <c r="L8" s="87">
+      <c r="L8" s="89">
         <f>[2]EB1!L19</f>
         <v>0</v>
       </c>
-      <c r="M8" s="87">
+      <c r="M8" s="89">
         <f>[2]EB1!M19</f>
         <v>0</v>
       </c>
-      <c r="N8" s="88">
+      <c r="N8" s="90">
         <f>[2]EB1!N19</f>
         <v>0</v>
       </c>
-      <c r="O8" s="87">
+      <c r="O8" s="89">
         <f>[2]EB1!O19</f>
         <v>0</v>
       </c>
-      <c r="P8" s="87">
+      <c r="P8" s="89">
         <f>[2]EB1!P19</f>
         <v>0</v>
       </c>
-      <c r="Q8" s="87">
+      <c r="Q8" s="89">
         <f>[2]EB1!Q19</f>
         <v>0</v>
       </c>
-      <c r="R8" s="87">
+      <c r="R8" s="89">
         <f>[2]EB1!R19</f>
         <v>0</v>
       </c>
-      <c r="S8" s="87">
+      <c r="S8" s="89">
         <f>[2]EB1!S19</f>
         <v>4.1868000000000006E-5</v>
       </c>
-      <c r="T8" s="87">
+      <c r="T8" s="89">
         <f>[2]EB1!T19</f>
         <v>0</v>
       </c>
-      <c r="U8" s="87">
+      <c r="U8" s="89">
         <f>[2]EB1!U19</f>
         <v>0</v>
       </c>
-      <c r="V8" s="89">
+      <c r="V8" s="91">
         <f t="shared" si="0"/>
         <v>8.9932882680000006</v>
       </c>
       <c r="AC8" s="41" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD8" s="52" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE8" s="66">
         <v>1</v>
@@ -5599,92 +5556,92 @@
     </row>
     <row r="9" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B9" s="41" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C9" s="49" t="s">
-        <v>68</v>
-      </c>
-      <c r="D9" s="87">
+        <v>69</v>
+      </c>
+      <c r="D9" s="89">
         <f>[2]EB1!D20</f>
         <v>0</v>
       </c>
-      <c r="E9" s="87">
+      <c r="E9" s="89">
         <f>[2]EB1!E20</f>
         <v>0</v>
       </c>
-      <c r="F9" s="87">
+      <c r="F9" s="89">
         <f>[2]EB1!F20</f>
         <v>0</v>
       </c>
-      <c r="G9" s="87">
+      <c r="G9" s="89">
         <f>[2]EB1!G20</f>
         <v>59.234009040000004</v>
       </c>
-      <c r="H9" s="87">
+      <c r="H9" s="89">
         <f>[2]EB1!H20</f>
         <v>2.9927246400000005</v>
       </c>
-      <c r="I9" s="87">
+      <c r="I9" s="89">
         <f>[2]EB1!I20</f>
         <v>1.2346873199999999</v>
       </c>
-      <c r="J9" s="87">
+      <c r="J9" s="89">
         <f>[2]EB1!J20</f>
         <v>28.510014600000005</v>
       </c>
-      <c r="K9" s="87">
+      <c r="K9" s="89">
         <f>[2]EB1!K20</f>
         <v>0</v>
       </c>
-      <c r="L9" s="87">
+      <c r="L9" s="89">
         <f>[2]EB1!L20</f>
         <v>1.2556213199999999</v>
       </c>
-      <c r="M9" s="87">
+      <c r="M9" s="89">
         <f>[2]EB1!M20</f>
         <v>8.1692841600000001</v>
       </c>
-      <c r="N9" s="88">
+      <c r="N9" s="90">
         <f>[2]EB1!N20</f>
         <v>0</v>
       </c>
-      <c r="O9" s="87">
+      <c r="O9" s="89">
         <f>[2]EB1!O20</f>
         <v>0</v>
       </c>
-      <c r="P9" s="87">
+      <c r="P9" s="89">
         <f>[2]EB1!P20</f>
         <v>0</v>
       </c>
-      <c r="Q9" s="87">
+      <c r="Q9" s="89">
         <f>[2]EB1!Q20</f>
         <v>0</v>
       </c>
-      <c r="R9" s="87">
+      <c r="R9" s="89">
         <f>[2]EB1!R20</f>
         <v>0</v>
       </c>
-      <c r="S9" s="87">
+      <c r="S9" s="89">
         <f>[2]EB1!S20</f>
         <v>0</v>
       </c>
-      <c r="T9" s="87">
+      <c r="T9" s="89">
         <f>[2]EB1!T20</f>
         <v>0</v>
       </c>
-      <c r="U9" s="87">
+      <c r="U9" s="89">
         <f>[2]EB1!U20</f>
         <v>0</v>
       </c>
-      <c r="V9" s="89">
+      <c r="V9" s="91">
         <f t="shared" si="0"/>
         <v>101.39634108000001</v>
       </c>
       <c r="AC9" s="41" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AD9" s="52" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AE9" s="66">
         <v>1</v>
@@ -5734,10 +5691,10 @@
     </row>
     <row r="10" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B10" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" s="50" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D10" s="43">
         <f>[2]EB1!D21</f>
@@ -5811,15 +5768,15 @@
         <f>[2]EB1!U21</f>
         <v>0</v>
       </c>
-      <c r="V10" s="90">
+      <c r="V10" s="92">
         <f t="shared" si="0"/>
         <v>9.4588185599999992</v>
       </c>
       <c r="AC10" s="41" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AD10" s="53" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AE10" s="61">
         <v>1</v>
@@ -5869,92 +5826,92 @@
     </row>
     <row r="11" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B11" s="41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C11" s="49" t="s">
-        <v>71</v>
-      </c>
-      <c r="D11" s="87">
+        <v>72</v>
+      </c>
+      <c r="D11" s="89">
         <f>[2]EB1!D22</f>
         <v>0</v>
       </c>
-      <c r="E11" s="87">
+      <c r="E11" s="89">
         <f>[2]EB1!E22</f>
         <v>0</v>
       </c>
-      <c r="F11" s="87">
+      <c r="F11" s="89">
         <f>[2]EB1!F22</f>
         <v>0</v>
       </c>
-      <c r="G11" s="87">
+      <c r="G11" s="89">
         <f>[2]EB1!G22</f>
         <v>0</v>
       </c>
-      <c r="H11" s="87">
+      <c r="H11" s="89">
         <f>[2]EB1!H22</f>
         <v>0</v>
       </c>
-      <c r="I11" s="87">
+      <c r="I11" s="89">
         <f>[2]EB1!I22</f>
         <v>0</v>
       </c>
-      <c r="J11" s="87">
+      <c r="J11" s="89">
         <f>[2]EB1!J22</f>
         <v>0</v>
       </c>
-      <c r="K11" s="87">
+      <c r="K11" s="89">
         <f>[2]EB1!K22</f>
         <v>0</v>
       </c>
-      <c r="L11" s="87">
+      <c r="L11" s="89">
         <f>[2]EB1!L22</f>
         <v>0</v>
       </c>
-      <c r="M11" s="87">
+      <c r="M11" s="89">
         <f>[2]EB1!M22</f>
         <v>0</v>
       </c>
-      <c r="N11" s="88">
+      <c r="N11" s="90">
         <f>[2]EB1!N22</f>
         <v>0</v>
       </c>
-      <c r="O11" s="87">
+      <c r="O11" s="89">
         <f>[2]EB1!O22</f>
         <v>0</v>
       </c>
-      <c r="P11" s="87">
+      <c r="P11" s="89">
         <f>[2]EB1!P22</f>
         <v>0</v>
       </c>
-      <c r="Q11" s="87">
+      <c r="Q11" s="89">
         <f>[2]EB1!Q22</f>
         <v>0</v>
       </c>
-      <c r="R11" s="87">
+      <c r="R11" s="89">
         <f>[2]EB1!R22</f>
         <v>0</v>
       </c>
-      <c r="S11" s="87">
+      <c r="S11" s="89">
         <f>[2]EB1!S22</f>
         <v>0</v>
       </c>
-      <c r="T11" s="87">
+      <c r="T11" s="89">
         <f>[2]EB1!T22</f>
         <v>0</v>
       </c>
-      <c r="U11" s="87">
+      <c r="U11" s="89">
         <f>[2]EB1!U22</f>
         <v>0</v>
       </c>
-      <c r="V11" s="89">
+      <c r="V11" s="91">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC11" s="41" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AD11" s="52" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AE11" s="66">
         <v>1</v>
@@ -6004,52 +5961,52 @@
     </row>
     <row r="12" spans="2:45" x14ac:dyDescent="0.25">
       <c r="B12" s="41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C12" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="D12" s="87">
+        <v>73</v>
+      </c>
+      <c r="D12" s="89">
         <f>[2]EB1!D23</f>
         <v>0</v>
       </c>
-      <c r="E12" s="87">
+      <c r="E12" s="89">
         <f>[2]EB1!E23</f>
         <v>0</v>
       </c>
-      <c r="F12" s="87">
+      <c r="F12" s="89">
         <f>[2]EB1!F23</f>
         <v>0</v>
       </c>
-      <c r="G12" s="87">
+      <c r="G12" s="89">
         <f>[2]EB1!G23</f>
         <v>0</v>
       </c>
-      <c r="H12" s="87">
+      <c r="H12" s="89">
         <f>[2]EB1!H23</f>
         <v>0</v>
       </c>
-      <c r="I12" s="87">
+      <c r="I12" s="89">
         <f>[2]EB1!I23</f>
         <v>0</v>
       </c>
-      <c r="J12" s="87">
+      <c r="J12" s="89">
         <f>[2]EB1!J23</f>
         <v>0</v>
       </c>
-      <c r="K12" s="87">
+      <c r="K12" s="89">
         <f>[2]EB1!K23</f>
         <v>0</v>
       </c>
-      <c r="L12" s="87">
+      <c r="L12" s="89">
         <f>[2]EB1!L23</f>
         <v>0</v>
       </c>
-      <c r="M12" s="87">
+      <c r="M12" s="89">
         <f>[2]EB1!M23</f>
         <v>0</v>
       </c>
-      <c r="N12" s="88">
+      <c r="N12" s="90">
         <f>[2]EB1!N23</f>
         <v>0</v>
       </c>
@@ -6069,27 +6026,27 @@
         <f>[2]EB1!R23</f>
         <v>0</v>
       </c>
-      <c r="S12" s="87">
+      <c r="S12" s="89">
         <f>[2]EB1!S23</f>
         <v>0</v>
       </c>
-      <c r="T12" s="87">
+      <c r="T12" s="89">
         <f>[2]EB1!T23</f>
         <v>0</v>
       </c>
-      <c r="U12" s="87">
+      <c r="U12" s="89">
         <f>[2]EB1!U23</f>
         <v>0</v>
       </c>
-      <c r="V12" s="89">
+      <c r="V12" s="91">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="AC12" s="41" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="AD12" s="52" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AE12" s="66">
         <v>1</v>
@@ -6138,11 +6095,11 @@
       </c>
     </row>
     <row r="13" spans="2:45" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B13" s="84" t="s">
-        <v>89</v>
+      <c r="B13" s="86" t="s">
+        <v>90</v>
       </c>
       <c r="C13" s="47" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="D13" s="45">
         <f t="shared" ref="D13:V13" si="1">SUM(D5:D12)</f>
@@ -6209,7 +6166,7 @@
         <v>295.9805925</v>
       </c>
       <c r="AC13" s="41" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="AD13" s="58"/>
       <c r="AE13" s="58"/>
@@ -6252,7 +6209,7 @@
     </row>
     <row r="16" spans="2:45" ht="14.4" x14ac:dyDescent="0.3">
       <c r="C16" s="44" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D16" s="44"/>
       <c r="E16" s="44"/>
@@ -6282,271 +6239,271 @@
     </row>
     <row r="19" spans="2:24" ht="39.6" x14ac:dyDescent="0.25">
       <c r="B19" s="23" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" s="124" t="s">
-        <v>114</v>
-      </c>
-      <c r="D19" s="125" t="s">
-        <v>51</v>
-      </c>
-      <c r="E19" s="126" t="s">
+        <v>102</v>
+      </c>
+      <c r="C19" s="126" t="s">
+        <v>115</v>
+      </c>
+      <c r="D19" s="127" t="s">
         <v>52</v>
       </c>
-      <c r="F19" s="126" t="s">
-        <v>121</v>
-      </c>
-      <c r="G19" s="126" t="s">
+      <c r="E19" s="128" t="s">
+        <v>53</v>
+      </c>
+      <c r="F19" s="128" t="s">
+        <v>122</v>
+      </c>
+      <c r="G19" s="128" t="s">
+        <v>135</v>
+      </c>
+      <c r="H19" s="128" t="s">
+        <v>132</v>
+      </c>
+      <c r="I19" s="128" t="s">
+        <v>125</v>
+      </c>
+      <c r="J19" s="128" t="s">
+        <v>133</v>
+      </c>
+      <c r="K19" s="128" t="s">
         <v>134</v>
       </c>
-      <c r="H19" s="126" t="s">
+      <c r="L19" s="128" t="s">
+        <v>130</v>
+      </c>
+      <c r="M19" s="128" t="s">
         <v>131</v>
       </c>
-      <c r="I19" s="126" t="s">
-        <v>124</v>
-      </c>
-      <c r="J19" s="126" t="s">
-        <v>132</v>
-      </c>
-      <c r="K19" s="126" t="s">
-        <v>133</v>
-      </c>
-      <c r="L19" s="126" t="s">
-        <v>129</v>
-      </c>
-      <c r="M19" s="126" t="s">
-        <v>130</v>
-      </c>
-      <c r="N19" s="126" t="s">
-        <v>53</v>
-      </c>
-      <c r="O19" s="126" t="s">
-        <v>152</v>
-      </c>
-      <c r="P19" s="126" t="s">
-        <v>153</v>
-      </c>
-      <c r="Q19" s="126" t="s">
-        <v>154</v>
-      </c>
-      <c r="R19" s="126" t="s">
+      <c r="N19" s="128" t="s">
+        <v>54</v>
+      </c>
+      <c r="O19" s="128" t="s">
         <v>155</v>
       </c>
-      <c r="S19" s="126" t="s">
-        <v>55</v>
-      </c>
-      <c r="T19" s="126" t="s">
+      <c r="P19" s="128" t="s">
+        <v>156</v>
+      </c>
+      <c r="Q19" s="128" t="s">
+        <v>157</v>
+      </c>
+      <c r="R19" s="128" t="s">
+        <v>158</v>
+      </c>
+      <c r="S19" s="128" t="s">
         <v>56</v>
       </c>
-      <c r="U19" s="126" t="s">
-        <v>88</v>
-      </c>
-      <c r="V19" s="127" t="s">
+      <c r="T19" s="128" t="s">
         <v>57</v>
       </c>
+      <c r="U19" s="128" t="s">
+        <v>89</v>
+      </c>
+      <c r="V19" s="129" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="20" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B20" s="95" t="s">
-        <v>63</v>
-      </c>
-      <c r="C20" s="92" t="s">
-        <v>162</v>
-      </c>
-      <c r="D20" s="116">
+      <c r="B20" s="97" t="s">
+        <v>64</v>
+      </c>
+      <c r="C20" s="94" t="s">
+        <v>165</v>
+      </c>
+      <c r="D20" s="118">
         <v>1</v>
       </c>
-      <c r="E20" s="123"/>
-      <c r="F20" s="123"/>
-      <c r="G20" s="123"/>
-      <c r="H20" s="123"/>
-      <c r="I20" s="123"/>
-      <c r="J20" s="123"/>
-      <c r="K20" s="123"/>
-      <c r="L20" s="115">
+      <c r="E20" s="125"/>
+      <c r="F20" s="125"/>
+      <c r="G20" s="117">
+        <v>0.8</v>
+      </c>
+      <c r="H20" s="125"/>
+      <c r="I20" s="125"/>
+      <c r="J20" s="125"/>
+      <c r="K20" s="125"/>
+      <c r="L20" s="117">
         <v>1</v>
       </c>
-      <c r="M20" s="123"/>
-      <c r="N20" s="123"/>
-      <c r="O20" s="115">
+      <c r="M20" s="125"/>
+      <c r="N20" s="125"/>
+      <c r="O20" s="117">
         <v>1</v>
       </c>
-      <c r="P20" s="123"/>
-      <c r="Q20" s="123"/>
-      <c r="R20" s="123"/>
-      <c r="S20" s="123"/>
-      <c r="T20" s="123"/>
-      <c r="U20" s="123"/>
+      <c r="P20" s="125"/>
+      <c r="Q20" s="125"/>
+      <c r="R20" s="125"/>
+      <c r="S20" s="125"/>
+      <c r="T20" s="125"/>
+      <c r="U20" s="125"/>
       <c r="V20" s="49"/>
-      <c r="X20" s="114" t="s">
-        <v>164</v>
+      <c r="X20" s="116" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="21" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B21" s="95" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="92" t="s">
-        <v>179</v>
+      <c r="B21" s="97" t="s">
+        <v>64</v>
+      </c>
+      <c r="C21" s="94" t="s">
+        <v>182</v>
       </c>
       <c r="D21" s="52"/>
-      <c r="E21" s="123"/>
-      <c r="F21" s="123"/>
-      <c r="G21" s="115">
-        <v>1</v>
-      </c>
-      <c r="H21" s="123"/>
-      <c r="I21" s="115">
-        <v>1</v>
-      </c>
-      <c r="J21" s="123"/>
-      <c r="K21" s="123"/>
-      <c r="L21" s="123"/>
-      <c r="M21" s="123"/>
-      <c r="N21" s="123"/>
-      <c r="O21" s="123"/>
-      <c r="P21" s="123"/>
-      <c r="Q21" s="123"/>
-      <c r="R21" s="123"/>
-      <c r="S21" s="123"/>
-      <c r="T21" s="123"/>
-      <c r="U21" s="115">
+      <c r="E21" s="125"/>
+      <c r="F21" s="125"/>
+      <c r="G21" s="117">
+        <v>0.2</v>
+      </c>
+      <c r="H21" s="125"/>
+      <c r="I21" s="125"/>
+      <c r="J21" s="125"/>
+      <c r="K21" s="125"/>
+      <c r="L21" s="125"/>
+      <c r="M21" s="125"/>
+      <c r="N21" s="125"/>
+      <c r="O21" s="125"/>
+      <c r="P21" s="125"/>
+      <c r="Q21" s="125"/>
+      <c r="R21" s="125"/>
+      <c r="S21" s="125"/>
+      <c r="T21" s="125"/>
+      <c r="U21" s="117">
         <v>0.25</v>
       </c>
       <c r="V21" s="49"/>
-      <c r="X21" s="114" t="s">
-        <v>180</v>
+      <c r="X21" s="116" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="22" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B22" s="95" t="s">
-        <v>63</v>
-      </c>
-      <c r="C22" s="92" t="s">
-        <v>163</v>
+      <c r="B22" s="97" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" s="94" t="s">
+        <v>166</v>
       </c>
       <c r="D22" s="52"/>
-      <c r="E22" s="123"/>
-      <c r="F22" s="123"/>
-      <c r="G22" s="123"/>
-      <c r="H22" s="123"/>
-      <c r="I22" s="123"/>
-      <c r="J22" s="123"/>
-      <c r="K22" s="123"/>
-      <c r="L22" s="123"/>
-      <c r="M22" s="123"/>
-      <c r="N22" s="123"/>
-      <c r="O22" s="123"/>
-      <c r="P22" s="123"/>
-      <c r="Q22" s="123"/>
-      <c r="R22" s="123"/>
-      <c r="S22" s="123"/>
-      <c r="T22" s="123"/>
-      <c r="U22" s="115">
+      <c r="E22" s="125"/>
+      <c r="F22" s="125"/>
+      <c r="G22" s="125"/>
+      <c r="H22" s="125"/>
+      <c r="I22" s="125"/>
+      <c r="J22" s="125"/>
+      <c r="K22" s="125"/>
+      <c r="L22" s="125"/>
+      <c r="M22" s="125"/>
+      <c r="N22" s="125"/>
+      <c r="O22" s="125"/>
+      <c r="P22" s="125"/>
+      <c r="Q22" s="125"/>
+      <c r="R22" s="125"/>
+      <c r="S22" s="125"/>
+      <c r="T22" s="125"/>
+      <c r="U22" s="117">
         <v>0.2</v>
       </c>
       <c r="V22" s="49"/>
-      <c r="X22" s="114" t="s">
-        <v>165</v>
+      <c r="X22" s="116" t="s">
+        <v>168</v>
       </c>
     </row>
     <row r="23" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B23" s="95" t="s">
-        <v>63</v>
-      </c>
-      <c r="C23" s="92" t="s">
-        <v>166</v>
+      <c r="B23" s="97" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="94" t="s">
+        <v>169</v>
       </c>
       <c r="D23" s="52"/>
-      <c r="E23" s="123"/>
-      <c r="F23" s="123"/>
-      <c r="G23" s="123"/>
-      <c r="H23" s="123"/>
-      <c r="I23" s="123"/>
-      <c r="J23" s="123"/>
-      <c r="K23" s="123"/>
-      <c r="L23" s="123"/>
-      <c r="M23" s="123"/>
-      <c r="N23" s="123"/>
-      <c r="O23" s="123"/>
-      <c r="P23" s="123"/>
-      <c r="Q23" s="123"/>
-      <c r="R23" s="123"/>
-      <c r="S23" s="123"/>
-      <c r="T23" s="123"/>
-      <c r="U23" s="115">
+      <c r="E23" s="125"/>
+      <c r="F23" s="125"/>
+      <c r="G23" s="125"/>
+      <c r="H23" s="125"/>
+      <c r="I23" s="125"/>
+      <c r="J23" s="125"/>
+      <c r="K23" s="125"/>
+      <c r="L23" s="125"/>
+      <c r="M23" s="125"/>
+      <c r="N23" s="125"/>
+      <c r="O23" s="125"/>
+      <c r="P23" s="125"/>
+      <c r="Q23" s="125"/>
+      <c r="R23" s="125"/>
+      <c r="S23" s="125"/>
+      <c r="T23" s="125"/>
+      <c r="U23" s="117">
         <v>0.25</v>
       </c>
       <c r="V23" s="49"/>
       <c r="X23" s="50" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
     </row>
     <row r="24" spans="2:24" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="B24" s="95" t="s">
-        <v>63</v>
-      </c>
-      <c r="C24" s="92" t="s">
-        <v>168</v>
+      <c r="B24" s="97" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="94" t="s">
+        <v>171</v>
       </c>
       <c r="D24" s="52"/>
-      <c r="E24" s="123"/>
-      <c r="F24" s="123"/>
-      <c r="G24" s="123"/>
-      <c r="H24" s="123"/>
-      <c r="I24" s="123"/>
-      <c r="J24" s="123"/>
-      <c r="K24" s="123"/>
-      <c r="L24" s="123"/>
-      <c r="M24" s="123"/>
-      <c r="N24" s="123"/>
-      <c r="O24" s="123"/>
-      <c r="P24" s="123"/>
-      <c r="Q24" s="123"/>
-      <c r="R24" s="123"/>
-      <c r="S24" s="123"/>
-      <c r="T24" s="123"/>
-      <c r="U24" s="115">
+      <c r="E24" s="125"/>
+      <c r="F24" s="125"/>
+      <c r="G24" s="125"/>
+      <c r="H24" s="125"/>
+      <c r="I24" s="125"/>
+      <c r="J24" s="125"/>
+      <c r="K24" s="125"/>
+      <c r="L24" s="125"/>
+      <c r="M24" s="125"/>
+      <c r="N24" s="125"/>
+      <c r="O24" s="125"/>
+      <c r="P24" s="125"/>
+      <c r="Q24" s="125"/>
+      <c r="R24" s="125"/>
+      <c r="S24" s="125"/>
+      <c r="T24" s="125"/>
+      <c r="U24" s="117">
         <v>0.3</v>
       </c>
       <c r="V24" s="49"/>
-      <c r="X24" s="114" t="s">
-        <v>169</v>
+      <c r="X24" s="116" t="s">
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="2:24" x14ac:dyDescent="0.25">
       <c r="C27" s="54" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D27" s="56" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E27" s="55" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
     </row>
     <row r="28" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B28" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="C28" s="93" t="s">
+        <v>116</v>
+      </c>
+      <c r="C28" s="95" t="s">
+        <v>109</v>
+      </c>
+      <c r="D28" s="95" t="s">
+        <v>110</v>
+      </c>
+      <c r="E28" s="96" t="s">
         <v>108</v>
-      </c>
-      <c r="D28" s="93" t="s">
-        <v>109</v>
-      </c>
-      <c r="E28" s="94" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="29" spans="2:24" x14ac:dyDescent="0.25">
       <c r="B29" s="41" t="s">
-        <v>63</v>
-      </c>
-      <c r="C29" s="102">
+        <v>64</v>
+      </c>
+      <c r="C29" s="104">
         <v>1</v>
       </c>
-      <c r="D29" s="103"/>
-      <c r="E29" s="104"/>
+      <c r="D29" s="105"/>
+      <c r="E29" s="106"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6567,26 +6524,26 @@
   <sheetData>
     <row r="2" spans="2:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B2" s="79" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
     </row>
     <row r="4" spans="2:10" ht="17.399999999999999" x14ac:dyDescent="0.3">
-      <c r="E4" s="97"/>
-      <c r="F4" s="97"/>
-      <c r="G4" s="97"/>
-      <c r="H4" s="97"/>
-      <c r="I4" s="97"/>
-      <c r="J4" s="97"/>
+      <c r="E4" s="99"/>
+      <c r="F4" s="99"/>
+      <c r="G4" s="99"/>
+      <c r="H4" s="99"/>
+      <c r="I4" s="99"/>
+      <c r="J4" s="99"/>
     </row>
     <row r="5" spans="2:10" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E5" s="80" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="F5" s="80"/>
       <c r="G5" s="80"/>
       <c r="H5" s="80"/>
-      <c r="I5" s="98"/>
-      <c r="J5" s="98"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="100"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6622,22 +6579,22 @@
   <sheetData>
     <row r="1" spans="2:18" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H1" s="30"/>
     </row>
@@ -6651,7 +6608,7 @@
         <v>Industry</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E2" s="10" t="str">
         <f>'EB1'!Z2</f>
@@ -6662,47 +6619,47 @@
         <v>M$2021</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="H2" s="9"/>
-      <c r="J2" s="105" t="s">
+      <c r="J2" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="K2" s="105"/>
-      <c r="L2" s="106"/>
-      <c r="M2" s="106"/>
-      <c r="N2" s="106"/>
-      <c r="O2" s="106"/>
-      <c r="P2" s="106"/>
-      <c r="Q2" s="106"/>
-      <c r="R2" s="106"/>
+      <c r="K2" s="107"/>
+      <c r="L2" s="108"/>
+      <c r="M2" s="108"/>
+      <c r="N2" s="108"/>
+      <c r="O2" s="108"/>
+      <c r="P2" s="108"/>
+      <c r="Q2" s="108"/>
+      <c r="R2" s="108"/>
     </row>
     <row r="3" spans="2:18" x14ac:dyDescent="0.25">
-      <c r="J3" s="107" t="s">
+      <c r="J3" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="108" t="s">
+      <c r="K3" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="M3" s="107" t="s">
+      <c r="L3" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="M3" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="107" t="s">
+      <c r="N3" s="109" t="s">
         <v>4</v>
       </c>
-      <c r="O3" s="107" t="s">
+      <c r="O3" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="P3" s="107" t="s">
+      <c r="P3" s="109" t="s">
         <v>9</v>
       </c>
-      <c r="Q3" s="107" t="s">
+      <c r="Q3" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="R3" s="107" t="s">
+      <c r="R3" s="109" t="s">
         <v>12</v>
       </c>
     </row>
@@ -6712,31 +6669,31 @@
       <c r="D4" s="9"/>
       <c r="E4" s="9"/>
       <c r="G4" s="9"/>
-      <c r="J4" s="109" t="s">
-        <v>36</v>
-      </c>
-      <c r="K4" s="109" t="s">
+      <c r="J4" s="111" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="L4" s="109" t="s">
+      <c r="L4" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="M4" s="109" t="s">
+      <c r="M4" s="111" t="s">
         <v>27</v>
       </c>
-      <c r="N4" s="109" t="s">
+      <c r="N4" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="109" t="s">
-        <v>39</v>
-      </c>
-      <c r="P4" s="109" t="s">
+      <c r="O4" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="Q4" s="109" t="s">
+      <c r="P4" s="111" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q4" s="111" t="s">
         <v>28</v>
       </c>
-      <c r="R4" s="109" t="s">
+      <c r="R4" s="111" t="s">
         <v>29</v>
       </c>
     </row>
@@ -6745,122 +6702,122 @@
       <c r="F5" s="12"/>
       <c r="G5" s="78"/>
       <c r="H5" s="11"/>
-      <c r="J5" s="110" t="s">
-        <v>73</v>
-      </c>
-      <c r="K5" s="110"/>
-      <c r="L5" s="110" t="str">
+      <c r="J5" s="112" t="s">
+        <v>74</v>
+      </c>
+      <c r="K5" s="112"/>
+      <c r="L5" s="112" t="str">
         <f>$B$2&amp;[3]EB2!$D$2</f>
         <v>INDCOA</v>
       </c>
-      <c r="M5" s="111" t="str">
+      <c r="M5" s="113" t="str">
         <f>$C$2&amp;" "&amp;[3]EB2!$D$3</f>
         <v>Industry Solid Fuels</v>
       </c>
-      <c r="N5" s="110" t="str">
+      <c r="N5" s="112" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O5" s="110"/>
-      <c r="P5" s="110"/>
-      <c r="Q5" s="110"/>
-      <c r="R5" s="110"/>
+      <c r="O5" s="112"/>
+      <c r="P5" s="112"/>
+      <c r="Q5" s="112"/>
+      <c r="R5" s="112"/>
     </row>
     <row r="6" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E6" s="12"/>
       <c r="F6" s="12"/>
       <c r="G6" s="78"/>
       <c r="H6" s="11"/>
-      <c r="J6" s="110"/>
-      <c r="K6" s="110"/>
-      <c r="L6" s="110" t="str">
+      <c r="J6" s="112"/>
+      <c r="K6" s="112"/>
+      <c r="L6" s="112" t="str">
         <f>$B$2&amp;[3]EB2!$E$2</f>
         <v>INDGAS</v>
       </c>
-      <c r="M6" s="111" t="str">
+      <c r="M6" s="113" t="str">
         <f>$C$2&amp;" "&amp;[3]EB2!$E$3</f>
         <v>Industry Natural Gas</v>
       </c>
-      <c r="N6" s="110" t="str">
+      <c r="N6" s="112" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O6" s="110"/>
-      <c r="P6" s="110"/>
-      <c r="Q6" s="110"/>
-      <c r="R6" s="110"/>
+      <c r="O6" s="112"/>
+      <c r="P6" s="112"/>
+      <c r="Q6" s="112"/>
+      <c r="R6" s="112"/>
     </row>
     <row r="7" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E7" s="12"/>
       <c r="F7" s="12"/>
       <c r="G7" s="78"/>
       <c r="H7" s="11"/>
-      <c r="J7" s="110"/>
-      <c r="K7" s="110"/>
-      <c r="L7" s="110" t="str">
+      <c r="J7" s="112"/>
+      <c r="K7" s="112"/>
+      <c r="L7" s="112" t="str">
         <f>$B$2&amp;[3]EB2!$F$2</f>
         <v>INDOIL</v>
       </c>
-      <c r="M7" s="111" t="str">
+      <c r="M7" s="113" t="str">
         <f>$C$2&amp;" "&amp;[3]EB2!$F$3</f>
         <v>Industry Crude Oil</v>
       </c>
-      <c r="N7" s="110" t="str">
+      <c r="N7" s="112" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O7" s="110"/>
-      <c r="P7" s="110"/>
-      <c r="Q7" s="110"/>
-      <c r="R7" s="110"/>
+      <c r="O7" s="112"/>
+      <c r="P7" s="112"/>
+      <c r="Q7" s="112"/>
+      <c r="R7" s="112"/>
     </row>
     <row r="8" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E8" s="12"/>
       <c r="F8" s="12"/>
       <c r="G8" s="78"/>
       <c r="H8" s="11"/>
-      <c r="J8" s="110"/>
-      <c r="K8" s="110"/>
-      <c r="L8" s="110" t="str">
+      <c r="J8" s="112"/>
+      <c r="K8" s="112"/>
+      <c r="L8" s="112" t="str">
         <f>$B$2&amp;[3]EB2!$O$2</f>
         <v>INDBIO</v>
       </c>
-      <c r="M8" s="111" t="str">
+      <c r="M8" s="113" t="str">
         <f>$C$2&amp;" "&amp;[3]EB2!$O$3</f>
         <v>Industry Biomass</v>
       </c>
-      <c r="N8" s="110" t="str">
+      <c r="N8" s="112" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O8" s="110"/>
-      <c r="P8" s="110"/>
-      <c r="Q8" s="110"/>
-      <c r="R8" s="110"/>
+      <c r="O8" s="112"/>
+      <c r="P8" s="112"/>
+      <c r="Q8" s="112"/>
+      <c r="R8" s="112"/>
     </row>
     <row r="9" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E9" s="12"/>
       <c r="F9" s="12"/>
       <c r="G9" s="78"/>
       <c r="H9" s="11"/>
-      <c r="J9" s="110"/>
-      <c r="K9" s="110"/>
-      <c r="L9" s="110" t="str">
+      <c r="J9" s="112"/>
+      <c r="K9" s="112"/>
+      <c r="L9" s="112" t="str">
         <f>$B$2&amp;[3]EB2!$U$2</f>
         <v>INDELC</v>
       </c>
-      <c r="M9" s="111" t="str">
+      <c r="M9" s="113" t="str">
         <f>$C$2&amp;" "&amp;[3]EB2!$U$3</f>
         <v>Industry Electricity</v>
       </c>
-      <c r="N9" s="110" t="str">
+      <c r="N9" s="112" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O9" s="110"/>
-      <c r="P9" s="110"/>
-      <c r="Q9" s="110"/>
-      <c r="R9" s="110"/>
+      <c r="O9" s="112"/>
+      <c r="P9" s="112"/>
+      <c r="Q9" s="112"/>
+      <c r="R9" s="112"/>
     </row>
     <row r="10" spans="2:18" x14ac:dyDescent="0.25">
       <c r="E10" s="12"/>
@@ -6883,17 +6840,17 @@
       </c>
       <c r="E12" s="4"/>
       <c r="F12" s="4"/>
-      <c r="J12" s="105" t="s">
+      <c r="J12" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="K12" s="105"/>
-      <c r="L12" s="110"/>
-      <c r="M12" s="110"/>
-      <c r="N12" s="110"/>
-      <c r="O12" s="110"/>
-      <c r="P12" s="110"/>
-      <c r="Q12" s="110"/>
-      <c r="R12" s="110"/>
+      <c r="K12" s="107"/>
+      <c r="L12" s="112"/>
+      <c r="M12" s="112"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="112"/>
+      <c r="P12" s="112"/>
+      <c r="Q12" s="112"/>
+      <c r="R12" s="112"/>
     </row>
     <row r="13" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B13" s="18" t="s">
@@ -6905,49 +6862,49 @@
       <c r="D13" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="E13" s="83" t="s">
-        <v>137</v>
+      <c r="E13" s="84" t="s">
+        <v>140</v>
       </c>
       <c r="F13" s="81" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G13" s="81" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="H13" s="81" t="s">
-        <v>80</v>
-      </c>
-      <c r="J13" s="107" t="s">
+        <v>81</v>
+      </c>
+      <c r="J13" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="K13" s="108" t="s">
+      <c r="K13" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="L13" s="107" t="s">
+      <c r="L13" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="M13" s="107" t="s">
+      <c r="M13" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="N13" s="107" t="s">
+      <c r="N13" s="109" t="s">
         <v>16</v>
       </c>
-      <c r="O13" s="107" t="s">
+      <c r="O13" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="P13" s="107" t="s">
+      <c r="P13" s="109" t="s">
         <v>18</v>
       </c>
-      <c r="Q13" s="107" t="s">
+      <c r="Q13" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="R13" s="107" t="s">
+      <c r="R13" s="109" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="14" spans="2:18" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B14" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C14" s="16" t="s">
         <v>32</v>
@@ -6956,48 +6913,48 @@
         <v>33</v>
       </c>
       <c r="E14" s="16" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="F14" s="16" t="s">
         <v>34</v>
       </c>
       <c r="G14" s="16" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="H14" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="J14" s="109" t="s">
-        <v>37</v>
-      </c>
-      <c r="K14" s="109" t="s">
+        <v>159</v>
+      </c>
+      <c r="J14" s="111" t="s">
+        <v>38</v>
+      </c>
+      <c r="K14" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="L14" s="109" t="s">
+      <c r="L14" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="109" t="s">
+      <c r="M14" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="N14" s="109" t="s">
+      <c r="N14" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="O14" s="109" t="s">
+      <c r="O14" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="P14" s="109" t="s">
+      <c r="P14" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q14" s="111" t="s">
         <v>42</v>
       </c>
-      <c r="Q14" s="109" t="s">
-        <v>41</v>
-      </c>
-      <c r="R14" s="109" t="s">
+      <c r="R14" s="111" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="15" spans="2:18" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C15" s="15"/>
       <c r="D15" s="15"/>
@@ -7008,19 +6965,19 @@
       </c>
       <c r="G15" s="13"/>
       <c r="H15" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="J15" s="109" t="s">
-        <v>82</v>
-      </c>
-      <c r="K15" s="112"/>
-      <c r="L15" s="112"/>
-      <c r="M15" s="112"/>
-      <c r="N15" s="112"/>
-      <c r="O15" s="112"/>
-      <c r="P15" s="112"/>
-      <c r="Q15" s="112"/>
-      <c r="R15" s="112"/>
+        <v>93</v>
+      </c>
+      <c r="J15" s="111" t="s">
+        <v>83</v>
+      </c>
+      <c r="K15" s="114"/>
+      <c r="L15" s="114"/>
+      <c r="M15" s="114"/>
+      <c r="N15" s="114"/>
+      <c r="O15" s="114"/>
+      <c r="P15" s="114"/>
+      <c r="Q15" s="114"/>
+      <c r="R15" s="114"/>
     </row>
     <row r="16" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B16" t="str">
@@ -7043,29 +7000,29 @@
       <c r="H16" s="75">
         <v>50</v>
       </c>
-      <c r="J16" s="106" t="s">
-        <v>111</v>
-      </c>
-      <c r="K16" s="110"/>
-      <c r="L16" s="110" t="str">
+      <c r="J16" s="108" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="112"/>
+      <c r="L16" s="112" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L5</f>
         <v>FTE-INDCOA</v>
       </c>
-      <c r="M16" s="111" t="str">
+      <c r="M16" s="113" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M5</f>
         <v>Sector Fuel Technology Existing Industry Solid Fuels</v>
       </c>
-      <c r="N16" s="110" t="str">
+      <c r="N16" s="112" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O16" s="110" t="str">
+      <c r="O16" s="112" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="P16" s="110"/>
-      <c r="Q16" s="110"/>
-      <c r="R16" s="110"/>
+      <c r="P16" s="112"/>
+      <c r="Q16" s="112"/>
+      <c r="R16" s="112"/>
     </row>
     <row r="17" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B17" t="str">
@@ -7088,27 +7045,27 @@
       <c r="H17" s="75">
         <v>50</v>
       </c>
-      <c r="J17" s="110"/>
-      <c r="K17" s="110"/>
-      <c r="L17" s="110" t="str">
+      <c r="J17" s="112"/>
+      <c r="K17" s="112"/>
+      <c r="L17" s="112" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L6</f>
         <v>FTE-INDGAS</v>
       </c>
-      <c r="M17" s="111" t="str">
+      <c r="M17" s="113" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M6</f>
         <v>Sector Fuel Technology Existing Industry Natural Gas</v>
       </c>
-      <c r="N17" s="110" t="str">
+      <c r="N17" s="112" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O17" s="110" t="str">
+      <c r="O17" s="112" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="P17" s="110"/>
-      <c r="Q17" s="110"/>
-      <c r="R17" s="110"/>
+      <c r="P17" s="112"/>
+      <c r="Q17" s="112"/>
+      <c r="R17" s="112"/>
     </row>
     <row r="18" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B18" t="str">
@@ -7123,7 +7080,7 @@
         <f>L7</f>
         <v>INDOIL</v>
       </c>
-      <c r="E18" s="113">
+      <c r="E18" s="115">
         <f>-'EB1'!G$7/-SUM('EB1'!$G$7:$M$7)</f>
         <v>0.99164862356943995</v>
       </c>
@@ -7134,104 +7091,104 @@
       <c r="H18" s="75">
         <v>50</v>
       </c>
-      <c r="J18" s="110"/>
-      <c r="K18" s="110"/>
-      <c r="L18" s="110" t="str">
+      <c r="J18" s="112"/>
+      <c r="K18" s="112"/>
+      <c r="L18" s="112" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L7</f>
         <v>FTE-INDOIL</v>
       </c>
-      <c r="M18" s="111" t="str">
+      <c r="M18" s="113" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M7</f>
         <v>Sector Fuel Technology Existing Industry Crude Oil</v>
       </c>
-      <c r="N18" s="110" t="str">
+      <c r="N18" s="112" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O18" s="110" t="str">
+      <c r="O18" s="112" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="P18" s="110"/>
-      <c r="Q18" s="110"/>
-      <c r="R18" s="110"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="112"/>
+      <c r="R18" s="112"/>
     </row>
     <row r="19" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C19" t="str">
         <f>'EB1'!H$2</f>
         <v>KER</v>
       </c>
-      <c r="E19" s="113">
+      <c r="E19" s="115">
         <f>-'EB1'!H$7/-SUM('EB1'!$G$7:$M$7)</f>
         <v>0</v>
       </c>
       <c r="F19" s="12"/>
       <c r="G19" s="74"/>
       <c r="H19" s="75"/>
-      <c r="J19" s="110"/>
-      <c r="K19" s="110"/>
-      <c r="L19" s="110" t="str">
+      <c r="J19" s="112"/>
+      <c r="K19" s="112"/>
+      <c r="L19" s="112" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L8</f>
         <v>FTE-INDBIO</v>
       </c>
-      <c r="M19" s="111" t="str">
+      <c r="M19" s="113" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M8</f>
         <v>Sector Fuel Technology Existing Industry Biomass</v>
       </c>
-      <c r="N19" s="110" t="str">
+      <c r="N19" s="112" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O19" s="110" t="str">
+      <c r="O19" s="112" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="P19" s="110"/>
-      <c r="Q19" s="110"/>
-      <c r="R19" s="110"/>
+      <c r="P19" s="112"/>
+      <c r="Q19" s="112"/>
+      <c r="R19" s="112"/>
     </row>
     <row r="20" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C20" t="str">
         <f>'EB1'!I$2</f>
         <v>LPG</v>
       </c>
-      <c r="E20" s="113">
+      <c r="E20" s="115">
         <f>-'EB1'!I$7/-SUM('EB1'!$G$7:$M$7)</f>
         <v>3.0047280279262957E-3</v>
       </c>
       <c r="F20" s="12"/>
       <c r="G20" s="74"/>
       <c r="H20" s="75"/>
-      <c r="J20" s="110"/>
-      <c r="K20" s="110"/>
-      <c r="L20" s="110" t="str">
+      <c r="J20" s="112"/>
+      <c r="K20" s="112"/>
+      <c r="L20" s="112" t="str">
         <f>"FT"&amp;$G$2&amp;"-"&amp;L9</f>
         <v>FTE-INDELC</v>
       </c>
-      <c r="M20" s="111" t="str">
+      <c r="M20" s="113" t="str">
         <f>$D$2&amp;" Technology"&amp;" "&amp;$G$1&amp;" "&amp;M9</f>
         <v>Sector Fuel Technology Existing Industry Electricity</v>
       </c>
-      <c r="N20" s="110" t="str">
+      <c r="N20" s="112" t="str">
         <f>$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="O20" s="110" t="str">
+      <c r="O20" s="112" t="str">
         <f>$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
-      <c r="P20" s="110" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q20" s="110"/>
-      <c r="R20" s="110"/>
+      <c r="P20" s="112" t="s">
+        <v>147</v>
+      </c>
+      <c r="Q20" s="112"/>
+      <c r="R20" s="112"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.25">
       <c r="C21" t="str">
         <f>'EB1'!J$2</f>
         <v>GSL</v>
       </c>
-      <c r="E21" s="113">
+      <c r="E21" s="115">
         <f>-'EB1'!J$7/-SUM('EB1'!$G$7:$M$7)</f>
         <v>0</v>
       </c>
@@ -7245,7 +7202,7 @@
         <f>'EB1'!K$2</f>
         <v>NAP</v>
       </c>
-      <c r="E22" s="113">
+      <c r="E22" s="115">
         <f>-'EB1'!K$7/-SUM('EB1'!$G$7:$M$7)</f>
         <v>0</v>
       </c>
@@ -7261,7 +7218,7 @@
         <f>'EB1'!L$2</f>
         <v>HFO</v>
       </c>
-      <c r="E23" s="113">
+      <c r="E23" s="115">
         <f>-'EB1'!L$7/-SUM('EB1'!$G$7:$M$7)</f>
         <v>5.3466484026335557E-3</v>
       </c>
@@ -7277,7 +7234,7 @@
         <f>'EB1'!M$2</f>
         <v>OPP</v>
       </c>
-      <c r="E24" s="113">
+      <c r="E24" s="115">
         <f>-'EB1'!M$7/-SUM('EB1'!$G$7:$M$7)</f>
         <v>0</v>
       </c>
@@ -7340,7 +7297,7 @@
     <row r="28" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B28" s="24"/>
       <c r="D28" s="24"/>
-      <c r="E28" s="99"/>
+      <c r="E28" s="101"/>
       <c r="F28" s="12"/>
       <c r="G28" s="78"/>
       <c r="H28" s="11"/>
@@ -7348,7 +7305,7 @@
     <row r="29" spans="2:18" x14ac:dyDescent="0.25">
       <c r="B29" s="24"/>
       <c r="D29" s="24"/>
-      <c r="E29" s="99"/>
+      <c r="E29" s="101"/>
       <c r="F29" s="12"/>
       <c r="G29" s="78"/>
       <c r="H29" s="11"/>
@@ -7368,13 +7325,13 @@
     <row r="34" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B34" s="42"/>
       <c r="C34" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="35" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B35" s="72"/>
       <c r="C35" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -7415,23 +7372,23 @@
   <sheetData>
     <row r="1" spans="2:21" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="G1" s="8"/>
       <c r="I1" s="8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="2" spans="2:21" ht="31.2" x14ac:dyDescent="0.3">
@@ -7457,46 +7414,46 @@
       </c>
       <c r="G2" s="10"/>
       <c r="I2" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="M2" s="105" t="s">
+        <v>101</v>
+      </c>
+      <c r="M2" s="107" t="s">
         <v>14</v>
       </c>
-      <c r="N2" s="105"/>
-      <c r="O2" s="106"/>
-      <c r="P2" s="106"/>
-      <c r="Q2" s="106"/>
-      <c r="R2" s="106"/>
-      <c r="S2" s="106"/>
-      <c r="T2" s="106"/>
-      <c r="U2" s="106"/>
+      <c r="N2" s="107"/>
+      <c r="O2" s="108"/>
+      <c r="P2" s="108"/>
+      <c r="Q2" s="108"/>
+      <c r="R2" s="108"/>
+      <c r="S2" s="108"/>
+      <c r="T2" s="108"/>
+      <c r="U2" s="108"/>
     </row>
     <row r="3" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="M3" s="107" t="s">
+      <c r="M3" s="109" t="s">
         <v>7</v>
       </c>
-      <c r="N3" s="108" t="s">
+      <c r="N3" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="O3" s="107" t="s">
-        <v>0</v>
-      </c>
-      <c r="P3" s="107" t="s">
+      <c r="O3" s="109" t="s">
+        <v>0</v>
+      </c>
+      <c r="P3" s="109" t="s">
         <v>3</v>
       </c>
-      <c r="Q3" s="107" t="s">
+      <c r="Q3" s="109" t="s">
         <v>4</v>
       </c>
-      <c r="R3" s="107" t="s">
+      <c r="R3" s="109" t="s">
         <v>8</v>
       </c>
-      <c r="S3" s="107" t="s">
+      <c r="S3" s="109" t="s">
         <v>9</v>
       </c>
-      <c r="T3" s="107" t="s">
+      <c r="T3" s="109" t="s">
         <v>10</v>
       </c>
-      <c r="U3" s="107" t="s">
+      <c r="U3" s="109" t="s">
         <v>12</v>
       </c>
     </row>
@@ -7508,31 +7465,31 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
-      <c r="M4" s="109" t="s">
-        <v>36</v>
-      </c>
-      <c r="N4" s="109" t="s">
+      <c r="M4" s="111" t="s">
+        <v>37</v>
+      </c>
+      <c r="N4" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="O4" s="109" t="s">
+      <c r="O4" s="111" t="s">
         <v>26</v>
       </c>
-      <c r="P4" s="109" t="s">
+      <c r="P4" s="111" t="s">
         <v>27</v>
       </c>
-      <c r="Q4" s="109" t="s">
+      <c r="Q4" s="111" t="s">
         <v>4</v>
       </c>
-      <c r="R4" s="109" t="s">
-        <v>39</v>
-      </c>
-      <c r="S4" s="109" t="s">
+      <c r="R4" s="111" t="s">
         <v>40</v>
       </c>
-      <c r="T4" s="109" t="s">
+      <c r="S4" s="111" t="s">
+        <v>41</v>
+      </c>
+      <c r="T4" s="111" t="s">
         <v>28</v>
       </c>
-      <c r="U4" s="109" t="s">
+      <c r="U4" s="111" t="s">
         <v>29</v>
       </c>
     </row>
@@ -7544,25 +7501,25 @@
       <c r="F5" s="9"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
-      <c r="M5" s="106" t="s">
-        <v>84</v>
-      </c>
-      <c r="N5" s="110"/>
-      <c r="O5" s="106" t="str">
+      <c r="M5" s="108" t="s">
+        <v>85</v>
+      </c>
+      <c r="N5" s="112"/>
+      <c r="O5" s="108" t="str">
         <f>LEFT($M$5,1)&amp;LEFT(B2,1)&amp;'EB1'!$C$20</f>
         <v>DIBOIL</v>
       </c>
-      <c r="P5" s="106" t="str">
+      <c r="P5" s="108" t="str">
         <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB1'!$X$20</f>
         <v>Demand Industry Sector - Boiler</v>
       </c>
-      <c r="Q5" s="106" t="s">
-        <v>77</v>
-      </c>
-      <c r="R5" s="106"/>
-      <c r="S5" s="106"/>
-      <c r="T5" s="106"/>
-      <c r="U5" s="106"/>
+      <c r="Q5" s="108" t="s">
+        <v>78</v>
+      </c>
+      <c r="R5" s="108"/>
+      <c r="S5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="108"/>
     </row>
     <row r="6" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="9"/>
@@ -7572,25 +7529,25 @@
       <c r="F6" s="9"/>
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
-      <c r="M6" s="136" t="s">
-        <v>84</v>
-      </c>
-      <c r="N6" s="130"/>
-      <c r="O6" s="138" t="str">
+      <c r="M6" s="108" t="s">
+        <v>85</v>
+      </c>
+      <c r="N6" s="112"/>
+      <c r="O6" s="108" t="str">
         <f>LEFT($M$5,1)&amp;LEFT(B2,1)&amp;'EB1'!$C$21</f>
         <v>DIOAPP</v>
       </c>
-      <c r="P6" s="139" t="str">
+      <c r="P6" s="108" t="str">
         <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB1'!$X$21</f>
         <v>Demand Industry Sector - Other Appliance</v>
       </c>
-      <c r="Q6" s="106" t="s">
-        <v>77</v>
-      </c>
-      <c r="R6" s="106"/>
-      <c r="S6" s="106"/>
-      <c r="T6" s="106"/>
-      <c r="U6" s="106"/>
+      <c r="Q6" s="108" t="s">
+        <v>78</v>
+      </c>
+      <c r="R6" s="108"/>
+      <c r="S6" s="108"/>
+      <c r="T6" s="108"/>
+      <c r="U6" s="108"/>
     </row>
     <row r="7" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="9"/>
@@ -7600,25 +7557,25 @@
       <c r="F7" s="9"/>
       <c r="G7" s="9"/>
       <c r="H7" s="9"/>
-      <c r="M7" s="106" t="s">
-        <v>84</v>
-      </c>
-      <c r="N7" s="110"/>
-      <c r="O7" s="106" t="str">
+      <c r="M7" s="108" t="s">
+        <v>85</v>
+      </c>
+      <c r="N7" s="112"/>
+      <c r="O7" s="108" t="str">
         <f>LEFT($M$5,1)&amp;LEFT(B2,1)&amp;'EB1'!$C$22</f>
         <v>DICOMP</v>
       </c>
-      <c r="P7" s="106" t="str">
+      <c r="P7" s="108" t="str">
         <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB1'!$X$22</f>
         <v>Demand Industry Sector - Compressor</v>
       </c>
-      <c r="Q7" s="106" t="s">
-        <v>77</v>
-      </c>
-      <c r="R7" s="106"/>
-      <c r="S7" s="106"/>
-      <c r="T7" s="106"/>
-      <c r="U7" s="106"/>
+      <c r="Q7" s="108" t="s">
+        <v>78</v>
+      </c>
+      <c r="R7" s="108"/>
+      <c r="S7" s="108"/>
+      <c r="T7" s="108"/>
+      <c r="U7" s="108"/>
     </row>
     <row r="8" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8" s="9"/>
@@ -7628,55 +7585,53 @@
       <c r="F8" s="9"/>
       <c r="G8" s="9"/>
       <c r="H8" s="9"/>
-      <c r="M8" s="106" t="s">
-        <v>84</v>
-      </c>
-      <c r="N8" s="110"/>
-      <c r="O8" s="106" t="str">
+      <c r="M8" s="108" t="s">
+        <v>85</v>
+      </c>
+      <c r="N8" s="112"/>
+      <c r="O8" s="108" t="str">
         <f>LEFT($M$5,1)&amp;LEFT(B2,1)&amp;'EB1'!$C$23</f>
         <v>DIPUMP</v>
       </c>
-      <c r="P8" s="106" t="str">
+      <c r="P8" s="108" t="str">
         <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB1'!$X$23</f>
         <v>Demand Industry Sector - Pump</v>
       </c>
-      <c r="Q8" s="106" t="s">
-        <v>77</v>
-      </c>
-      <c r="R8" s="106"/>
-      <c r="S8" s="106"/>
-      <c r="T8" s="106"/>
-      <c r="U8" s="106"/>
+      <c r="Q8" s="108" t="s">
+        <v>78</v>
+      </c>
+      <c r="R8" s="108"/>
+      <c r="S8" s="108"/>
+      <c r="T8" s="108"/>
+      <c r="U8" s="108"/>
     </row>
     <row r="9" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
-      <c r="D9" s="9" t="s">
-        <v>174</v>
-      </c>
+      <c r="D9" s="9"/>
       <c r="E9" s="9"/>
       <c r="F9" s="9"/>
       <c r="G9" s="9"/>
       <c r="H9" s="9"/>
-      <c r="M9" s="106" t="s">
-        <v>84</v>
-      </c>
-      <c r="N9" s="110"/>
-      <c r="O9" s="106" t="str">
+      <c r="M9" s="108" t="s">
+        <v>85</v>
+      </c>
+      <c r="N9" s="112"/>
+      <c r="O9" s="108" t="str">
         <f>LEFT($M$5,1)&amp;LEFT(B2,1)&amp;'EB1'!$C$24</f>
         <v>DIMOTO</v>
       </c>
-      <c r="P9" s="106" t="str">
+      <c r="P9" s="108" t="str">
         <f>LEFT($D$2,6)&amp;" "&amp;$C$2&amp; " Sector - "&amp;'EB1'!$X$24</f>
         <v>Demand Industry Sector - Heavy Motor</v>
       </c>
-      <c r="Q9" s="106" t="s">
-        <v>77</v>
-      </c>
-      <c r="R9" s="106"/>
-      <c r="S9" s="106"/>
-      <c r="T9" s="106"/>
-      <c r="U9" s="106"/>
+      <c r="Q9" s="108" t="s">
+        <v>78</v>
+      </c>
+      <c r="R9" s="108"/>
+      <c r="S9" s="108"/>
+      <c r="T9" s="108"/>
+      <c r="U9" s="108"/>
     </row>
     <row r="10" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10" s="9"/>
@@ -7686,32 +7641,32 @@
       <c r="F10" s="9"/>
       <c r="G10" s="9"/>
       <c r="H10" s="9"/>
-      <c r="M10" s="110" t="s">
-        <v>104</v>
-      </c>
-      <c r="N10" s="110"/>
-      <c r="O10" s="110" t="str">
+      <c r="M10" s="112" t="s">
+        <v>105</v>
+      </c>
+      <c r="N10" s="112"/>
+      <c r="O10" s="112" t="str">
         <f>$B$2&amp;'EB1'!$C$27</f>
         <v>INDCO2</v>
       </c>
-      <c r="P10" s="110" t="str">
+      <c r="P10" s="112" t="str">
         <f>$C$2&amp;" "&amp;'EB1'!$C$28</f>
         <v>Industry Carbon dioxide</v>
       </c>
-      <c r="Q10" s="110" t="str">
+      <c r="Q10" s="112" t="str">
         <f>'EB1'!$AA$2</f>
         <v>kt</v>
       </c>
-      <c r="R10" s="106"/>
-      <c r="S10" s="106"/>
-      <c r="T10" s="106"/>
-      <c r="U10" s="106"/>
+      <c r="R10" s="108"/>
+      <c r="S10" s="108"/>
+      <c r="T10" s="108"/>
+      <c r="U10" s="108"/>
     </row>
     <row r="11" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="R11" s="110"/>
-      <c r="S11" s="110"/>
-      <c r="T11" s="110"/>
-      <c r="U11" s="110"/>
+      <c r="R11" s="112"/>
+      <c r="S11" s="112"/>
+      <c r="T11" s="112"/>
+      <c r="U11" s="112"/>
     </row>
     <row r="12" spans="2:21" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B12" s="9"/>
@@ -7721,15 +7676,15 @@
       <c r="F12" s="9"/>
       <c r="G12" s="9"/>
       <c r="H12" s="9"/>
-      <c r="M12" s="106"/>
-      <c r="N12" s="110"/>
-      <c r="O12" s="106"/>
-      <c r="P12" s="106"/>
-      <c r="Q12" s="106"/>
-      <c r="R12" s="106"/>
-      <c r="S12" s="106"/>
-      <c r="T12" s="106"/>
-      <c r="U12" s="106"/>
+      <c r="M12" s="108"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="108"/>
+      <c r="P12" s="108"/>
+      <c r="Q12" s="108"/>
+      <c r="R12" s="108"/>
+      <c r="S12" s="108"/>
+      <c r="T12" s="108"/>
+      <c r="U12" s="108"/>
     </row>
     <row r="14" spans="2:21" x14ac:dyDescent="0.25">
       <c r="D14" s="4" t="s">
@@ -7741,17 +7696,17 @@
       <c r="I14" s="4"/>
       <c r="J14" s="4"/>
       <c r="K14" s="14"/>
-      <c r="M14" s="105" t="s">
+      <c r="M14" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="N14" s="105"/>
-      <c r="O14" s="110"/>
-      <c r="P14" s="110"/>
-      <c r="Q14" s="110"/>
-      <c r="R14" s="110"/>
-      <c r="S14" s="110"/>
-      <c r="T14" s="110"/>
-      <c r="U14" s="110"/>
+      <c r="N14" s="107"/>
+      <c r="O14" s="112"/>
+      <c r="P14" s="112"/>
+      <c r="Q14" s="112"/>
+      <c r="R14" s="112"/>
+      <c r="S14" s="112"/>
+      <c r="T14" s="112"/>
+      <c r="U14" s="112"/>
     </row>
     <row r="15" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B15" s="18" t="s">
@@ -7764,55 +7719,55 @@
         <v>6</v>
       </c>
       <c r="E15" s="81" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F15" s="81" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="G15" s="81" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H15" s="81" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="I15" s="81" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J15" s="4"/>
-      <c r="K15" s="118" t="s">
+      <c r="K15" s="120" t="s">
         <v>35</v>
       </c>
-      <c r="M15" s="107" t="s">
+      <c r="M15" s="109" t="s">
         <v>11</v>
       </c>
-      <c r="N15" s="108" t="s">
+      <c r="N15" s="110" t="s">
         <v>30</v>
       </c>
-      <c r="O15" s="107" t="s">
+      <c r="O15" s="109" t="s">
         <v>1</v>
       </c>
-      <c r="P15" s="107" t="s">
+      <c r="P15" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="Q15" s="107" t="s">
+      <c r="Q15" s="109" t="s">
         <v>16</v>
       </c>
-      <c r="R15" s="107" t="s">
+      <c r="R15" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="S15" s="107" t="s">
+      <c r="S15" s="109" t="s">
         <v>18</v>
       </c>
-      <c r="T15" s="107" t="s">
+      <c r="T15" s="109" t="s">
         <v>19</v>
       </c>
-      <c r="U15" s="107" t="s">
+      <c r="U15" s="109" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="16" spans="2:21" ht="31.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="16" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C16" s="16" t="s">
         <v>32</v>
@@ -7824,89 +7779,89 @@
         <v>34</v>
       </c>
       <c r="F16" s="16" t="s">
-        <v>90</v>
-      </c>
-      <c r="G16" s="91" t="s">
-        <v>98</v>
+        <v>91</v>
+      </c>
+      <c r="G16" s="93" t="s">
+        <v>99</v>
       </c>
       <c r="H16" s="16" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="I16" s="16" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="J16" s="4"/>
-      <c r="K16" s="118" t="s">
-        <v>177</v>
-      </c>
-      <c r="M16" s="109" t="s">
-        <v>37</v>
-      </c>
-      <c r="N16" s="109" t="s">
+      <c r="K16" s="120" t="s">
+        <v>180</v>
+      </c>
+      <c r="M16" s="111" t="s">
+        <v>38</v>
+      </c>
+      <c r="N16" s="111" t="s">
         <v>31</v>
       </c>
-      <c r="O16" s="109" t="s">
+      <c r="O16" s="111" t="s">
         <v>21</v>
       </c>
-      <c r="P16" s="109" t="s">
+      <c r="P16" s="111" t="s">
         <v>22</v>
       </c>
-      <c r="Q16" s="109" t="s">
+      <c r="Q16" s="111" t="s">
         <v>23</v>
       </c>
-      <c r="R16" s="109" t="s">
+      <c r="R16" s="111" t="s">
         <v>24</v>
       </c>
-      <c r="S16" s="109" t="s">
+      <c r="S16" s="111" t="s">
+        <v>43</v>
+      </c>
+      <c r="T16" s="111" t="s">
         <v>42</v>
       </c>
-      <c r="T16" s="109" t="s">
-        <v>41</v>
-      </c>
-      <c r="U16" s="109" t="s">
+      <c r="U16" s="111" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="17" spans="2:21" ht="21.6" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B17" s="15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="13" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F17" s="13"/>
-      <c r="G17" s="82"/>
+      <c r="G17" s="83"/>
       <c r="H17" s="13" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="13"/>
-      <c r="M17" s="109" t="s">
-        <v>82</v>
-      </c>
-      <c r="N17" s="109"/>
-      <c r="O17" s="109"/>
-      <c r="P17" s="109"/>
-      <c r="Q17" s="109"/>
-      <c r="R17" s="109"/>
-      <c r="S17" s="109"/>
-      <c r="T17" s="109"/>
-      <c r="U17" s="109"/>
+      <c r="M17" s="111" t="s">
+        <v>83</v>
+      </c>
+      <c r="N17" s="111"/>
+      <c r="O17" s="111"/>
+      <c r="P17" s="111"/>
+      <c r="Q17" s="111"/>
+      <c r="R17" s="111"/>
+      <c r="S17" s="111"/>
+      <c r="T17" s="111"/>
+      <c r="U17" s="111"/>
     </row>
     <row r="18" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B18" s="110" t="str">
+      <c r="B18" s="112" t="str">
         <f t="shared" ref="B18:B24" si="0">O18</f>
         <v>IBOILECOA</v>
       </c>
       <c r="C18" t="s">
-        <v>173</v>
-      </c>
-      <c r="D18" s="110" t="str">
+        <v>176</v>
+      </c>
+      <c r="D18" s="112" t="str">
         <f>$O$5</f>
         <v>DIBOIL</v>
       </c>
@@ -7914,52 +7869,52 @@
         <f>'EB1'!$D$7*'EB1'!$D$20/(G18*H18)*1.01</f>
         <v>1.3022033997716895</v>
       </c>
-      <c r="F18" s="119">
+      <c r="F18" s="121">
         <v>0.8</v>
       </c>
-      <c r="G18" s="119">
+      <c r="G18" s="121">
         <v>0.5</v>
       </c>
-      <c r="H18" s="117">
+      <c r="H18" s="119">
         <v>31.536000000000001</v>
       </c>
       <c r="I18" s="42">
         <v>30</v>
       </c>
       <c r="J18" s="17"/>
-      <c r="K18" s="120">
+      <c r="K18" s="122">
         <f t="shared" ref="K18:K25" si="1">E18*G18*H18</f>
         <v>20.533143207600002</v>
       </c>
-      <c r="M18" s="106" t="s">
-        <v>96</v>
-      </c>
-      <c r="O18" s="110" t="str">
+      <c r="M18" s="108" t="s">
+        <v>97</v>
+      </c>
+      <c r="O18" s="112" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$20&amp;$I$2&amp;'EB1'!D$2</f>
         <v>IBOILECOA</v>
       </c>
-      <c r="P18" s="110" t="str">
+      <c r="P18" s="112" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$20&amp;" - "&amp;'EB1'!$D$3</f>
         <v>Demand Technologies Industry Sector - Existing Boiler - Solid Fuels</v>
       </c>
-      <c r="Q18" s="110" t="str">
+      <c r="Q18" s="112" t="str">
         <f t="shared" ref="Q18:Q26" si="2">$E$2</f>
         <v>PJ</v>
       </c>
-      <c r="R18" s="110" t="str">
+      <c r="R18" s="112" t="str">
         <f t="shared" ref="R18:R26" si="3">$E$2&amp;"a"</f>
         <v>PJa</v>
       </c>
     </row>
     <row r="19" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B19" s="110" t="str">
+      <c r="B19" s="112" t="str">
         <f t="shared" si="0"/>
         <v>IBOILEBIO</v>
       </c>
       <c r="C19" t="s">
-        <v>175</v>
-      </c>
-      <c r="D19" s="110" t="str">
+        <v>178</v>
+      </c>
+      <c r="D19" s="112" t="str">
         <f>$O$5</f>
         <v>DIBOIL</v>
       </c>
@@ -7967,51 +7922,51 @@
         <f>'EB1'!$O$7*'EB1'!$O$20/(G19*H19)*1.01</f>
         <v>3.8442582643835617</v>
       </c>
-      <c r="F19" s="119">
+      <c r="F19" s="121">
         <v>0.85</v>
       </c>
-      <c r="G19" s="119">
+      <c r="G19" s="121">
         <v>0.5</v>
       </c>
-      <c r="H19" s="117">
+      <c r="H19" s="119">
         <v>31.536000000000001</v>
       </c>
       <c r="I19" s="42">
         <v>30</v>
       </c>
-      <c r="K19" s="120">
+      <c r="K19" s="122">
         <f t="shared" si="1"/>
         <v>60.616264312800006</v>
       </c>
-      <c r="M19" s="106" t="s">
-        <v>96</v>
-      </c>
-      <c r="O19" s="110" t="str">
+      <c r="M19" s="108" t="s">
+        <v>97</v>
+      </c>
+      <c r="O19" s="112" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$20&amp;$I$2&amp;'EB1'!O$2</f>
         <v>IBOILEBIO</v>
       </c>
-      <c r="P19" s="110" t="str">
+      <c r="P19" s="112" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$20&amp;" - "&amp;'EB1'!$O$3</f>
         <v>Demand Technologies Industry Sector - Existing Boiler - Biomass</v>
       </c>
-      <c r="Q19" s="110" t="str">
+      <c r="Q19" s="112" t="str">
         <f t="shared" si="2"/>
         <v>PJ</v>
       </c>
-      <c r="R19" s="110" t="str">
+      <c r="R19" s="112" t="str">
         <f t="shared" si="3"/>
         <v>PJa</v>
       </c>
     </row>
     <row r="20" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B20" s="110" t="str">
+      <c r="B20" s="112" t="str">
         <f t="shared" si="0"/>
         <v>IBOILEELC</v>
       </c>
       <c r="C20" t="s">
-        <v>176</v>
-      </c>
-      <c r="D20" s="110" t="str">
+        <v>179</v>
+      </c>
+      <c r="D20" s="112" t="str">
         <f>$O$5</f>
         <v>DIBOIL</v>
       </c>
@@ -8019,155 +7974,155 @@
         <f>'EB1'!$U$7*'EB1'!$U$20/(G20*H20)*1.01</f>
         <v>0</v>
       </c>
-      <c r="F20" s="119">
+      <c r="F20" s="121">
         <v>0.8</v>
       </c>
-      <c r="G20" s="119">
+      <c r="G20" s="121">
         <v>0.5</v>
       </c>
-      <c r="H20" s="117">
+      <c r="H20" s="119">
         <v>31.536000000000001</v>
       </c>
       <c r="I20" s="42">
         <v>30</v>
       </c>
-      <c r="K20" s="120">
+      <c r="K20" s="122">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="M20" s="106" t="s">
-        <v>96</v>
-      </c>
-      <c r="O20" s="110" t="str">
+      <c r="M20" s="108" t="s">
+        <v>97</v>
+      </c>
+      <c r="O20" s="112" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$20&amp;$I$2&amp;'EB1'!U$2</f>
         <v>IBOILEELC</v>
       </c>
-      <c r="P20" s="110" t="str">
+      <c r="P20" s="112" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$20&amp;" - "&amp;'EB1'!$U$3</f>
         <v>Demand Technologies Industry Sector - Existing Boiler - Electricity</v>
       </c>
-      <c r="Q20" s="110" t="str">
+      <c r="Q20" s="112" t="str">
         <f t="shared" si="2"/>
         <v>PJ</v>
       </c>
-      <c r="R20" s="110" t="str">
+      <c r="R20" s="112" t="str">
         <f t="shared" si="3"/>
         <v>PJa</v>
       </c>
     </row>
     <row r="21" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B21" s="140" t="s">
-        <v>181</v>
-      </c>
-      <c r="C21" s="141" t="s">
-        <v>182</v>
-      </c>
-      <c r="D21" s="110" t="str">
+      <c r="B21" s="112" t="str">
+        <f t="shared" si="0"/>
+        <v>IBOILEDSL</v>
+      </c>
+      <c r="C21" t="s">
+        <v>177</v>
+      </c>
+      <c r="D21" s="112" t="str">
         <f>$O$5</f>
         <v>DIBOIL</v>
       </c>
       <c r="E21" s="73">
-        <f>'EB1'!$L$7*'EB1'!$L$20/(G21*H21)*1.01</f>
-        <v>3.2449824200913241E-3</v>
-      </c>
-      <c r="F21" s="119">
+        <f>'EB1'!$G$7*'EB1'!$G$20/(G21*H21)*1.01</f>
+        <v>0.48148030063926939</v>
+      </c>
+      <c r="F21" s="121">
         <v>0.8</v>
       </c>
-      <c r="G21" s="119">
+      <c r="G21" s="121">
         <v>0.5</v>
       </c>
-      <c r="H21" s="117">
+      <c r="H21" s="119">
         <v>31.536000000000001</v>
       </c>
       <c r="I21" s="42">
         <v>30</v>
       </c>
-      <c r="J21" s="17"/>
-      <c r="K21" s="120">
-        <f t="shared" ref="K21" si="4">E21*G21*H21</f>
-        <v>5.1166882800000001E-2</v>
-      </c>
-      <c r="M21" s="140" t="s">
-        <v>96</v>
-      </c>
-      <c r="O21" s="140" t="s">
-        <v>181</v>
-      </c>
-      <c r="P21" s="140" t="s">
-        <v>183</v>
-      </c>
-      <c r="Q21" s="110" t="str">
+      <c r="K21" s="122">
+        <f t="shared" si="1"/>
+        <v>7.59198138048</v>
+      </c>
+      <c r="M21" s="108" t="s">
+        <v>97</v>
+      </c>
+      <c r="O21" s="112" t="str">
+        <f>LEFT($B$2)&amp;'EB1'!$C$20&amp;$I$2&amp;'EB1'!G$2</f>
+        <v>IBOILEDSL</v>
+      </c>
+      <c r="P21" s="112" t="str">
+        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$20&amp;" - "&amp;'EB1'!$G$3</f>
+        <v>Demand Technologies Industry Sector - Existing Boiler - Diesel oil</v>
+      </c>
+      <c r="Q21" s="112" t="str">
         <f t="shared" si="2"/>
         <v>PJ</v>
       </c>
-      <c r="R21" s="110" t="str">
+      <c r="R21" s="112" t="str">
         <f t="shared" si="3"/>
         <v>PJa</v>
       </c>
     </row>
     <row r="22" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B22" s="128" t="str">
-        <f>O22</f>
-        <v>IOAPPEDSL</v>
-      </c>
-      <c r="C22" s="129" t="s">
-        <v>174</v>
-      </c>
-      <c r="D22" s="130" t="str">
+      <c r="B22" s="112" t="str">
+        <f t="shared" si="0"/>
+        <v>IOAPPEELC</v>
+      </c>
+      <c r="C22" t="s">
+        <v>179</v>
+      </c>
+      <c r="D22" s="112" t="str">
         <f>$O$6</f>
         <v>DIOAPP</v>
       </c>
-      <c r="E22" s="131">
-        <f>'EB1'!$G$7*'EB1'!$G$21/(G22*H22)*1.01</f>
-        <v>0.60185037579908673</v>
-      </c>
-      <c r="F22" s="132">
-        <v>0.2</v>
-      </c>
-      <c r="G22" s="132">
+      <c r="E22" s="73">
+        <f>'EB1'!$U$7*'EB1'!$U$21/(G22*H22)*1.01</f>
+        <v>0.24567332813926943</v>
+      </c>
+      <c r="F22" s="121">
+        <v>0.95</v>
+      </c>
+      <c r="G22" s="121">
         <v>0.5</v>
       </c>
-      <c r="H22" s="133">
+      <c r="H22" s="119">
         <v>31.536000000000001</v>
       </c>
-      <c r="I22" s="134">
+      <c r="I22" s="42">
         <v>10</v>
       </c>
-      <c r="J22" s="129"/>
-      <c r="K22" s="135">
-        <f>E22*G22*H22</f>
-        <v>9.4899767256000001</v>
-      </c>
-      <c r="M22" s="136" t="s">
-        <v>96</v>
-      </c>
-      <c r="N22" s="129"/>
-      <c r="O22" s="130" t="str">
-        <f>LEFT($B$2)&amp;'EB1'!$C$21&amp;$I$2&amp;'EB1'!G$2</f>
-        <v>IOAPPEDSL</v>
-      </c>
-      <c r="P22" s="130" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$21&amp;" - "&amp;'EB1'!$G$3</f>
-        <v>Demand Technologies Industry Sector - Existing Other Appliance - Diesel oil</v>
-      </c>
-      <c r="Q22" s="130" t="str">
+      <c r="K22" s="122">
+        <f t="shared" si="1"/>
+        <v>3.8737770381000005</v>
+      </c>
+      <c r="M22" s="108" t="s">
+        <v>97</v>
+      </c>
+      <c r="O22" s="112" t="str">
+        <f>LEFT($B$2)&amp;'EB1'!$C$21&amp;$I$2&amp;'EB1'!U$2</f>
+        <v>IOAPPEELC</v>
+      </c>
+      <c r="P22" s="112" t="str">
+        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$21&amp;" - "&amp;'EB1'!$U$3</f>
+        <v>Demand Technologies Industry Sector - Existing Other Appliance - Electricity</v>
+      </c>
+      <c r="Q22" s="112" t="str">
         <f t="shared" si="2"/>
         <v>PJ</v>
       </c>
-      <c r="R22" s="137" t="str">
+      <c r="R22" s="112" t="str">
         <f t="shared" si="3"/>
         <v>PJa</v>
       </c>
     </row>
     <row r="23" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B23" s="110" t="str">
+      <c r="B23" s="112" t="str">
         <f t="shared" si="0"/>
-        <v>IOAPPEELC</v>
+        <v>IOAPPEDSL</v>
       </c>
       <c r="C23" t="s">
-        <v>176</v>
-      </c>
-      <c r="D23" s="110" t="str">
+        <v>177</v>
+      </c>
+      <c r="D23" s="112" t="str">
         <f>$O$6</f>
         <v>DIOAPP</v>
       </c>
@@ -8175,51 +8130,51 @@
         <f>'EB1'!$U$7*'EB1'!$U$21/(G23*H23)*1.01</f>
         <v>0.24567332813926943</v>
       </c>
-      <c r="F23" s="119">
-        <v>0.95</v>
-      </c>
-      <c r="G23" s="119">
+      <c r="F23" s="121">
+        <v>0.2</v>
+      </c>
+      <c r="G23" s="121">
         <v>0.5</v>
       </c>
-      <c r="H23" s="117">
+      <c r="H23" s="119">
         <v>31.536000000000001</v>
       </c>
       <c r="I23" s="42">
         <v>10</v>
       </c>
-      <c r="K23" s="120">
-        <f t="shared" si="1"/>
+      <c r="K23" s="122">
+        <f>E23*G23*H23</f>
         <v>3.8737770381000005</v>
       </c>
-      <c r="M23" s="106" t="s">
-        <v>96</v>
-      </c>
-      <c r="O23" s="110" t="str">
-        <f>LEFT($B$2)&amp;'EB1'!$C$21&amp;$I$2&amp;'EB1'!U$2</f>
-        <v>IOAPPEELC</v>
-      </c>
-      <c r="P23" s="110" t="str">
-        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$21&amp;" - "&amp;'EB1'!$U$3</f>
-        <v>Demand Technologies Industry Sector - Existing Other Appliance - Electricity</v>
-      </c>
-      <c r="Q23" s="110" t="str">
+      <c r="M23" s="108" t="s">
+        <v>97</v>
+      </c>
+      <c r="O23" s="112" t="str">
+        <f>LEFT($B$2)&amp;'EB1'!$C$21&amp;$I$2&amp;'EB1'!G$2</f>
+        <v>IOAPPEDSL</v>
+      </c>
+      <c r="P23" s="112" t="str">
+        <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$21&amp;" - "&amp;'EB1'!$G$3</f>
+        <v>Demand Technologies Industry Sector - Existing Other Appliance - Diesel oil</v>
+      </c>
+      <c r="Q23" s="112" t="str">
         <f t="shared" si="2"/>
         <v>PJ</v>
       </c>
-      <c r="R23" s="110" t="str">
+      <c r="R23" s="112" t="str">
         <f t="shared" si="3"/>
         <v>PJa</v>
       </c>
     </row>
     <row r="24" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B24" s="110" t="str">
+      <c r="B24" s="112" t="str">
         <f t="shared" si="0"/>
         <v>ICOMPEELC</v>
       </c>
       <c r="C24" t="s">
-        <v>176</v>
-      </c>
-      <c r="D24" s="110" t="str">
+        <v>179</v>
+      </c>
+      <c r="D24" s="112" t="str">
         <f>$O$7</f>
         <v>DICOMP</v>
       </c>
@@ -8227,51 +8182,51 @@
         <f>'EB1'!$U$7*'EB1'!$U$22/(G24*H24)*1.01</f>
         <v>0.19653866251141555</v>
       </c>
-      <c r="F24" s="119">
+      <c r="F24" s="121">
         <v>0.95</v>
       </c>
-      <c r="G24" s="119">
+      <c r="G24" s="121">
         <v>0.5</v>
       </c>
-      <c r="H24" s="117">
+      <c r="H24" s="119">
         <v>31.536000000000001</v>
       </c>
       <c r="I24" s="42">
         <v>10</v>
       </c>
-      <c r="K24" s="120">
+      <c r="K24" s="122">
         <f t="shared" si="1"/>
         <v>3.0990216304800007</v>
       </c>
-      <c r="M24" s="106" t="s">
-        <v>96</v>
-      </c>
-      <c r="O24" s="110" t="str">
+      <c r="M24" s="108" t="s">
+        <v>97</v>
+      </c>
+      <c r="O24" s="112" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$22&amp;$I$2&amp;'EB1'!U$2</f>
         <v>ICOMPEELC</v>
       </c>
-      <c r="P24" s="110" t="str">
+      <c r="P24" s="112" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$22&amp;" - "&amp;'EB1'!$U$3</f>
         <v>Demand Technologies Industry Sector - Existing Compressor - Electricity</v>
       </c>
-      <c r="Q24" s="110" t="str">
+      <c r="Q24" s="112" t="str">
         <f t="shared" si="2"/>
         <v>PJ</v>
       </c>
-      <c r="R24" s="110" t="str">
+      <c r="R24" s="112" t="str">
         <f t="shared" si="3"/>
         <v>PJa</v>
       </c>
     </row>
     <row r="25" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B25" s="110" t="str">
+      <c r="B25" s="112" t="str">
         <f>O25</f>
         <v>IPUMPEELC</v>
       </c>
       <c r="C25" t="s">
-        <v>176</v>
-      </c>
-      <c r="D25" s="110" t="str">
+        <v>179</v>
+      </c>
+      <c r="D25" s="112" t="str">
         <f>$O$8</f>
         <v>DIPUMP</v>
       </c>
@@ -8279,52 +8234,52 @@
         <f>'EB1'!$U$7*'EB1'!$U$23/(G25*H25)*1.01</f>
         <v>0.24567332813926943</v>
       </c>
-      <c r="F25" s="119">
+      <c r="F25" s="121">
         <v>0.6</v>
       </c>
-      <c r="G25" s="119">
+      <c r="G25" s="121">
         <v>0.5</v>
       </c>
-      <c r="H25" s="117">
+      <c r="H25" s="119">
         <v>31.536000000000001</v>
       </c>
       <c r="I25" s="42">
         <v>10</v>
       </c>
-      <c r="J25" s="101"/>
-      <c r="K25" s="120">
+      <c r="J25" s="103"/>
+      <c r="K25" s="122">
         <f t="shared" si="1"/>
         <v>3.8737770381000005</v>
       </c>
-      <c r="M25" s="106" t="s">
-        <v>96</v>
-      </c>
-      <c r="O25" s="110" t="str">
+      <c r="M25" s="108" t="s">
+        <v>97</v>
+      </c>
+      <c r="O25" s="112" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$23&amp;$I$2&amp;'EB1'!U$2</f>
         <v>IPUMPEELC</v>
       </c>
-      <c r="P25" s="110" t="str">
+      <c r="P25" s="112" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$23&amp;" - "&amp;'EB1'!$U$3</f>
         <v>Demand Technologies Industry Sector - Existing Pump - Electricity</v>
       </c>
-      <c r="Q25" s="110" t="str">
+      <c r="Q25" s="112" t="str">
         <f t="shared" si="2"/>
         <v>PJ</v>
       </c>
-      <c r="R25" s="110" t="str">
+      <c r="R25" s="112" t="str">
         <f t="shared" si="3"/>
         <v>PJa</v>
       </c>
     </row>
     <row r="26" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="B26" s="110" t="str">
+      <c r="B26" s="112" t="str">
         <f>O26</f>
         <v>IMOTOEELC</v>
       </c>
       <c r="C26" t="s">
-        <v>176</v>
-      </c>
-      <c r="D26" s="110" t="str">
+        <v>179</v>
+      </c>
+      <c r="D26" s="112" t="str">
         <f>$O$9</f>
         <v>DIMOTO</v>
       </c>
@@ -8332,72 +8287,72 @@
         <f>'EB1'!$U$7*'EB1'!$U$24/(G26*H26)*1.01</f>
         <v>0.28574701535038105</v>
       </c>
-      <c r="F26" s="119">
+      <c r="F26" s="121">
         <v>0.9</v>
       </c>
-      <c r="G26" s="119">
+      <c r="G26" s="121">
         <v>0.5</v>
       </c>
-      <c r="H26" s="117">
+      <c r="H26" s="119">
         <v>32.536000000000001</v>
       </c>
       <c r="I26" s="42">
         <v>10</v>
       </c>
-      <c r="J26" s="101"/>
-      <c r="K26" s="120">
-        <f t="shared" ref="K26" si="5">E26*G26*H26</f>
+      <c r="J26" s="103"/>
+      <c r="K26" s="122">
+        <f t="shared" ref="K26" si="4">E26*G26*H26</f>
         <v>4.648532445719999</v>
       </c>
-      <c r="M26" s="106" t="s">
-        <v>96</v>
-      </c>
-      <c r="O26" s="110" t="str">
+      <c r="M26" s="108" t="s">
+        <v>97</v>
+      </c>
+      <c r="O26" s="112" t="str">
         <f>LEFT($B$2)&amp;'EB1'!$C$24&amp;$I$2&amp;'EB1'!U$2</f>
         <v>IMOTOEELC</v>
       </c>
-      <c r="P26" s="110" t="str">
+      <c r="P26" s="112" t="str">
         <f>$D$2&amp;" "&amp;$C$2&amp; " Sector - "&amp;""&amp;$I$1&amp;" "&amp;'EB1'!$X$24&amp;" - "&amp;'EB1'!$U$3</f>
         <v>Demand Technologies Industry Sector - Existing Heavy Motor - Electricity</v>
       </c>
-      <c r="Q26" s="110" t="str">
+      <c r="Q26" s="112" t="str">
         <f t="shared" si="2"/>
         <v>PJ</v>
       </c>
-      <c r="R26" s="110" t="str">
+      <c r="R26" s="112" t="str">
         <f t="shared" si="3"/>
         <v>PJa</v>
       </c>
     </row>
     <row r="27" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I27" s="101"/>
-      <c r="J27" s="101"/>
+      <c r="I27" s="103"/>
+      <c r="J27" s="103"/>
       <c r="K27" s="17"/>
     </row>
     <row r="28" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I28" s="101"/>
-      <c r="J28" s="101"/>
+      <c r="I28" s="103"/>
+      <c r="J28" s="103"/>
       <c r="K28" s="17"/>
     </row>
     <row r="29" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B29" s="42"/>
       <c r="C29" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="I29" s="101"/>
-      <c r="J29" s="101"/>
+        <v>143</v>
+      </c>
+      <c r="I29" s="103"/>
+      <c r="J29" s="103"/>
     </row>
     <row r="30" spans="2:21" x14ac:dyDescent="0.25">
       <c r="B30" s="72"/>
       <c r="C30" s="1" t="s">
-        <v>141</v>
-      </c>
-      <c r="I30" s="101"/>
-      <c r="J30" s="101"/>
+        <v>144</v>
+      </c>
+      <c r="I30" s="103"/>
+      <c r="J30" s="103"/>
     </row>
     <row r="31" spans="2:21" x14ac:dyDescent="0.25">
-      <c r="I31" s="101"/>
-      <c r="J31" s="101"/>
+      <c r="I31" s="103"/>
+      <c r="J31" s="103"/>
       <c r="L31" s="1"/>
     </row>
     <row r="32" spans="2:21" x14ac:dyDescent="0.25">
@@ -8439,24 +8394,24 @@
   <sheetData>
     <row r="1" spans="2:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="B1" s="8" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C1" s="8" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E1" s="8" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="2" spans="2:10" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B2" s="10" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
@@ -8470,83 +8425,163 @@
       </c>
     </row>
     <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D5" s="3"/>
+      <c r="E5" s="1"/>
       <c r="I5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="J5" s="1"/>
     </row>
     <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B6" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E6" s="85">
+        <v>2021</v>
+      </c>
       <c r="G6" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>0</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J6" s="2">
         <v>2021</v>
       </c>
     </row>
     <row r="7" spans="2:10" ht="31.2" x14ac:dyDescent="0.25">
+      <c r="B7" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C7" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D7" s="16" t="s">
+        <v>138</v>
+      </c>
+      <c r="E7" s="82" t="s">
+        <v>36</v>
+      </c>
       <c r="G7" s="16" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H7" s="16" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I7" s="16"/>
       <c r="J7" s="16"/>
     </row>
     <row r="8" spans="2:10" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="82" t="str">
+        <f>E2</f>
+        <v>PJ</v>
+      </c>
       <c r="G8" s="15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="H8" s="15"/>
       <c r="I8" s="15"/>
       <c r="J8" s="15"/>
     </row>
     <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B9" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" t="str">
+        <f>DemTechs_IND!$O5</f>
+        <v>DIBOIL</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="76">
+        <f>SUM(DemTechs_IND!K18:K21)</f>
+        <v>88.741388900879997</v>
+      </c>
       <c r="G9" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H9" s="1" t="str">
         <f>DemTechs_IND!$O$5</f>
         <v>DIBOIL</v>
       </c>
       <c r="I9" s="24" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J9" s="73">
         <v>0.35</v>
       </c>
     </row>
     <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B10" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" t="str">
+        <f>DemTechs_IND!$O6</f>
+        <v>DIOAPP</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="76">
+        <f>DemTechs_IND!K22</f>
+        <v>3.8737770381000005</v>
+      </c>
       <c r="G10" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H10" s="1" t="str">
         <f>DemTechs_IND!$O$5</f>
         <v>DIBOIL</v>
       </c>
       <c r="I10" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J10" s="73">
         <v>0.15</v>
       </c>
     </row>
     <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C11" t="str">
+        <f>DemTechs_IND!$O7</f>
+        <v>DICOMP</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E11" s="76">
+        <f>DemTechs_IND!K24</f>
+        <v>3.0990216304800007</v>
+      </c>
       <c r="G11" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H11" s="1" t="str">
         <f>DemTechs_IND!$O$5</f>
         <v>DIBOIL</v>
       </c>
       <c r="I11" s="24" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J11" s="73">
         <f>1-J9-J10-J12</f>
@@ -8554,60 +8589,90 @@
       </c>
     </row>
     <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B12" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" t="str">
+        <f>DemTechs_IND!$O8</f>
+        <v>DIPUMP</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E12" s="76">
+        <f>DemTechs_IND!K25</f>
+        <v>3.8737770381000005</v>
+      </c>
       <c r="G12" s="28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H12" s="28" t="str">
         <f>DemTechs_IND!$O$5</f>
         <v>DIBOIL</v>
       </c>
       <c r="I12" s="29" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J12" s="77">
         <v>0.15</v>
       </c>
     </row>
     <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B13" t="s">
+        <v>35</v>
+      </c>
+      <c r="C13" t="str">
+        <f>DemTechs_IND!$O9</f>
+        <v>DIMOTO</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E13" s="76">
+        <f>DemTechs_IND!K26</f>
+        <v>4.648532445719999</v>
+      </c>
       <c r="G13" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H13" s="1" t="str">
         <f>DemTechs_IND!$O$6</f>
         <v>DIOAPP</v>
       </c>
       <c r="I13" s="24" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J13" s="73">
         <v>0.35</v>
       </c>
     </row>
     <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E14" s="26"/>
       <c r="G14" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H14" s="1" t="str">
         <f>DemTechs_IND!$O$6</f>
         <v>DIOAPP</v>
       </c>
       <c r="I14" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J14" s="73">
         <v>0.15</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E15" s="26"/>
       <c r="G15" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H15" s="1" t="str">
         <f>DemTechs_IND!$O$6</f>
         <v>DIOAPP</v>
       </c>
       <c r="I15" s="24" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J15" s="73">
         <f>1-J13-J14-J16</f>
@@ -8615,45 +8680,48 @@
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E16" s="26"/>
       <c r="G16" s="28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H16" s="28" t="str">
         <f>DemTechs_IND!$O$6</f>
         <v>DIOAPP</v>
       </c>
       <c r="I16" s="29" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J16" s="77">
         <v>0.15</v>
       </c>
     </row>
     <row r="17" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E17" s="26"/>
       <c r="G17" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H17" s="1" t="str">
         <f>DemTechs_IND!$O$7</f>
         <v>DICOMP</v>
       </c>
       <c r="I17" s="24" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J17" s="73">
         <v>0.35</v>
       </c>
     </row>
     <row r="18" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="E18" s="26"/>
       <c r="G18" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H18" s="1" t="str">
         <f>DemTechs_IND!$O$7</f>
         <v>DICOMP</v>
       </c>
       <c r="I18" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J18" s="73">
         <v>0.15</v>
@@ -8662,14 +8730,14 @@
     <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E19" s="26"/>
       <c r="G19" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H19" s="1" t="str">
         <f>DemTechs_IND!$O$7</f>
         <v>DICOMP</v>
       </c>
       <c r="I19" s="24" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J19" s="73">
         <f>1-J17-J18-J20</f>
@@ -8679,14 +8747,14 @@
     <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E20" s="26"/>
       <c r="G20" s="28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H20" s="28" t="str">
         <f>DemTechs_IND!$O$7</f>
         <v>DICOMP</v>
       </c>
       <c r="I20" s="29" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J20" s="77">
         <v>0.15</v>
@@ -8695,14 +8763,14 @@
     <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E21" s="26"/>
       <c r="G21" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H21" s="1" t="str">
         <f>DemTechs_IND!$O$8</f>
         <v>DIPUMP</v>
       </c>
       <c r="I21" s="24" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J21" s="73">
         <v>0.35</v>
@@ -8711,14 +8779,14 @@
     <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E22" s="26"/>
       <c r="G22" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H22" s="1" t="str">
         <f>DemTechs_IND!$O$8</f>
         <v>DIPUMP</v>
       </c>
       <c r="I22" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J22" s="73">
         <v>0.15</v>
@@ -8727,14 +8795,14 @@
     <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E23" s="26"/>
       <c r="G23" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H23" s="1" t="str">
         <f>DemTechs_IND!$O$8</f>
         <v>DIPUMP</v>
       </c>
       <c r="I23" s="24" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J23" s="73">
         <f>1-J21-J22-J24</f>
@@ -8744,14 +8812,14 @@
     <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E24" s="7"/>
       <c r="G24" s="28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H24" s="28" t="str">
         <f>DemTechs_IND!$O$8</f>
         <v>DIPUMP</v>
       </c>
       <c r="I24" s="29" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J24" s="77">
         <v>0.15</v>
@@ -8759,14 +8827,14 @@
     </row>
     <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G25" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H25" s="1" t="str">
         <f>DemTechs_IND!$O$9</f>
         <v>DIMOTO</v>
       </c>
       <c r="I25" s="24" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="J25" s="73">
         <v>0.35</v>
@@ -8775,14 +8843,14 @@
     <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="E26" s="7"/>
       <c r="G26" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H26" s="1" t="str">
         <f>DemTechs_IND!$O$9</f>
         <v>DIMOTO</v>
       </c>
       <c r="I26" s="24" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J26" s="73">
         <v>0.15</v>
@@ -8790,14 +8858,14 @@
     </row>
     <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G27" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H27" s="1" t="str">
         <f>DemTechs_IND!$O$9</f>
         <v>DIMOTO</v>
       </c>
       <c r="I27" s="24" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="J27" s="73">
         <f>1-J25-J26-J28</f>
@@ -8806,14 +8874,14 @@
     </row>
     <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G28" s="28" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H28" s="28" t="str">
         <f>DemTechs_IND!$O$9</f>
         <v>DIMOTO</v>
       </c>
       <c r="I28" s="29" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="J28" s="77">
         <v>0.15</v>
@@ -8822,13 +8890,13 @@
     <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="42"/>
       <c r="C32" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="33" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B33" s="72"/>
       <c r="C33" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -8847,7 +8915,7 @@
   <sheetData>
     <row r="3" spans="2:9" ht="17.399999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="33" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -8867,7 +8935,7 @@
     </row>
     <row r="5" spans="2:9" ht="17.399999999999999" x14ac:dyDescent="0.3">
       <c r="B5" s="31" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C5" s="32"/>
     </row>
@@ -8888,28 +8956,28 @@
         <v>INDOIL</v>
       </c>
       <c r="F6" s="36" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="G6" s="35"/>
       <c r="H6" s="1"/>
     </row>
     <row r="7" spans="2:9" ht="13.8" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B7" s="15" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="E7" s="15" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>139</v>
-      </c>
-      <c r="G7" s="100"/>
+        <v>142</v>
+      </c>
+      <c r="G7" s="102"/>
       <c r="H7" s="1"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
@@ -8935,13 +9003,13 @@
     <row r="23" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B23" s="42"/>
       <c r="C23" s="1" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
     </row>
     <row r="24" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B24" s="72"/>
       <c r="C24" s="1" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
